--- a/grupos/4ALCV - Estadisticos 20212.xlsx
+++ b/grupos/4ALCV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="137">
   <si>
     <t>Materia</t>
   </si>
@@ -173,25 +173,25 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
+    <t>Polanco Domínguez Rosa María</t>
+  </si>
+  <si>
     <t>Muñoz Rivadeneyra Salvador</t>
   </si>
   <si>
     <t>Flores Ovalle Victor</t>
   </si>
   <si>
+    <t>Ángel Martínez Noe Cristobal</t>
+  </si>
+  <si>
+    <t>Martínez Castillo Columba</t>
+  </si>
+  <si>
     <t>Rivera Serra Alma Lilian</t>
-  </si>
-  <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
-    <t>Polanco Domínguez Rosa María</t>
-  </si>
-  <si>
-    <t>Ángel Martínez Noe Cristobal</t>
-  </si>
-  <si>
-    <t>Martínez Castillo Columba</t>
   </si>
   <si>
     <t>NC</t>
@@ -930,7 +930,7 @@
         <v>13</v>
       </c>
       <c r="B4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>6</v>
@@ -945,10 +945,10 @@
         <v>6</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -993,7 +993,7 @@
         <v>-1</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X4">
         <v>6</v>
@@ -1008,10 +1008,10 @@
         <v>6</v>
       </c>
       <c r="AB4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC4">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -1019,7 +1019,7 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C5">
         <v>7</v>
@@ -1034,10 +1034,10 @@
         <v>9</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -1082,7 +1082,7 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X5">
         <v>7</v>
@@ -1097,10 +1097,10 @@
         <v>9</v>
       </c>
       <c r="AB5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC5">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1108,7 +1108,7 @@
         <v>15</v>
       </c>
       <c r="B6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C6">
         <v>9</v>
@@ -1123,10 +1123,10 @@
         <v>9</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -1171,7 +1171,7 @@
         <v>-1</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X6">
         <v>9</v>
@@ -1186,10 +1186,10 @@
         <v>9</v>
       </c>
       <c r="AB6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC6">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1197,7 +1197,7 @@
         <v>16</v>
       </c>
       <c r="B7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C7">
         <v>6</v>
@@ -1212,10 +1212,10 @@
         <v>9</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I7">
         <v>-1</v>
@@ -1260,7 +1260,7 @@
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X7">
         <v>6</v>
@@ -1275,10 +1275,10 @@
         <v>9</v>
       </c>
       <c r="AB7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC7">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1304,7 +1304,7 @@
         <v>-1</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I8">
         <v>-1</v>
@@ -1367,7 +1367,7 @@
         <v>-1</v>
       </c>
       <c r="AC8">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1390,10 +1390,10 @@
         <v>10</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I9">
         <v>-1</v>
@@ -1453,10 +1453,10 @@
         <v>10</v>
       </c>
       <c r="AB9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC9">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1464,7 +1464,7 @@
         <v>19</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C10">
         <v>-1</v>
@@ -1482,7 +1482,7 @@
         <v>-1</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I10">
         <v>-1</v>
@@ -1527,7 +1527,7 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X10">
         <v>-1</v>
@@ -1545,7 +1545,7 @@
         <v>-1</v>
       </c>
       <c r="AC10">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1568,10 +1568,10 @@
         <v>5</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -1631,10 +1631,10 @@
         <v>5</v>
       </c>
       <c r="AB11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC11">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1642,7 +1642,7 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C12">
         <v>9</v>
@@ -1657,10 +1657,10 @@
         <v>10</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -1705,7 +1705,7 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X12">
         <v>9</v>
@@ -1720,10 +1720,10 @@
         <v>10</v>
       </c>
       <c r="AB12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC12">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1731,7 +1731,7 @@
         <v>22</v>
       </c>
       <c r="B13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C13">
         <v>9</v>
@@ -1740,16 +1740,16 @@
         <v>-1</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F13">
         <v>6</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -1794,7 +1794,7 @@
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X13">
         <v>9</v>
@@ -1803,16 +1803,16 @@
         <v>-1</v>
       </c>
       <c r="Z13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA13">
         <v>6</v>
       </c>
       <c r="AB13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC13">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1820,7 +1820,7 @@
         <v>23</v>
       </c>
       <c r="B14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C14">
         <v>10</v>
@@ -1835,10 +1835,10 @@
         <v>9</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -1883,7 +1883,7 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X14">
         <v>10</v>
@@ -1898,10 +1898,10 @@
         <v>9</v>
       </c>
       <c r="AB14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC14">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1909,7 +1909,7 @@
         <v>24</v>
       </c>
       <c r="B15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C15">
         <v>10</v>
@@ -1924,10 +1924,10 @@
         <v>9</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -1972,7 +1972,7 @@
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X15">
         <v>10</v>
@@ -1987,10 +1987,10 @@
         <v>9</v>
       </c>
       <c r="AB15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC15">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1998,7 +1998,7 @@
         <v>25</v>
       </c>
       <c r="B16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C16">
         <v>9</v>
@@ -2013,10 +2013,10 @@
         <v>8</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -2061,7 +2061,7 @@
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X16">
         <v>9</v>
@@ -2076,10 +2076,10 @@
         <v>8</v>
       </c>
       <c r="AB16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC16">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -2087,7 +2087,7 @@
         <v>26</v>
       </c>
       <c r="B17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C17">
         <v>10</v>
@@ -2102,10 +2102,10 @@
         <v>8</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I17">
         <v>-1</v>
@@ -2150,7 +2150,7 @@
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X17">
         <v>10</v>
@@ -2165,10 +2165,10 @@
         <v>8</v>
       </c>
       <c r="AB17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC17">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2176,7 +2176,7 @@
         <v>27</v>
       </c>
       <c r="B18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C18">
         <v>9</v>
@@ -2191,10 +2191,10 @@
         <v>10</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I18">
         <v>-1</v>
@@ -2239,7 +2239,7 @@
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X18">
         <v>9</v>
@@ -2254,10 +2254,10 @@
         <v>10</v>
       </c>
       <c r="AB18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC18">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2318,7 +2318,7 @@
         <v>29</v>
       </c>
       <c r="B20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C20">
         <v>10</v>
@@ -2333,10 +2333,10 @@
         <v>9</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I20">
         <v>-1</v>
@@ -2381,7 +2381,7 @@
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X20">
         <v>10</v>
@@ -2396,10 +2396,10 @@
         <v>9</v>
       </c>
       <c r="AB20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC20">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2425,7 +2425,7 @@
         <v>-1</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -2488,7 +2488,7 @@
         <v>-1</v>
       </c>
       <c r="AC21">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2496,7 +2496,7 @@
         <v>31</v>
       </c>
       <c r="B22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C22">
         <v>8</v>
@@ -2511,10 +2511,10 @@
         <v>10</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -2559,7 +2559,7 @@
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>8</v>
@@ -2574,10 +2574,10 @@
         <v>10</v>
       </c>
       <c r="AB22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC22">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2585,7 +2585,7 @@
         <v>32</v>
       </c>
       <c r="B23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C23">
         <v>10</v>
@@ -2600,10 +2600,10 @@
         <v>8</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I23">
         <v>-1</v>
@@ -2648,7 +2648,7 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X23">
         <v>10</v>
@@ -2663,10 +2663,10 @@
         <v>8</v>
       </c>
       <c r="AB23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC23">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2674,7 +2674,7 @@
         <v>33</v>
       </c>
       <c r="B24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C24">
         <v>10</v>
@@ -2689,10 +2689,10 @@
         <v>9</v>
       </c>
       <c r="G24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -2737,7 +2737,7 @@
         <v>-1</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X24">
         <v>10</v>
@@ -2752,10 +2752,10 @@
         <v>9</v>
       </c>
       <c r="AB24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC24">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2763,7 +2763,7 @@
         <v>34</v>
       </c>
       <c r="B25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C25">
         <v>6</v>
@@ -2778,10 +2778,10 @@
         <v>10</v>
       </c>
       <c r="G25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I25">
         <v>-1</v>
@@ -2826,7 +2826,7 @@
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X25">
         <v>6</v>
@@ -2841,10 +2841,10 @@
         <v>10</v>
       </c>
       <c r="AB25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC25">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:29">
@@ -2852,7 +2852,7 @@
         <v>35</v>
       </c>
       <c r="B26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C26">
         <v>10</v>
@@ -2867,10 +2867,10 @@
         <v>8</v>
       </c>
       <c r="G26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I26">
         <v>-1</v>
@@ -2915,7 +2915,7 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X26">
         <v>10</v>
@@ -2930,10 +2930,10 @@
         <v>8</v>
       </c>
       <c r="AB26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC26">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -2941,7 +2941,7 @@
         <v>36</v>
       </c>
       <c r="B27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C27">
         <v>8</v>
@@ -2956,10 +2956,10 @@
         <v>6</v>
       </c>
       <c r="G27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -3004,7 +3004,7 @@
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X27">
         <v>8</v>
@@ -3019,10 +3019,10 @@
         <v>6</v>
       </c>
       <c r="AB27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC27">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -3030,7 +3030,7 @@
         <v>37</v>
       </c>
       <c r="B28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C28">
         <v>9</v>
@@ -3045,10 +3045,10 @@
         <v>10</v>
       </c>
       <c r="G28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I28">
         <v>-1</v>
@@ -3093,7 +3093,7 @@
         <v>-1</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X28">
         <v>9</v>
@@ -3108,10 +3108,10 @@
         <v>10</v>
       </c>
       <c r="AB28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC28">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3119,7 +3119,7 @@
         <v>38</v>
       </c>
       <c r="B29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="C29">
         <v>7</v>
@@ -3137,7 +3137,7 @@
         <v>-1</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I29">
         <v>-1</v>
@@ -3182,7 +3182,7 @@
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X29">
         <v>7</v>
@@ -3200,7 +3200,7 @@
         <v>-1</v>
       </c>
       <c r="AC29">
-        <v>-1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3223,10 +3223,10 @@
         <v>10</v>
       </c>
       <c r="G30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I30">
         <v>-1</v>
@@ -3286,10 +3286,10 @@
         <v>10</v>
       </c>
       <c r="AB30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC30">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3297,7 +3297,7 @@
         <v>40</v>
       </c>
       <c r="B31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C31">
         <v>8</v>
@@ -3312,10 +3312,10 @@
         <v>9</v>
       </c>
       <c r="G31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -3360,7 +3360,7 @@
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X31">
         <v>8</v>
@@ -3375,10 +3375,10 @@
         <v>9</v>
       </c>
       <c r="AB31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC31">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -3386,7 +3386,7 @@
         <v>41</v>
       </c>
       <c r="B32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C32">
         <v>10</v>
@@ -3401,10 +3401,10 @@
         <v>10</v>
       </c>
       <c r="G32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -3449,7 +3449,7 @@
         <v>-1</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X32">
         <v>10</v>
@@ -3464,10 +3464,10 @@
         <v>10</v>
       </c>
       <c r="AB32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC32">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -3523,7 +3523,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>51</v>
@@ -3532,149 +3532,158 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>10.71</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
+      <c r="H2">
+        <v>8</v>
+      </c>
       <c r="I2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>89.29000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>52</v>
       </c>
       <c r="C3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>14.29</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
+      <c r="H3">
+        <v>6.8</v>
+      </c>
       <c r="I3">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J3">
-        <v>100</v>
+        <v>85.70999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>53</v>
       </c>
       <c r="C4">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>82.14</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
+      <c r="H4">
+        <v>8.800000000000001</v>
+      </c>
       <c r="I4">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="J4">
-        <v>100</v>
+        <v>17.86</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>54</v>
       </c>
       <c r="C5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>7.14</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="I5">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>92.86</v>
+        <v>17.24</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>55</v>
       </c>
       <c r="C6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D6">
+        <v>24</v>
+      </c>
+      <c r="E6">
         <v>4</v>
       </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
       <c r="F6">
-        <v>14.29</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>13.79</v>
       </c>
       <c r="H6">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I6">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>85.70999999999999</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>56</v>
@@ -3683,30 +3692,30 @@
         <v>29</v>
       </c>
       <c r="D7">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>82.76000000000001</v>
+        <v>89.66</v>
       </c>
       <c r="G7">
-        <v>13.79</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J7">
-        <v>3.45</v>
+        <v>10.34</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
         <v>57</v>
@@ -3715,13 +3724,13 @@
         <v>29</v>
       </c>
       <c r="D8">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>89.66</v>
+        <v>96.55</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -3730,10 +3739,10 @@
         <v>8.4</v>
       </c>
       <c r="I8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J8">
-        <v>10.34</v>
+        <v>3.45</v>
       </c>
     </row>
   </sheetData>
@@ -3743,7 +3752,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F141"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3787,7 +3796,7 @@
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3804,7 +3813,7 @@
         <v>108</v>
       </c>
       <c r="E3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
         <v>51</v>
@@ -3812,99 +3821,99 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920190</v>
+        <v>20330051920191</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920190</v>
+        <v>20330051920191</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920190</v>
+        <v>20330051920192</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920191</v>
+        <v>20330051920193</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920191</v>
+        <v>20330051920193</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
         <v>51</v>
@@ -3912,39 +3921,39 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920191</v>
+        <v>20330051920194</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920191</v>
+        <v>20330051920194</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D10" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
         <v>52</v>
@@ -3952,19 +3961,19 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920191</v>
+        <v>20330051920194</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D11" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
         <v>53</v>
@@ -3972,19 +3981,19 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920192</v>
+        <v>20330051920194</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D12" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
         <v>51</v>
@@ -3992,19 +4001,19 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920192</v>
+        <v>20330051920194</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D13" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
         <v>54</v>
@@ -4012,19 +4021,19 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>20330051920192</v>
+        <v>20330051920196</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D14" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
         <v>52</v>
@@ -4032,99 +4041,99 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>20330051920192</v>
+        <v>20330051920197</v>
       </c>
       <c r="B15" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D15" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E15" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>20330051920193</v>
+        <v>20330051920198</v>
       </c>
       <c r="B16" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C16" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="D16" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E16" t="s">
         <v>7</v>
       </c>
       <c r="F16" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>20330051920193</v>
+        <v>20330051920199</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C17" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="D17" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="E17" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>20330051920193</v>
+        <v>20330051920199</v>
       </c>
       <c r="B18" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C18" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="D18" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>20330051920193</v>
+        <v>20330051920200</v>
       </c>
       <c r="B19" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C19" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="D19" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E19" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F19" t="s">
         <v>52</v>
@@ -4132,159 +4141,159 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>20330051920193</v>
+        <v>20330051920200</v>
       </c>
       <c r="B20" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C20" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="D20" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E20" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>20330051920194</v>
+        <v>20330051920201</v>
       </c>
       <c r="B21" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C21" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="D21" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="E21" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F21" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>20330051920194</v>
+        <v>20330051920201</v>
       </c>
       <c r="B22" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C22" t="s">
-        <v>90</v>
+        <v>72</v>
       </c>
       <c r="D22" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="E22" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>20330051920194</v>
+        <v>19330051920280</v>
       </c>
       <c r="B23" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C23" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D23" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="E23" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F23" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>20330051920194</v>
+        <v>19330051920280</v>
       </c>
       <c r="B24" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C24" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D24" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>20330051920194</v>
+        <v>19330051920420</v>
       </c>
       <c r="B25" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C25" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="D25" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="E25" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F25" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>20330051920194</v>
+        <v>19330051920420</v>
       </c>
       <c r="B26" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C26" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="D26" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="E26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F26" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>20330051920196</v>
+        <v>19330051920420</v>
       </c>
       <c r="B27" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C27" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D27" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="E27" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F27" t="s">
         <v>55</v>
@@ -4292,199 +4301,199 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>20330051920196</v>
+        <v>19330051920420</v>
       </c>
       <c r="B28" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C28" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D28" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="E28" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F28" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>20330051920196</v>
+        <v>20330051920202</v>
       </c>
       <c r="B29" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C29" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D29" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="E29" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F29" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>20330051920196</v>
+        <v>20330051920202</v>
       </c>
       <c r="B30" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C30" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D30" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="E30" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>20330051920196</v>
+        <v>20330051920202</v>
       </c>
       <c r="B31" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C31" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D31" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="E31" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F31" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>20330051920197</v>
+        <v>20330051920204</v>
       </c>
       <c r="B32" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C32" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D32" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="E32" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F32" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>20330051920197</v>
+        <v>20330051920204</v>
       </c>
       <c r="B33" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C33" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D33" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="E33" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F33" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>20330051920197</v>
+        <v>20330051920204</v>
       </c>
       <c r="B34" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C34" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D34" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="E34" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F34" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>20330051920197</v>
+        <v>20330051920204</v>
       </c>
       <c r="B35" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="C35" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D35" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="E35" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F35" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>20330051920198</v>
+        <v>20330051920206</v>
       </c>
       <c r="B36" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C36" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="D36" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="E36" t="s">
         <v>7</v>
       </c>
       <c r="F36" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>20330051920198</v>
+        <v>20330051920206</v>
       </c>
       <c r="B37" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C37" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="D37" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="E37" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F37" t="s">
         <v>51</v>
@@ -4492,19 +4501,19 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>20330051920198</v>
+        <v>20330051920207</v>
       </c>
       <c r="B38" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C38" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D38" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="E38" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F38" t="s">
         <v>52</v>
@@ -4512,19 +4521,19 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>20330051920198</v>
+        <v>20330051920207</v>
       </c>
       <c r="B39" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C39" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="D39" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="E39" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F39" t="s">
         <v>53</v>
@@ -4532,179 +4541,179 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <v>20330051920199</v>
+        <v>20330051920207</v>
       </c>
       <c r="B40" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C40" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D40" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="E40" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F40" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>20330051920199</v>
+        <v>20330051920207</v>
       </c>
       <c r="B41" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C41" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D41" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="E41" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F41" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>20330051920199</v>
+        <v>20330051920208</v>
       </c>
       <c r="B42" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="C42" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D42" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="E42" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F42" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43">
-        <v>20330051920199</v>
+        <v>20330051920208</v>
       </c>
       <c r="B43" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="C43" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="D43" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="E43" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44">
-        <v>20330051920199</v>
+        <v>19330051920290</v>
       </c>
       <c r="B44" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C44" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="D44" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="E44" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F44" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45">
-        <v>20330051920200</v>
+        <v>19330051920290</v>
       </c>
       <c r="B45" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="C45" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="D45" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="E45" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F45" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46">
-        <v>20330051920200</v>
+        <v>20330051920209</v>
       </c>
       <c r="B46" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C46" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="D46" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="E46" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F46" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47">
-        <v>20330051920200</v>
+        <v>20330051920209</v>
       </c>
       <c r="B47" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C47" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="D47" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
       </c>
       <c r="F47" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48">
-        <v>20330051920200</v>
+        <v>20330051920210</v>
       </c>
       <c r="B48" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C48" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D48" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="E48" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F48" t="s">
         <v>52</v>
@@ -4712,59 +4721,59 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49">
-        <v>20330051920200</v>
+        <v>20330051920210</v>
       </c>
       <c r="B49" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="C49" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D49" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="E49" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F49" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50">
-        <v>20330051920201</v>
+        <v>20330051920212</v>
       </c>
       <c r="B50" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="C50" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="D50" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="E50" t="s">
         <v>7</v>
       </c>
       <c r="F50" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51">
-        <v>20330051920201</v>
+        <v>20330051920212</v>
       </c>
       <c r="B51" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="C51" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
       <c r="D51" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="E51" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F51" t="s">
         <v>51</v>
@@ -4772,239 +4781,239 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52">
-        <v>20330051920201</v>
+        <v>20330051920213</v>
       </c>
       <c r="B52" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="C52" t="s">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="D52" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="E52" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F52" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53">
-        <v>20330051920201</v>
+        <v>20330051920213</v>
       </c>
       <c r="B53" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="C53" t="s">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="D53" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="E53" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F53" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54">
-        <v>20330051920201</v>
+        <v>20330051920214</v>
       </c>
       <c r="B54" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="C54" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="D54" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="E54" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F54" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55">
-        <v>19330051920280</v>
+        <v>20330051920214</v>
       </c>
       <c r="B55" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C55" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D55" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="E55" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F55" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56">
-        <v>19330051920280</v>
+        <v>20330051920214</v>
       </c>
       <c r="B56" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C56" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="D56" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="E56" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F56" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57">
-        <v>19330051920280</v>
+        <v>20330051920215</v>
       </c>
       <c r="B57" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C57" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="D57" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="E57" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F57" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58">
-        <v>19330051920280</v>
+        <v>19330051920177</v>
       </c>
       <c r="B58" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C58" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D58" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="E58" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F58" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59">
-        <v>19330051920280</v>
+        <v>19330051920177</v>
       </c>
       <c r="B59" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="C59" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D59" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="E59" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F59" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60">
-        <v>19330051920420</v>
+        <v>20330051920217</v>
       </c>
       <c r="B60" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="C60" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="D60" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="E60" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F60" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61">
-        <v>19330051920420</v>
+        <v>20330051920217</v>
       </c>
       <c r="B61" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="C61" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="D61" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="E61" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F61" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="62" spans="1:6">
       <c r="A62">
-        <v>19330051920420</v>
+        <v>20330051920218</v>
       </c>
       <c r="B62" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="C62" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="D62" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="E62" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F62" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63">
-        <v>19330051920420</v>
+        <v>20330051920218</v>
       </c>
       <c r="B63" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="C63" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="D63" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="E63" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F63" t="s">
         <v>53</v>
@@ -5012,1562 +5021,42 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64">
-        <v>20330051920202</v>
+        <v>20330051920218</v>
       </c>
       <c r="B64" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="C64" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="D64" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="E64" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F64" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65">
-        <v>20330051920202</v>
+        <v>20330051920219</v>
       </c>
       <c r="B65" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="C65" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="D65" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="E65" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F65" t="s">
         <v>51</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>20330051920202</v>
-      </c>
-      <c r="B66" t="s">
-        <v>74</v>
-      </c>
-      <c r="C66" t="s">
-        <v>87</v>
-      </c>
-      <c r="D66" t="s">
-        <v>121</v>
-      </c>
-      <c r="E66" t="s">
-        <v>8</v>
-      </c>
-      <c r="F66" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>20330051920202</v>
-      </c>
-      <c r="B67" t="s">
-        <v>74</v>
-      </c>
-      <c r="C67" t="s">
-        <v>87</v>
-      </c>
-      <c r="D67" t="s">
-        <v>121</v>
-      </c>
-      <c r="E67" t="s">
-        <v>10</v>
-      </c>
-      <c r="F67" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>20330051920202</v>
-      </c>
-      <c r="B68" t="s">
-        <v>74</v>
-      </c>
-      <c r="C68" t="s">
-        <v>87</v>
-      </c>
-      <c r="D68" t="s">
-        <v>121</v>
-      </c>
-      <c r="E68" t="s">
-        <v>11</v>
-      </c>
-      <c r="F68" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>20330051920204</v>
-      </c>
-      <c r="B69" t="s">
-        <v>75</v>
-      </c>
-      <c r="C69" t="s">
-        <v>98</v>
-      </c>
-      <c r="D69" t="s">
-        <v>122</v>
-      </c>
-      <c r="E69" t="s">
-        <v>6</v>
-      </c>
-      <c r="F69" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>20330051920204</v>
-      </c>
-      <c r="B70" t="s">
-        <v>75</v>
-      </c>
-      <c r="C70" t="s">
-        <v>98</v>
-      </c>
-      <c r="D70" t="s">
-        <v>122</v>
-      </c>
-      <c r="E70" t="s">
-        <v>7</v>
-      </c>
-      <c r="F70" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>20330051920204</v>
-      </c>
-      <c r="B71" t="s">
-        <v>75</v>
-      </c>
-      <c r="C71" t="s">
-        <v>98</v>
-      </c>
-      <c r="D71" t="s">
-        <v>122</v>
-      </c>
-      <c r="E71" t="s">
-        <v>5</v>
-      </c>
-      <c r="F71" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>20330051920204</v>
-      </c>
-      <c r="B72" t="s">
-        <v>75</v>
-      </c>
-      <c r="C72" t="s">
-        <v>98</v>
-      </c>
-      <c r="D72" t="s">
-        <v>122</v>
-      </c>
-      <c r="E72" t="s">
-        <v>8</v>
-      </c>
-      <c r="F72" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>20330051920204</v>
-      </c>
-      <c r="B73" t="s">
-        <v>75</v>
-      </c>
-      <c r="C73" t="s">
-        <v>98</v>
-      </c>
-      <c r="D73" t="s">
-        <v>122</v>
-      </c>
-      <c r="E73" t="s">
-        <v>10</v>
-      </c>
-      <c r="F73" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>20330051920204</v>
-      </c>
-      <c r="B74" t="s">
-        <v>75</v>
-      </c>
-      <c r="C74" t="s">
-        <v>98</v>
-      </c>
-      <c r="D74" t="s">
-        <v>122</v>
-      </c>
-      <c r="E74" t="s">
-        <v>11</v>
-      </c>
-      <c r="F74" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>20330051920206</v>
-      </c>
-      <c r="B75" t="s">
-        <v>76</v>
-      </c>
-      <c r="C75" t="s">
-        <v>83</v>
-      </c>
-      <c r="D75" t="s">
-        <v>123</v>
-      </c>
-      <c r="E75" t="s">
-        <v>7</v>
-      </c>
-      <c r="F75" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="A76">
-        <v>20330051920206</v>
-      </c>
-      <c r="B76" t="s">
-        <v>76</v>
-      </c>
-      <c r="C76" t="s">
-        <v>83</v>
-      </c>
-      <c r="D76" t="s">
-        <v>123</v>
-      </c>
-      <c r="E76" t="s">
-        <v>5</v>
-      </c>
-      <c r="F76" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="A77">
-        <v>20330051920206</v>
-      </c>
-      <c r="B77" t="s">
-        <v>76</v>
-      </c>
-      <c r="C77" t="s">
-        <v>83</v>
-      </c>
-      <c r="D77" t="s">
-        <v>123</v>
-      </c>
-      <c r="E77" t="s">
-        <v>8</v>
-      </c>
-      <c r="F77" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6">
-      <c r="A78">
-        <v>20330051920206</v>
-      </c>
-      <c r="B78" t="s">
-        <v>76</v>
-      </c>
-      <c r="C78" t="s">
-        <v>83</v>
-      </c>
-      <c r="D78" t="s">
-        <v>123</v>
-      </c>
-      <c r="E78" t="s">
-        <v>10</v>
-      </c>
-      <c r="F78" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6">
-      <c r="A79">
-        <v>20330051920206</v>
-      </c>
-      <c r="B79" t="s">
-        <v>76</v>
-      </c>
-      <c r="C79" t="s">
-        <v>83</v>
-      </c>
-      <c r="D79" t="s">
-        <v>123</v>
-      </c>
-      <c r="E79" t="s">
-        <v>11</v>
-      </c>
-      <c r="F79" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80">
-        <v>20330051920207</v>
-      </c>
-      <c r="B80" t="s">
-        <v>77</v>
-      </c>
-      <c r="C80" t="s">
-        <v>99</v>
-      </c>
-      <c r="D80" t="s">
-        <v>124</v>
-      </c>
-      <c r="E80" t="s">
-        <v>7</v>
-      </c>
-      <c r="F80" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="A81">
-        <v>20330051920207</v>
-      </c>
-      <c r="B81" t="s">
-        <v>77</v>
-      </c>
-      <c r="C81" t="s">
-        <v>99</v>
-      </c>
-      <c r="D81" t="s">
-        <v>124</v>
-      </c>
-      <c r="E81" t="s">
-        <v>5</v>
-      </c>
-      <c r="F81" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="A82">
-        <v>20330051920207</v>
-      </c>
-      <c r="B82" t="s">
-        <v>77</v>
-      </c>
-      <c r="C82" t="s">
-        <v>99</v>
-      </c>
-      <c r="D82" t="s">
-        <v>124</v>
-      </c>
-      <c r="E82" t="s">
-        <v>8</v>
-      </c>
-      <c r="F82" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6">
-      <c r="A83">
-        <v>20330051920207</v>
-      </c>
-      <c r="B83" t="s">
-        <v>77</v>
-      </c>
-      <c r="C83" t="s">
-        <v>99</v>
-      </c>
-      <c r="D83" t="s">
-        <v>124</v>
-      </c>
-      <c r="E83" t="s">
-        <v>10</v>
-      </c>
-      <c r="F83" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6">
-      <c r="A84">
-        <v>20330051920207</v>
-      </c>
-      <c r="B84" t="s">
-        <v>77</v>
-      </c>
-      <c r="C84" t="s">
-        <v>99</v>
-      </c>
-      <c r="D84" t="s">
-        <v>124</v>
-      </c>
-      <c r="E84" t="s">
-        <v>11</v>
-      </c>
-      <c r="F84" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85">
-        <v>20330051920208</v>
-      </c>
-      <c r="B85" t="s">
-        <v>78</v>
-      </c>
-      <c r="C85" t="s">
-        <v>100</v>
-      </c>
-      <c r="D85" t="s">
-        <v>125</v>
-      </c>
-      <c r="E85" t="s">
-        <v>7</v>
-      </c>
-      <c r="F85" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="A86">
-        <v>20330051920208</v>
-      </c>
-      <c r="B86" t="s">
-        <v>78</v>
-      </c>
-      <c r="C86" t="s">
-        <v>100</v>
-      </c>
-      <c r="D86" t="s">
-        <v>125</v>
-      </c>
-      <c r="E86" t="s">
-        <v>5</v>
-      </c>
-      <c r="F86" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="A87">
-        <v>20330051920208</v>
-      </c>
-      <c r="B87" t="s">
-        <v>78</v>
-      </c>
-      <c r="C87" t="s">
-        <v>100</v>
-      </c>
-      <c r="D87" t="s">
-        <v>125</v>
-      </c>
-      <c r="E87" t="s">
-        <v>8</v>
-      </c>
-      <c r="F87" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6">
-      <c r="A88">
-        <v>20330051920208</v>
-      </c>
-      <c r="B88" t="s">
-        <v>78</v>
-      </c>
-      <c r="C88" t="s">
-        <v>100</v>
-      </c>
-      <c r="D88" t="s">
-        <v>125</v>
-      </c>
-      <c r="E88" t="s">
-        <v>10</v>
-      </c>
-      <c r="F88" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6">
-      <c r="A89">
-        <v>20330051920208</v>
-      </c>
-      <c r="B89" t="s">
-        <v>78</v>
-      </c>
-      <c r="C89" t="s">
-        <v>100</v>
-      </c>
-      <c r="D89" t="s">
-        <v>125</v>
-      </c>
-      <c r="E89" t="s">
-        <v>11</v>
-      </c>
-      <c r="F89" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6">
-      <c r="A90">
-        <v>19330051920290</v>
-      </c>
-      <c r="B90" t="s">
-        <v>79</v>
-      </c>
-      <c r="C90" t="s">
-        <v>101</v>
-      </c>
-      <c r="D90" t="s">
-        <v>126</v>
-      </c>
-      <c r="E90" t="s">
-        <v>7</v>
-      </c>
-      <c r="F90" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="A91">
-        <v>19330051920290</v>
-      </c>
-      <c r="B91" t="s">
-        <v>79</v>
-      </c>
-      <c r="C91" t="s">
-        <v>101</v>
-      </c>
-      <c r="D91" t="s">
-        <v>126</v>
-      </c>
-      <c r="E91" t="s">
-        <v>5</v>
-      </c>
-      <c r="F91" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6">
-      <c r="A92">
-        <v>19330051920290</v>
-      </c>
-      <c r="B92" t="s">
-        <v>79</v>
-      </c>
-      <c r="C92" t="s">
-        <v>101</v>
-      </c>
-      <c r="D92" t="s">
-        <v>126</v>
-      </c>
-      <c r="E92" t="s">
-        <v>8</v>
-      </c>
-      <c r="F92" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6">
-      <c r="A93">
-        <v>19330051920290</v>
-      </c>
-      <c r="B93" t="s">
-        <v>79</v>
-      </c>
-      <c r="C93" t="s">
-        <v>101</v>
-      </c>
-      <c r="D93" t="s">
-        <v>126</v>
-      </c>
-      <c r="E93" t="s">
-        <v>10</v>
-      </c>
-      <c r="F93" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6">
-      <c r="A94">
-        <v>19330051920290</v>
-      </c>
-      <c r="B94" t="s">
-        <v>79</v>
-      </c>
-      <c r="C94" t="s">
-        <v>101</v>
-      </c>
-      <c r="D94" t="s">
-        <v>126</v>
-      </c>
-      <c r="E94" t="s">
-        <v>11</v>
-      </c>
-      <c r="F94" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6">
-      <c r="A95">
-        <v>20330051920209</v>
-      </c>
-      <c r="B95" t="s">
-        <v>80</v>
-      </c>
-      <c r="C95" t="s">
-        <v>102</v>
-      </c>
-      <c r="D95" t="s">
-        <v>127</v>
-      </c>
-      <c r="E95" t="s">
-        <v>7</v>
-      </c>
-      <c r="F95" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6">
-      <c r="A96">
-        <v>20330051920209</v>
-      </c>
-      <c r="B96" t="s">
-        <v>80</v>
-      </c>
-      <c r="C96" t="s">
-        <v>102</v>
-      </c>
-      <c r="D96" t="s">
-        <v>127</v>
-      </c>
-      <c r="E96" t="s">
-        <v>5</v>
-      </c>
-      <c r="F96" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="A97">
-        <v>20330051920209</v>
-      </c>
-      <c r="B97" t="s">
-        <v>80</v>
-      </c>
-      <c r="C97" t="s">
-        <v>102</v>
-      </c>
-      <c r="D97" t="s">
-        <v>127</v>
-      </c>
-      <c r="E97" t="s">
-        <v>8</v>
-      </c>
-      <c r="F97" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="A98">
-        <v>20330051920209</v>
-      </c>
-      <c r="B98" t="s">
-        <v>80</v>
-      </c>
-      <c r="C98" t="s">
-        <v>102</v>
-      </c>
-      <c r="D98" t="s">
-        <v>127</v>
-      </c>
-      <c r="E98" t="s">
-        <v>10</v>
-      </c>
-      <c r="F98" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="A99">
-        <v>20330051920209</v>
-      </c>
-      <c r="B99" t="s">
-        <v>80</v>
-      </c>
-      <c r="C99" t="s">
-        <v>102</v>
-      </c>
-      <c r="D99" t="s">
-        <v>127</v>
-      </c>
-      <c r="E99" t="s">
-        <v>11</v>
-      </c>
-      <c r="F99" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
-      <c r="A100">
-        <v>20330051920210</v>
-      </c>
-      <c r="B100" t="s">
-        <v>81</v>
-      </c>
-      <c r="C100" t="s">
-        <v>87</v>
-      </c>
-      <c r="D100" t="s">
-        <v>128</v>
-      </c>
-      <c r="E100" t="s">
-        <v>7</v>
-      </c>
-      <c r="F100" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6">
-      <c r="A101">
-        <v>20330051920210</v>
-      </c>
-      <c r="B101" t="s">
-        <v>81</v>
-      </c>
-      <c r="C101" t="s">
-        <v>87</v>
-      </c>
-      <c r="D101" t="s">
-        <v>128</v>
-      </c>
-      <c r="E101" t="s">
-        <v>5</v>
-      </c>
-      <c r="F101" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
-      <c r="A102">
-        <v>20330051920210</v>
-      </c>
-      <c r="B102" t="s">
-        <v>81</v>
-      </c>
-      <c r="C102" t="s">
-        <v>87</v>
-      </c>
-      <c r="D102" t="s">
-        <v>128</v>
-      </c>
-      <c r="E102" t="s">
-        <v>8</v>
-      </c>
-      <c r="F102" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
-      <c r="A103">
-        <v>20330051920210</v>
-      </c>
-      <c r="B103" t="s">
-        <v>81</v>
-      </c>
-      <c r="C103" t="s">
-        <v>87</v>
-      </c>
-      <c r="D103" t="s">
-        <v>128</v>
-      </c>
-      <c r="E103" t="s">
-        <v>10</v>
-      </c>
-      <c r="F103" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6">
-      <c r="A104">
-        <v>20330051920210</v>
-      </c>
-      <c r="B104" t="s">
-        <v>81</v>
-      </c>
-      <c r="C104" t="s">
-        <v>87</v>
-      </c>
-      <c r="D104" t="s">
-        <v>128</v>
-      </c>
-      <c r="E104" t="s">
-        <v>11</v>
-      </c>
-      <c r="F104" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6">
-      <c r="A105">
-        <v>20330051920212</v>
-      </c>
-      <c r="B105" t="s">
-        <v>82</v>
-      </c>
-      <c r="C105" t="s">
-        <v>103</v>
-      </c>
-      <c r="D105" t="s">
-        <v>129</v>
-      </c>
-      <c r="E105" t="s">
-        <v>7</v>
-      </c>
-      <c r="F105" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6">
-      <c r="A106">
-        <v>20330051920212</v>
-      </c>
-      <c r="B106" t="s">
-        <v>82</v>
-      </c>
-      <c r="C106" t="s">
-        <v>103</v>
-      </c>
-      <c r="D106" t="s">
-        <v>129</v>
-      </c>
-      <c r="E106" t="s">
-        <v>5</v>
-      </c>
-      <c r="F106" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6">
-      <c r="A107">
-        <v>20330051920212</v>
-      </c>
-      <c r="B107" t="s">
-        <v>82</v>
-      </c>
-      <c r="C107" t="s">
-        <v>103</v>
-      </c>
-      <c r="D107" t="s">
-        <v>129</v>
-      </c>
-      <c r="E107" t="s">
-        <v>8</v>
-      </c>
-      <c r="F107" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6">
-      <c r="A108">
-        <v>20330051920212</v>
-      </c>
-      <c r="B108" t="s">
-        <v>82</v>
-      </c>
-      <c r="C108" t="s">
-        <v>103</v>
-      </c>
-      <c r="D108" t="s">
-        <v>129</v>
-      </c>
-      <c r="E108" t="s">
-        <v>10</v>
-      </c>
-      <c r="F108" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6">
-      <c r="A109">
-        <v>20330051920212</v>
-      </c>
-      <c r="B109" t="s">
-        <v>82</v>
-      </c>
-      <c r="C109" t="s">
-        <v>103</v>
-      </c>
-      <c r="D109" t="s">
-        <v>129</v>
-      </c>
-      <c r="E109" t="s">
-        <v>11</v>
-      </c>
-      <c r="F109" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6">
-      <c r="A110">
-        <v>20330051920213</v>
-      </c>
-      <c r="B110" t="s">
-        <v>83</v>
-      </c>
-      <c r="C110" t="s">
-        <v>104</v>
-      </c>
-      <c r="D110" t="s">
-        <v>130</v>
-      </c>
-      <c r="E110" t="s">
-        <v>7</v>
-      </c>
-      <c r="F110" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6">
-      <c r="A111">
-        <v>20330051920213</v>
-      </c>
-      <c r="B111" t="s">
-        <v>83</v>
-      </c>
-      <c r="C111" t="s">
-        <v>104</v>
-      </c>
-      <c r="D111" t="s">
-        <v>130</v>
-      </c>
-      <c r="E111" t="s">
-        <v>5</v>
-      </c>
-      <c r="F111" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6">
-      <c r="A112">
-        <v>20330051920213</v>
-      </c>
-      <c r="B112" t="s">
-        <v>83</v>
-      </c>
-      <c r="C112" t="s">
-        <v>104</v>
-      </c>
-      <c r="D112" t="s">
-        <v>130</v>
-      </c>
-      <c r="E112" t="s">
-        <v>8</v>
-      </c>
-      <c r="F112" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6">
-      <c r="A113">
-        <v>20330051920213</v>
-      </c>
-      <c r="B113" t="s">
-        <v>83</v>
-      </c>
-      <c r="C113" t="s">
-        <v>104</v>
-      </c>
-      <c r="D113" t="s">
-        <v>130</v>
-      </c>
-      <c r="E113" t="s">
-        <v>10</v>
-      </c>
-      <c r="F113" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6">
-      <c r="A114">
-        <v>20330051920213</v>
-      </c>
-      <c r="B114" t="s">
-        <v>83</v>
-      </c>
-      <c r="C114" t="s">
-        <v>104</v>
-      </c>
-      <c r="D114" t="s">
-        <v>130</v>
-      </c>
-      <c r="E114" t="s">
-        <v>11</v>
-      </c>
-      <c r="F114" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6">
-      <c r="A115">
-        <v>20330051920214</v>
-      </c>
-      <c r="B115" t="s">
-        <v>84</v>
-      </c>
-      <c r="C115" t="s">
-        <v>105</v>
-      </c>
-      <c r="D115" t="s">
-        <v>131</v>
-      </c>
-      <c r="E115" t="s">
-        <v>7</v>
-      </c>
-      <c r="F115" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6">
-      <c r="A116">
-        <v>20330051920214</v>
-      </c>
-      <c r="B116" t="s">
-        <v>84</v>
-      </c>
-      <c r="C116" t="s">
-        <v>105</v>
-      </c>
-      <c r="D116" t="s">
-        <v>131</v>
-      </c>
-      <c r="E116" t="s">
-        <v>5</v>
-      </c>
-      <c r="F116" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6">
-      <c r="A117">
-        <v>20330051920214</v>
-      </c>
-      <c r="B117" t="s">
-        <v>84</v>
-      </c>
-      <c r="C117" t="s">
-        <v>105</v>
-      </c>
-      <c r="D117" t="s">
-        <v>131</v>
-      </c>
-      <c r="E117" t="s">
-        <v>8</v>
-      </c>
-      <c r="F117" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6">
-      <c r="A118">
-        <v>20330051920214</v>
-      </c>
-      <c r="B118" t="s">
-        <v>84</v>
-      </c>
-      <c r="C118" t="s">
-        <v>105</v>
-      </c>
-      <c r="D118" t="s">
-        <v>131</v>
-      </c>
-      <c r="E118" t="s">
-        <v>10</v>
-      </c>
-      <c r="F118" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6">
-      <c r="A119">
-        <v>20330051920214</v>
-      </c>
-      <c r="B119" t="s">
-        <v>84</v>
-      </c>
-      <c r="C119" t="s">
-        <v>105</v>
-      </c>
-      <c r="D119" t="s">
-        <v>131</v>
-      </c>
-      <c r="E119" t="s">
-        <v>11</v>
-      </c>
-      <c r="F119" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6">
-      <c r="A120">
-        <v>20330051920215</v>
-      </c>
-      <c r="B120" t="s">
-        <v>84</v>
-      </c>
-      <c r="C120" t="s">
-        <v>73</v>
-      </c>
-      <c r="D120" t="s">
-        <v>132</v>
-      </c>
-      <c r="E120" t="s">
-        <v>7</v>
-      </c>
-      <c r="F120" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6">
-      <c r="A121">
-        <v>20330051920215</v>
-      </c>
-      <c r="B121" t="s">
-        <v>84</v>
-      </c>
-      <c r="C121" t="s">
-        <v>73</v>
-      </c>
-      <c r="D121" t="s">
-        <v>132</v>
-      </c>
-      <c r="E121" t="s">
-        <v>5</v>
-      </c>
-      <c r="F121" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6">
-      <c r="A122">
-        <v>20330051920215</v>
-      </c>
-      <c r="B122" t="s">
-        <v>84</v>
-      </c>
-      <c r="C122" t="s">
-        <v>73</v>
-      </c>
-      <c r="D122" t="s">
-        <v>132</v>
-      </c>
-      <c r="E122" t="s">
-        <v>10</v>
-      </c>
-      <c r="F122" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6">
-      <c r="A123">
-        <v>20330051920215</v>
-      </c>
-      <c r="B123" t="s">
-        <v>84</v>
-      </c>
-      <c r="C123" t="s">
-        <v>73</v>
-      </c>
-      <c r="D123" t="s">
-        <v>132</v>
-      </c>
-      <c r="E123" t="s">
-        <v>11</v>
-      </c>
-      <c r="F123" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6">
-      <c r="A124">
-        <v>19330051920177</v>
-      </c>
-      <c r="B124" t="s">
-        <v>84</v>
-      </c>
-      <c r="C124" t="s">
-        <v>100</v>
-      </c>
-      <c r="D124" t="s">
-        <v>133</v>
-      </c>
-      <c r="E124" t="s">
-        <v>5</v>
-      </c>
-      <c r="F124" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6">
-      <c r="A125">
-        <v>19330051920177</v>
-      </c>
-      <c r="B125" t="s">
-        <v>84</v>
-      </c>
-      <c r="C125" t="s">
-        <v>100</v>
-      </c>
-      <c r="D125" t="s">
-        <v>133</v>
-      </c>
-      <c r="E125" t="s">
-        <v>8</v>
-      </c>
-      <c r="F125" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6">
-      <c r="A126">
-        <v>19330051920177</v>
-      </c>
-      <c r="B126" t="s">
-        <v>84</v>
-      </c>
-      <c r="C126" t="s">
-        <v>100</v>
-      </c>
-      <c r="D126" t="s">
-        <v>133</v>
-      </c>
-      <c r="E126" t="s">
-        <v>10</v>
-      </c>
-      <c r="F126" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6">
-      <c r="A127">
-        <v>19330051920177</v>
-      </c>
-      <c r="B127" t="s">
-        <v>84</v>
-      </c>
-      <c r="C127" t="s">
-        <v>100</v>
-      </c>
-      <c r="D127" t="s">
-        <v>133</v>
-      </c>
-      <c r="E127" t="s">
-        <v>11</v>
-      </c>
-      <c r="F127" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6">
-      <c r="A128">
-        <v>20330051920217</v>
-      </c>
-      <c r="B128" t="s">
-        <v>84</v>
-      </c>
-      <c r="C128" t="s">
-        <v>106</v>
-      </c>
-      <c r="D128" t="s">
-        <v>134</v>
-      </c>
-      <c r="E128" t="s">
-        <v>7</v>
-      </c>
-      <c r="F128" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6">
-      <c r="A129">
-        <v>20330051920217</v>
-      </c>
-      <c r="B129" t="s">
-        <v>84</v>
-      </c>
-      <c r="C129" t="s">
-        <v>106</v>
-      </c>
-      <c r="D129" t="s">
-        <v>134</v>
-      </c>
-      <c r="E129" t="s">
-        <v>5</v>
-      </c>
-      <c r="F129" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6">
-      <c r="A130">
-        <v>20330051920217</v>
-      </c>
-      <c r="B130" t="s">
-        <v>84</v>
-      </c>
-      <c r="C130" t="s">
-        <v>106</v>
-      </c>
-      <c r="D130" t="s">
-        <v>134</v>
-      </c>
-      <c r="E130" t="s">
-        <v>8</v>
-      </c>
-      <c r="F130" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6">
-      <c r="A131">
-        <v>20330051920217</v>
-      </c>
-      <c r="B131" t="s">
-        <v>84</v>
-      </c>
-      <c r="C131" t="s">
-        <v>106</v>
-      </c>
-      <c r="D131" t="s">
-        <v>134</v>
-      </c>
-      <c r="E131" t="s">
-        <v>10</v>
-      </c>
-      <c r="F131" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6">
-      <c r="A132">
-        <v>20330051920217</v>
-      </c>
-      <c r="B132" t="s">
-        <v>84</v>
-      </c>
-      <c r="C132" t="s">
-        <v>106</v>
-      </c>
-      <c r="D132" t="s">
-        <v>134</v>
-      </c>
-      <c r="E132" t="s">
-        <v>11</v>
-      </c>
-      <c r="F132" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6">
-      <c r="A133">
-        <v>20330051920218</v>
-      </c>
-      <c r="B133" t="s">
-        <v>85</v>
-      </c>
-      <c r="C133" t="s">
-        <v>103</v>
-      </c>
-      <c r="D133" t="s">
-        <v>135</v>
-      </c>
-      <c r="E133" t="s">
-        <v>7</v>
-      </c>
-      <c r="F133" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6">
-      <c r="A134">
-        <v>20330051920218</v>
-      </c>
-      <c r="B134" t="s">
-        <v>85</v>
-      </c>
-      <c r="C134" t="s">
-        <v>103</v>
-      </c>
-      <c r="D134" t="s">
-        <v>135</v>
-      </c>
-      <c r="E134" t="s">
-        <v>5</v>
-      </c>
-      <c r="F134" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6">
-      <c r="A135">
-        <v>20330051920218</v>
-      </c>
-      <c r="B135" t="s">
-        <v>85</v>
-      </c>
-      <c r="C135" t="s">
-        <v>103</v>
-      </c>
-      <c r="D135" t="s">
-        <v>135</v>
-      </c>
-      <c r="E135" t="s">
-        <v>8</v>
-      </c>
-      <c r="F135" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6">
-      <c r="A136">
-        <v>20330051920218</v>
-      </c>
-      <c r="B136" t="s">
-        <v>85</v>
-      </c>
-      <c r="C136" t="s">
-        <v>103</v>
-      </c>
-      <c r="D136" t="s">
-        <v>135</v>
-      </c>
-      <c r="E136" t="s">
-        <v>10</v>
-      </c>
-      <c r="F136" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6">
-      <c r="A137">
-        <v>20330051920218</v>
-      </c>
-      <c r="B137" t="s">
-        <v>85</v>
-      </c>
-      <c r="C137" t="s">
-        <v>103</v>
-      </c>
-      <c r="D137" t="s">
-        <v>135</v>
-      </c>
-      <c r="E137" t="s">
-        <v>11</v>
-      </c>
-      <c r="F137" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6">
-      <c r="A138">
-        <v>20330051920219</v>
-      </c>
-      <c r="B138" t="s">
-        <v>86</v>
-      </c>
-      <c r="C138" t="s">
-        <v>107</v>
-      </c>
-      <c r="D138" t="s">
-        <v>136</v>
-      </c>
-      <c r="E138" t="s">
-        <v>5</v>
-      </c>
-      <c r="F138" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6">
-      <c r="A139">
-        <v>20330051920219</v>
-      </c>
-      <c r="B139" t="s">
-        <v>86</v>
-      </c>
-      <c r="C139" t="s">
-        <v>107</v>
-      </c>
-      <c r="D139" t="s">
-        <v>136</v>
-      </c>
-      <c r="E139" t="s">
-        <v>8</v>
-      </c>
-      <c r="F139" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6">
-      <c r="A140">
-        <v>20330051920219</v>
-      </c>
-      <c r="B140" t="s">
-        <v>86</v>
-      </c>
-      <c r="C140" t="s">
-        <v>107</v>
-      </c>
-      <c r="D140" t="s">
-        <v>136</v>
-      </c>
-      <c r="E140" t="s">
-        <v>10</v>
-      </c>
-      <c r="F140" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6">
-      <c r="A141">
-        <v>20330051920219</v>
-      </c>
-      <c r="B141" t="s">
-        <v>86</v>
-      </c>
-      <c r="C141" t="s">
-        <v>107</v>
-      </c>
-      <c r="D141" t="s">
-        <v>136</v>
-      </c>
-      <c r="E141" t="s">
-        <v>11</v>
-      </c>
-      <c r="F141" t="s">
-        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -6615,466 +5104,466 @@
         <v>112</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920204</v>
+        <v>19330051920420</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920190</v>
+        <v>20330051920204</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="D4" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920191</v>
+        <v>20330051920207</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920193</v>
+        <v>20330051920202</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920196</v>
+        <v>20330051920214</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="D7" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920199</v>
+        <v>20330051920218</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="D8" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920200</v>
+        <v>20330051920190</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="E9">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920201</v>
+        <v>20330051920191</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920280</v>
+        <v>20330051920193</v>
       </c>
       <c r="B11" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="D11" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="E11">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920202</v>
+        <v>20330051920199</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D12" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E12">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920206</v>
+        <v>20330051920200</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C13" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="D13" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E13">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920207</v>
+        <v>20330051920201</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C14" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="D14" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E14">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920208</v>
+        <v>19330051920280</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C15" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D15" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="E15">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920290</v>
+        <v>20330051920206</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="D16" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E16">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920209</v>
+        <v>20330051920208</v>
       </c>
       <c r="B17" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C17" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D17" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E17">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920210</v>
+        <v>19330051920290</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C18" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="D18" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E18">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920212</v>
+        <v>20330051920209</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C19" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D19" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E19">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920213</v>
+        <v>20330051920210</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C20" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="D20" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E20">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920214</v>
+        <v>20330051920212</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C21" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D21" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E21">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920217</v>
+        <v>20330051920213</v>
       </c>
       <c r="B22" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C22" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D22" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E22">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920218</v>
+        <v>19330051920177</v>
       </c>
       <c r="B23" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C23" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D23" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E23">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920192</v>
+        <v>20330051920217</v>
       </c>
       <c r="B24" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="D24" t="s">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="E24">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920197</v>
+        <v>20330051920192</v>
       </c>
       <c r="B25" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C25" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D25" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E25">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920198</v>
+        <v>20330051920196</v>
       </c>
       <c r="B26" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C26" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D26" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E26">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920420</v>
+        <v>20330051920197</v>
       </c>
       <c r="B27" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C27" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="D27" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="E27">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920215</v>
+        <v>20330051920198</v>
       </c>
       <c r="B28" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="D28" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="E28">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920177</v>
+        <v>20330051920215</v>
       </c>
       <c r="B29" t="s">
         <v>84</v>
       </c>
       <c r="C29" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="D29" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E29">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -7091,7 +5580,7 @@
         <v>136</v>
       </c>
       <c r="E30">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -7101,7 +5590,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7131,6 +5620,880 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>20330051920190</v>
+      </c>
+      <c r="B2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>20330051920190</v>
+      </c>
+      <c r="B3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" t="s">
+        <v>108</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>20330051920191</v>
+      </c>
+      <c r="B4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>20330051920191</v>
+      </c>
+      <c r="B5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5" t="s">
+        <v>109</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>51</v>
+      </c>
+      <c r="G5">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>20330051920193</v>
+      </c>
+      <c r="B6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" t="s">
+        <v>52</v>
+      </c>
+      <c r="G6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>20330051920193</v>
+      </c>
+      <c r="B7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" t="s">
+        <v>111</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>20330051920199</v>
+      </c>
+      <c r="B8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D8" t="s">
+        <v>116</v>
+      </c>
+      <c r="E8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>20330051920199</v>
+      </c>
+      <c r="B9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" t="s">
+        <v>94</v>
+      </c>
+      <c r="D9" t="s">
+        <v>116</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>20330051920200</v>
+      </c>
+      <c r="B10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" t="s">
+        <v>95</v>
+      </c>
+      <c r="D10" t="s">
+        <v>117</v>
+      </c>
+      <c r="E10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>20330051920200</v>
+      </c>
+      <c r="B11" t="s">
+        <v>70</v>
+      </c>
+      <c r="C11" t="s">
+        <v>95</v>
+      </c>
+      <c r="D11" t="s">
+        <v>117</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>51</v>
+      </c>
+      <c r="G11">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>20330051920201</v>
+      </c>
+      <c r="B12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" t="s">
+        <v>72</v>
+      </c>
+      <c r="D12" t="s">
+        <v>118</v>
+      </c>
+      <c r="E12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" t="s">
+        <v>52</v>
+      </c>
+      <c r="G12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>20330051920201</v>
+      </c>
+      <c r="B13" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13" t="s">
+        <v>118</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>51</v>
+      </c>
+      <c r="G13">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>19330051920280</v>
+      </c>
+      <c r="B14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" t="s">
+        <v>96</v>
+      </c>
+      <c r="D14" t="s">
+        <v>119</v>
+      </c>
+      <c r="E14" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>19330051920280</v>
+      </c>
+      <c r="B15" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" t="s">
+        <v>96</v>
+      </c>
+      <c r="D15" t="s">
+        <v>119</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>51</v>
+      </c>
+      <c r="G15">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>20330051920206</v>
+      </c>
+      <c r="B16" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" t="s">
+        <v>123</v>
+      </c>
+      <c r="E16" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>20330051920206</v>
+      </c>
+      <c r="B17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" t="s">
+        <v>83</v>
+      </c>
+      <c r="D17" t="s">
+        <v>123</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
+        <v>51</v>
+      </c>
+      <c r="G17">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>20330051920208</v>
+      </c>
+      <c r="B18" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" t="s">
+        <v>100</v>
+      </c>
+      <c r="D18" t="s">
+        <v>125</v>
+      </c>
+      <c r="E18" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" t="s">
+        <v>52</v>
+      </c>
+      <c r="G18">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>20330051920208</v>
+      </c>
+      <c r="B19" t="s">
+        <v>78</v>
+      </c>
+      <c r="C19" t="s">
+        <v>100</v>
+      </c>
+      <c r="D19" t="s">
+        <v>125</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>51</v>
+      </c>
+      <c r="G19">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>19330051920290</v>
+      </c>
+      <c r="B20" t="s">
+        <v>79</v>
+      </c>
+      <c r="C20" t="s">
+        <v>101</v>
+      </c>
+      <c r="D20" t="s">
+        <v>126</v>
+      </c>
+      <c r="E20" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20" t="s">
+        <v>52</v>
+      </c>
+      <c r="G20">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>19330051920290</v>
+      </c>
+      <c r="B21" t="s">
+        <v>79</v>
+      </c>
+      <c r="C21" t="s">
+        <v>101</v>
+      </c>
+      <c r="D21" t="s">
+        <v>126</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>51</v>
+      </c>
+      <c r="G21">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>20330051920209</v>
+      </c>
+      <c r="B22" t="s">
+        <v>80</v>
+      </c>
+      <c r="C22" t="s">
+        <v>102</v>
+      </c>
+      <c r="D22" t="s">
+        <v>127</v>
+      </c>
+      <c r="E22" t="s">
+        <v>7</v>
+      </c>
+      <c r="F22" t="s">
+        <v>52</v>
+      </c>
+      <c r="G22">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>20330051920209</v>
+      </c>
+      <c r="B23" t="s">
+        <v>80</v>
+      </c>
+      <c r="C23" t="s">
+        <v>102</v>
+      </c>
+      <c r="D23" t="s">
+        <v>127</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>51</v>
+      </c>
+      <c r="G23">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>20330051920210</v>
+      </c>
+      <c r="B24" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" t="s">
+        <v>87</v>
+      </c>
+      <c r="D24" t="s">
+        <v>128</v>
+      </c>
+      <c r="E24" t="s">
+        <v>7</v>
+      </c>
+      <c r="F24" t="s">
+        <v>52</v>
+      </c>
+      <c r="G24">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>20330051920210</v>
+      </c>
+      <c r="B25" t="s">
+        <v>81</v>
+      </c>
+      <c r="C25" t="s">
+        <v>87</v>
+      </c>
+      <c r="D25" t="s">
+        <v>128</v>
+      </c>
+      <c r="E25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" t="s">
+        <v>51</v>
+      </c>
+      <c r="G25">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>20330051920212</v>
+      </c>
+      <c r="B26" t="s">
+        <v>82</v>
+      </c>
+      <c r="C26" t="s">
+        <v>103</v>
+      </c>
+      <c r="D26" t="s">
+        <v>129</v>
+      </c>
+      <c r="E26" t="s">
+        <v>7</v>
+      </c>
+      <c r="F26" t="s">
+        <v>52</v>
+      </c>
+      <c r="G26">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>20330051920212</v>
+      </c>
+      <c r="B27" t="s">
+        <v>82</v>
+      </c>
+      <c r="C27" t="s">
+        <v>103</v>
+      </c>
+      <c r="D27" t="s">
+        <v>129</v>
+      </c>
+      <c r="E27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" t="s">
+        <v>51</v>
+      </c>
+      <c r="G27">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>20330051920213</v>
+      </c>
+      <c r="B28" t="s">
+        <v>83</v>
+      </c>
+      <c r="C28" t="s">
+        <v>104</v>
+      </c>
+      <c r="D28" t="s">
+        <v>130</v>
+      </c>
+      <c r="E28" t="s">
+        <v>7</v>
+      </c>
+      <c r="F28" t="s">
+        <v>52</v>
+      </c>
+      <c r="G28">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>20330051920213</v>
+      </c>
+      <c r="B29" t="s">
+        <v>83</v>
+      </c>
+      <c r="C29" t="s">
+        <v>104</v>
+      </c>
+      <c r="D29" t="s">
+        <v>130</v>
+      </c>
+      <c r="E29" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" t="s">
+        <v>51</v>
+      </c>
+      <c r="G29">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>19330051920177</v>
+      </c>
+      <c r="B30" t="s">
+        <v>84</v>
+      </c>
+      <c r="C30" t="s">
+        <v>100</v>
+      </c>
+      <c r="D30" t="s">
+        <v>133</v>
+      </c>
+      <c r="E30" t="s">
+        <v>5</v>
+      </c>
+      <c r="F30" t="s">
+        <v>53</v>
+      </c>
+      <c r="G30">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>19330051920177</v>
+      </c>
+      <c r="B31" t="s">
+        <v>84</v>
+      </c>
+      <c r="C31" t="s">
+        <v>100</v>
+      </c>
+      <c r="D31" t="s">
+        <v>133</v>
+      </c>
+      <c r="E31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" t="s">
+        <v>51</v>
+      </c>
+      <c r="G31">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>20330051920217</v>
+      </c>
+      <c r="B32" t="s">
+        <v>84</v>
+      </c>
+      <c r="C32" t="s">
+        <v>106</v>
+      </c>
+      <c r="D32" t="s">
+        <v>134</v>
+      </c>
+      <c r="E32" t="s">
+        <v>7</v>
+      </c>
+      <c r="F32" t="s">
+        <v>52</v>
+      </c>
+      <c r="G32">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>20330051920217</v>
+      </c>
+      <c r="B33" t="s">
+        <v>84</v>
+      </c>
+      <c r="C33" t="s">
+        <v>106</v>
+      </c>
+      <c r="D33" t="s">
+        <v>134</v>
+      </c>
+      <c r="E33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" t="s">
+        <v>51</v>
+      </c>
+      <c r="G33">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>20330051920192</v>
+      </c>
+      <c r="B34" t="s">
+        <v>64</v>
+      </c>
+      <c r="C34" t="s">
+        <v>89</v>
+      </c>
+      <c r="D34" t="s">
+        <v>110</v>
+      </c>
+      <c r="E34" t="s">
+        <v>8</v>
+      </c>
+      <c r="F34" t="s">
+        <v>51</v>
+      </c>
+      <c r="G34">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
+        <v>20330051920196</v>
+      </c>
+      <c r="B35" t="s">
+        <v>67</v>
+      </c>
+      <c r="C35" t="s">
+        <v>91</v>
+      </c>
+      <c r="D35" t="s">
+        <v>113</v>
+      </c>
+      <c r="E35" t="s">
+        <v>7</v>
+      </c>
+      <c r="F35" t="s">
+        <v>52</v>
+      </c>
+      <c r="G35">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36">
+        <v>20330051920197</v>
+      </c>
+      <c r="B36" t="s">
+        <v>68</v>
+      </c>
+      <c r="C36" t="s">
+        <v>92</v>
+      </c>
+      <c r="D36" t="s">
+        <v>114</v>
+      </c>
+      <c r="E36" t="s">
+        <v>8</v>
+      </c>
+      <c r="F36" t="s">
+        <v>51</v>
+      </c>
+      <c r="G36">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37">
+        <v>20330051920198</v>
+      </c>
+      <c r="B37" t="s">
+        <v>69</v>
+      </c>
+      <c r="C37" t="s">
+        <v>93</v>
+      </c>
+      <c r="D37" t="s">
+        <v>115</v>
+      </c>
+      <c r="E37" t="s">
+        <v>7</v>
+      </c>
+      <c r="F37" t="s">
+        <v>52</v>
+      </c>
+      <c r="G37">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38">
+        <v>20330051920215</v>
+      </c>
+      <c r="B38" t="s">
+        <v>84</v>
+      </c>
+      <c r="C38" t="s">
+        <v>73</v>
+      </c>
+      <c r="D38" t="s">
+        <v>132</v>
+      </c>
+      <c r="E38" t="s">
+        <v>7</v>
+      </c>
+      <c r="F38" t="s">
+        <v>52</v>
+      </c>
+      <c r="G38">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39">
+        <v>20330051920219</v>
+      </c>
+      <c r="B39" t="s">
+        <v>86</v>
+      </c>
+      <c r="C39" t="s">
+        <v>107</v>
+      </c>
+      <c r="D39" t="s">
+        <v>136</v>
+      </c>
+      <c r="E39" t="s">
+        <v>8</v>
+      </c>
+      <c r="F39" t="s">
+        <v>51</v>
+      </c>
+      <c r="G39">
+        <v>-1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/4ALCV - Estadisticos 20212.xlsx
+++ b/grupos/4ALCV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="137">
   <si>
     <t>Materia</t>
   </si>
@@ -173,12 +173,12 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Polanco Domínguez Rosa María</t>
+  </si>
+  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
-    <t>Polanco Domínguez Rosa María</t>
-  </si>
-  <si>
     <t>Muñoz Rivadeneyra Salvador</t>
   </si>
   <si>
@@ -212,220 +212,220 @@
     <t>ARIAS</t>
   </si>
   <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>CHICO</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>ESPERON</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GALVEZ</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>MELENDEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>PEÑA</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>DE LA TEJA</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>ROQUE</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>SALGADO</t>
+  </si>
+  <si>
+    <t>OLIVERA</t>
+  </si>
+  <si>
+    <t>DAMIEN</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>MEJIA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>REYNA ARISBETH</t>
+  </si>
+  <si>
+    <t>ANALI</t>
+  </si>
+  <si>
+    <t>DULCE FERNANDA</t>
+  </si>
+  <si>
+    <t>KITZIA YAMILET</t>
+  </si>
+  <si>
+    <t>ERICK DE JESUS</t>
+  </si>
+  <si>
+    <t>MIA VALENTINA</t>
+  </si>
+  <si>
+    <t>AMARELY GUADALUPE</t>
+  </si>
+  <si>
+    <t>FRIDA SOFIA</t>
+  </si>
+  <si>
+    <t>ANTONIO ABIDAN</t>
+  </si>
+  <si>
+    <t>YAMILET</t>
+  </si>
+  <si>
+    <t>MILAGROS</t>
+  </si>
+  <si>
+    <t>ROBERTO JESUS</t>
+  </si>
+  <si>
+    <t>ITZEL</t>
+  </si>
+  <si>
+    <t>CRISTHIAN</t>
+  </si>
+  <si>
+    <t>MARITZA JULIANA</t>
+  </si>
+  <si>
+    <t>VICTOR MANUEL</t>
+  </si>
+  <si>
+    <t>LESLIE</t>
+  </si>
+  <si>
+    <t>HEIDY MARIAM</t>
+  </si>
+  <si>
+    <t>YEILI DAYNERIS</t>
+  </si>
+  <si>
+    <t>JULIO CESAR</t>
+  </si>
+  <si>
+    <t>INGRID SARAI</t>
+  </si>
+  <si>
+    <t>SUSANA</t>
+  </si>
+  <si>
+    <t>ALEJANDRA</t>
+  </si>
+  <si>
+    <t>AMADA ARELY</t>
+  </si>
+  <si>
+    <t>JOSSELIN ANDREA</t>
+  </si>
+  <si>
+    <t>LUIS DIEGO</t>
+  </si>
+  <si>
+    <t>ALISSON FERNANDA</t>
+  </si>
+  <si>
     <t>BALTAZARES</t>
   </si>
   <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CHICO</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>ESPERON</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GALVEZ</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>MELENDEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>PEÑA</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>DE LA TEJA</t>
-  </si>
-  <si>
     <t>VELAZQUEZ</t>
   </si>
   <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
     <t>CONTRERAS</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>ROQUE</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>SALGADO</t>
-  </si>
-  <si>
-    <t>OLIVERA</t>
-  </si>
-  <si>
-    <t>DAMIEN</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>MEJIA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
     <t>GALEOTE</t>
   </si>
   <si>
-    <t>REYNA ARISBETH</t>
-  </si>
-  <si>
-    <t>ANALI</t>
-  </si>
-  <si>
     <t>JOCELYN</t>
-  </si>
-  <si>
-    <t>DULCE FERNANDA</t>
-  </si>
-  <si>
-    <t>KITZIA YAMILET</t>
-  </si>
-  <si>
-    <t>ERICK DE JESUS</t>
-  </si>
-  <si>
-    <t>MIA VALENTINA</t>
-  </si>
-  <si>
-    <t>AMARELY GUADALUPE</t>
-  </si>
-  <si>
-    <t>FRIDA SOFIA</t>
-  </si>
-  <si>
-    <t>ANTONIO ABIDAN</t>
-  </si>
-  <si>
-    <t>YAMILET</t>
-  </si>
-  <si>
-    <t>MILAGROS</t>
-  </si>
-  <si>
-    <t>ROBERTO JESUS</t>
-  </si>
-  <si>
-    <t>ITZEL</t>
-  </si>
-  <si>
-    <t>CRISTHIAN</t>
-  </si>
-  <si>
-    <t>MARITZA JULIANA</t>
-  </si>
-  <si>
-    <t>VICTOR MANUEL</t>
-  </si>
-  <si>
-    <t>LESLIE</t>
-  </si>
-  <si>
-    <t>HEIDY MARIAM</t>
-  </si>
-  <si>
-    <t>YEILI DAYNERIS</t>
-  </si>
-  <si>
-    <t>JULIO CESAR</t>
-  </si>
-  <si>
-    <t>INGRID SARAI</t>
-  </si>
-  <si>
-    <t>SUSANA</t>
-  </si>
-  <si>
-    <t>ALEJANDRA</t>
-  </si>
-  <si>
-    <t>AMADA ARELY</t>
-  </si>
-  <si>
-    <t>JOSSELIN ANDREA</t>
-  </si>
-  <si>
-    <t>LUIS DIEGO</t>
-  </si>
-  <si>
-    <t>ALISSON FERNANDA</t>
   </si>
   <si>
     <t>EMILY</t>
@@ -939,7 +939,7 @@
         <v>-1</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F4">
         <v>6</v>
@@ -1002,7 +1002,7 @@
         <v>-1</v>
       </c>
       <c r="Z4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA4">
         <v>6</v>
@@ -1028,7 +1028,7 @@
         <v>-1</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F5">
         <v>9</v>
@@ -1091,7 +1091,7 @@
         <v>-1</v>
       </c>
       <c r="Z5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA5">
         <v>9</v>
@@ -1117,7 +1117,7 @@
         <v>6</v>
       </c>
       <c r="E6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F6">
         <v>9</v>
@@ -1180,7 +1180,7 @@
         <v>6</v>
       </c>
       <c r="Z6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA6">
         <v>9</v>
@@ -1206,7 +1206,7 @@
         <v>-1</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F7">
         <v>9</v>
@@ -1269,7 +1269,7 @@
         <v>-1</v>
       </c>
       <c r="Z7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA7">
         <v>9</v>
@@ -1295,7 +1295,7 @@
         <v>-1</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F8">
         <v>5</v>
@@ -1358,7 +1358,7 @@
         <v>-1</v>
       </c>
       <c r="Z8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA8">
         <v>5</v>
@@ -1384,7 +1384,7 @@
         <v>-1</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F9">
         <v>10</v>
@@ -1447,7 +1447,7 @@
         <v>-1</v>
       </c>
       <c r="Z9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA9">
         <v>10</v>
@@ -1473,7 +1473,7 @@
         <v>-1</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F10">
         <v>5</v>
@@ -1536,7 +1536,7 @@
         <v>-1</v>
       </c>
       <c r="Z10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA10">
         <v>5</v>
@@ -1562,7 +1562,7 @@
         <v>-1</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F11">
         <v>5</v>
@@ -1625,7 +1625,7 @@
         <v>-1</v>
       </c>
       <c r="Z11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA11">
         <v>5</v>
@@ -1918,7 +1918,7 @@
         <v>-1</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F15">
         <v>9</v>
@@ -1981,7 +1981,7 @@
         <v>-1</v>
       </c>
       <c r="Z15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA15">
         <v>9</v>
@@ -2007,7 +2007,7 @@
         <v>-1</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F16">
         <v>8</v>
@@ -2070,7 +2070,7 @@
         <v>-1</v>
       </c>
       <c r="Z16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA16">
         <v>8</v>
@@ -2096,7 +2096,7 @@
         <v>-1</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F17">
         <v>8</v>
@@ -2159,7 +2159,7 @@
         <v>-1</v>
       </c>
       <c r="Z17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA17">
         <v>8</v>
@@ -2505,7 +2505,7 @@
         <v>-1</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F22">
         <v>10</v>
@@ -2568,7 +2568,7 @@
         <v>-1</v>
       </c>
       <c r="Z22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA22">
         <v>10</v>
@@ -2594,7 +2594,7 @@
         <v>-1</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F23">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>-1</v>
       </c>
       <c r="Z23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA23">
         <v>8</v>
@@ -2772,7 +2772,7 @@
         <v>-1</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F25">
         <v>10</v>
@@ -2835,7 +2835,7 @@
         <v>-1</v>
       </c>
       <c r="Z25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA25">
         <v>10</v>
@@ -2861,7 +2861,7 @@
         <v>-1</v>
       </c>
       <c r="E26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F26">
         <v>8</v>
@@ -2924,7 +2924,7 @@
         <v>-1</v>
       </c>
       <c r="Z26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA26">
         <v>8</v>
@@ -3395,7 +3395,7 @@
         <v>7</v>
       </c>
       <c r="E32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F32">
         <v>10</v>
@@ -3458,7 +3458,7 @@
         <v>7</v>
       </c>
       <c r="Z32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA32">
         <v>10</v>
@@ -3523,7 +3523,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>51</v>
@@ -3532,30 +3532,30 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>10.71</v>
+        <v>14.29</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="I2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J2">
-        <v>89.29000000000001</v>
+        <v>85.70999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>52</v>
@@ -3564,25 +3564,25 @@
         <v>28</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>14.29</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="I3">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="J3">
-        <v>85.70999999999999</v>
+        <v>32.14</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3752,7 +3752,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3787,33 +3787,33 @@
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920190</v>
+        <v>20330051920191</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
         <v>51</v>
@@ -3821,59 +3821,59 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920191</v>
+        <v>20330051920193</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920191</v>
+        <v>20330051920194</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920192</v>
+        <v>20330051920194</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
         <v>51</v>
@@ -3881,79 +3881,79 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920193</v>
+        <v>20330051920194</v>
       </c>
       <c r="B7" t="s">
         <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="D7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920193</v>
+        <v>20330051920194</v>
       </c>
       <c r="B8" t="s">
         <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920194</v>
+        <v>20330051920196</v>
       </c>
       <c r="B9" t="s">
         <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D9" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920194</v>
+        <v>20330051920197</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D10" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
         <v>52</v>
@@ -3961,39 +3961,39 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920194</v>
+        <v>20330051920198</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
         <v>90</v>
       </c>
       <c r="D11" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920194</v>
+        <v>20330051920199</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
         <v>51</v>
@@ -4001,33 +4001,33 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920194</v>
+        <v>20330051920200</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C13" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D13" t="s">
         <v>112</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>20330051920196</v>
+        <v>20330051920201</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C14" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="D14" t="s">
         <v>113</v>
@@ -4036,24 +4036,24 @@
         <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>20330051920197</v>
+        <v>19330051920280</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D15" t="s">
         <v>114</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F15" t="s">
         <v>51</v>
@@ -4061,19 +4061,19 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>20330051920198</v>
+        <v>19330051920280</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C16" t="s">
         <v>93</v>
       </c>
       <c r="D16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E16" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F16" t="s">
         <v>52</v>
@@ -4081,159 +4081,159 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>20330051920199</v>
+        <v>19330051920420</v>
       </c>
       <c r="B17" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C17" t="s">
         <v>94</v>
       </c>
       <c r="D17" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E17" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>20330051920199</v>
+        <v>19330051920420</v>
       </c>
       <c r="B18" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C18" t="s">
         <v>94</v>
       </c>
       <c r="D18" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>20330051920200</v>
+        <v>19330051920420</v>
       </c>
       <c r="B19" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C19" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D19" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E19" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F19" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>20330051920200</v>
+        <v>19330051920420</v>
       </c>
       <c r="B20" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C20" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E20" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F20" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>20330051920201</v>
+        <v>20330051920202</v>
       </c>
       <c r="B21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C21" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="D21" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E21" t="s">
         <v>7</v>
       </c>
       <c r="F21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>20330051920201</v>
+        <v>20330051920202</v>
       </c>
       <c r="B22" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C22" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="D22" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E22" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F22" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>19330051920280</v>
+        <v>20330051920204</v>
       </c>
       <c r="B23" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D23" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E23" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F23" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>19330051920280</v>
+        <v>20330051920204</v>
       </c>
       <c r="B24" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C24" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D24" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E24" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F24" t="s">
         <v>51</v>
@@ -4241,199 +4241,199 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>19330051920420</v>
+        <v>20330051920204</v>
       </c>
       <c r="B25" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C25" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D25" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E25" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F25" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>19330051920420</v>
+        <v>20330051920206</v>
       </c>
       <c r="B26" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C26" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="D26" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E26" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F26" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>19330051920420</v>
+        <v>20330051920206</v>
       </c>
       <c r="B27" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C27" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="D27" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E27" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F27" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>19330051920420</v>
+        <v>20330051920207</v>
       </c>
       <c r="B28" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C28" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D28" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E28" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F28" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>20330051920202</v>
+        <v>20330051920207</v>
       </c>
       <c r="B29" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C29" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="D29" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E29" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>20330051920202</v>
+        <v>20330051920207</v>
       </c>
       <c r="B30" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C30" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="D30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E30" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F30" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>20330051920202</v>
+        <v>20330051920207</v>
       </c>
       <c r="B31" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C31" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="D31" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E31" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F31" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>20330051920204</v>
+        <v>20330051920208</v>
       </c>
       <c r="B32" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C32" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D32" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E32" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F32" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>20330051920204</v>
+        <v>19330051920290</v>
       </c>
       <c r="B33" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C33" t="s">
         <v>98</v>
       </c>
       <c r="D33" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E33" t="s">
         <v>7</v>
       </c>
       <c r="F33" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>20330051920204</v>
+        <v>20330051920209</v>
       </c>
       <c r="B34" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C34" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D34" t="s">
         <v>122</v>
       </c>
       <c r="E34" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F34" t="s">
         <v>51</v>
@@ -4441,33 +4441,33 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>20330051920204</v>
+        <v>20330051920209</v>
       </c>
       <c r="B35" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C35" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D35" t="s">
         <v>122</v>
       </c>
       <c r="E35" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F35" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>20330051920206</v>
+        <v>20330051920210</v>
       </c>
       <c r="B36" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C36" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D36" t="s">
         <v>123</v>
@@ -4476,24 +4476,24 @@
         <v>7</v>
       </c>
       <c r="F36" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>20330051920206</v>
+        <v>20330051920212</v>
       </c>
       <c r="B37" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C37" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="D37" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E37" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F37" t="s">
         <v>51</v>
@@ -4501,59 +4501,59 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>20330051920207</v>
+        <v>20330051920213</v>
       </c>
       <c r="B38" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C38" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D38" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E38" t="s">
         <v>7</v>
       </c>
       <c r="F38" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>20330051920207</v>
+        <v>20330051920213</v>
       </c>
       <c r="B39" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C39" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D39" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E39" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F39" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <v>20330051920207</v>
+        <v>20330051920214</v>
       </c>
       <c r="B40" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C40" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D40" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E40" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F40" t="s">
         <v>51</v>
@@ -4561,59 +4561,59 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>20330051920207</v>
+        <v>20330051920214</v>
       </c>
       <c r="B41" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C41" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D41" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E41" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F41" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>20330051920208</v>
+        <v>20330051920214</v>
       </c>
       <c r="B42" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C42" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D42" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E42" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F42" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43">
-        <v>20330051920208</v>
+        <v>20330051920215</v>
       </c>
       <c r="B43" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C43" t="s">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="D43" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E43" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F43" t="s">
         <v>51</v>
@@ -4621,442 +4621,122 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44">
-        <v>19330051920290</v>
+        <v>19330051920177</v>
       </c>
       <c r="B44" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C44" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D44" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E44" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F44" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45">
-        <v>19330051920290</v>
+        <v>19330051920177</v>
       </c>
       <c r="B45" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C45" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D45" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
       </c>
       <c r="F45" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46">
-        <v>20330051920209</v>
+        <v>20330051920217</v>
       </c>
       <c r="B46" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C46" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D46" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E46" t="s">
         <v>7</v>
       </c>
       <c r="F46" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47">
-        <v>20330051920209</v>
+        <v>20330051920217</v>
       </c>
       <c r="B47" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C47" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D47" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
       </c>
       <c r="F47" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48">
-        <v>20330051920210</v>
+        <v>20330051920218</v>
       </c>
       <c r="B48" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C48" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="D48" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E48" t="s">
         <v>7</v>
       </c>
       <c r="F48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49">
-        <v>20330051920210</v>
+        <v>20330051920218</v>
       </c>
       <c r="B49" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C49" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="D49" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E49" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F49" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>20330051920212</v>
-      </c>
-      <c r="B50" t="s">
-        <v>82</v>
-      </c>
-      <c r="C50" t="s">
-        <v>103</v>
-      </c>
-      <c r="D50" t="s">
-        <v>129</v>
-      </c>
-      <c r="E50" t="s">
-        <v>7</v>
-      </c>
-      <c r="F50" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>20330051920212</v>
-      </c>
-      <c r="B51" t="s">
-        <v>82</v>
-      </c>
-      <c r="C51" t="s">
-        <v>103</v>
-      </c>
-      <c r="D51" t="s">
-        <v>129</v>
-      </c>
-      <c r="E51" t="s">
-        <v>8</v>
-      </c>
-      <c r="F51" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>20330051920213</v>
-      </c>
-      <c r="B52" t="s">
-        <v>83</v>
-      </c>
-      <c r="C52" t="s">
-        <v>104</v>
-      </c>
-      <c r="D52" t="s">
-        <v>130</v>
-      </c>
-      <c r="E52" t="s">
-        <v>7</v>
-      </c>
-      <c r="F52" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>20330051920213</v>
-      </c>
-      <c r="B53" t="s">
-        <v>83</v>
-      </c>
-      <c r="C53" t="s">
-        <v>104</v>
-      </c>
-      <c r="D53" t="s">
-        <v>130</v>
-      </c>
-      <c r="E53" t="s">
-        <v>8</v>
-      </c>
-      <c r="F53" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>20330051920214</v>
-      </c>
-      <c r="B54" t="s">
-        <v>84</v>
-      </c>
-      <c r="C54" t="s">
-        <v>105</v>
-      </c>
-      <c r="D54" t="s">
-        <v>131</v>
-      </c>
-      <c r="E54" t="s">
-        <v>7</v>
-      </c>
-      <c r="F54" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>20330051920214</v>
-      </c>
-      <c r="B55" t="s">
-        <v>84</v>
-      </c>
-      <c r="C55" t="s">
-        <v>105</v>
-      </c>
-      <c r="D55" t="s">
-        <v>131</v>
-      </c>
-      <c r="E55" t="s">
-        <v>8</v>
-      </c>
-      <c r="F55" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>20330051920214</v>
-      </c>
-      <c r="B56" t="s">
-        <v>84</v>
-      </c>
-      <c r="C56" t="s">
-        <v>105</v>
-      </c>
-      <c r="D56" t="s">
-        <v>131</v>
-      </c>
-      <c r="E56" t="s">
-        <v>10</v>
-      </c>
-      <c r="F56" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>20330051920215</v>
-      </c>
-      <c r="B57" t="s">
-        <v>84</v>
-      </c>
-      <c r="C57" t="s">
-        <v>73</v>
-      </c>
-      <c r="D57" t="s">
-        <v>132</v>
-      </c>
-      <c r="E57" t="s">
-        <v>7</v>
-      </c>
-      <c r="F57" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>19330051920177</v>
-      </c>
-      <c r="B58" t="s">
-        <v>84</v>
-      </c>
-      <c r="C58" t="s">
-        <v>100</v>
-      </c>
-      <c r="D58" t="s">
-        <v>133</v>
-      </c>
-      <c r="E58" t="s">
-        <v>5</v>
-      </c>
-      <c r="F58" t="s">
         <v>53</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>19330051920177</v>
-      </c>
-      <c r="B59" t="s">
-        <v>84</v>
-      </c>
-      <c r="C59" t="s">
-        <v>100</v>
-      </c>
-      <c r="D59" t="s">
-        <v>133</v>
-      </c>
-      <c r="E59" t="s">
-        <v>8</v>
-      </c>
-      <c r="F59" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>20330051920217</v>
-      </c>
-      <c r="B60" t="s">
-        <v>84</v>
-      </c>
-      <c r="C60" t="s">
-        <v>106</v>
-      </c>
-      <c r="D60" t="s">
-        <v>134</v>
-      </c>
-      <c r="E60" t="s">
-        <v>7</v>
-      </c>
-      <c r="F60" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>20330051920217</v>
-      </c>
-      <c r="B61" t="s">
-        <v>84</v>
-      </c>
-      <c r="C61" t="s">
-        <v>106</v>
-      </c>
-      <c r="D61" t="s">
-        <v>134</v>
-      </c>
-      <c r="E61" t="s">
-        <v>8</v>
-      </c>
-      <c r="F61" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>20330051920218</v>
-      </c>
-      <c r="B62" t="s">
-        <v>85</v>
-      </c>
-      <c r="C62" t="s">
-        <v>103</v>
-      </c>
-      <c r="D62" t="s">
-        <v>135</v>
-      </c>
-      <c r="E62" t="s">
-        <v>7</v>
-      </c>
-      <c r="F62" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>20330051920218</v>
-      </c>
-      <c r="B63" t="s">
-        <v>85</v>
-      </c>
-      <c r="C63" t="s">
-        <v>103</v>
-      </c>
-      <c r="D63" t="s">
-        <v>135</v>
-      </c>
-      <c r="E63" t="s">
-        <v>5</v>
-      </c>
-      <c r="F63" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>20330051920218</v>
-      </c>
-      <c r="B64" t="s">
-        <v>85</v>
-      </c>
-      <c r="C64" t="s">
-        <v>103</v>
-      </c>
-      <c r="D64" t="s">
-        <v>135</v>
-      </c>
-      <c r="E64" t="s">
-        <v>8</v>
-      </c>
-      <c r="F64" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>20330051920219</v>
-      </c>
-      <c r="B65" t="s">
-        <v>86</v>
-      </c>
-      <c r="C65" t="s">
-        <v>107</v>
-      </c>
-      <c r="D65" t="s">
-        <v>136</v>
-      </c>
-      <c r="E65" t="s">
-        <v>8</v>
-      </c>
-      <c r="F65" t="s">
-        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -5095,16 +4775,16 @@
         <v>20330051920194</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -5112,13 +4792,13 @@
         <v>19330051920420</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E3">
         <v>4</v>
@@ -5126,16 +4806,16 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920204</v>
+        <v>20330051920207</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E4">
         <v>4</v>
@@ -5143,33 +4823,33 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920207</v>
+        <v>20330051920204</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920202</v>
+        <v>20330051920214</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="D6" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -5177,50 +4857,50 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920214</v>
+        <v>19330051920280</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920218</v>
+        <v>20330051920202</v>
       </c>
       <c r="B8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" t="s">
         <v>85</v>
       </c>
-      <c r="C8" t="s">
-        <v>103</v>
-      </c>
       <c r="D8" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920190</v>
+        <v>20330051920206</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -5228,16 +4908,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920191</v>
+        <v>20330051920209</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="D10" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -5245,16 +4925,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920193</v>
+        <v>20330051920213</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>71</v>
+        <v>101</v>
       </c>
       <c r="D11" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -5262,16 +4942,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920199</v>
+        <v>19330051920177</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D12" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -5279,16 +4959,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920200</v>
+        <v>20330051920217</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="C13" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="D13" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -5296,16 +4976,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920201</v>
+        <v>20330051920218</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="D14" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="E14">
         <v>2</v>
@@ -5313,186 +4993,186 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920280</v>
+        <v>20330051920190</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="C15" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="D15" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920206</v>
+        <v>20330051920191</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="C16" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D16" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920208</v>
+        <v>20330051920193</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="C17" t="s">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="D17" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920290</v>
+        <v>20330051920196</v>
       </c>
       <c r="B18" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="C18" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="D18" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920209</v>
+        <v>20330051920197</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="C19" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="D19" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920210</v>
+        <v>20330051920198</v>
       </c>
       <c r="B20" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="C20" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D20" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920212</v>
+        <v>20330051920199</v>
       </c>
       <c r="B21" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="C21" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="D21" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920213</v>
+        <v>20330051920200</v>
       </c>
       <c r="B22" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="D22" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920177</v>
+        <v>20330051920201</v>
       </c>
       <c r="B23" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="C23" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="D23" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920217</v>
+        <v>20330051920208</v>
       </c>
       <c r="B24" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C24" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D24" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920192</v>
+        <v>19330051920290</v>
       </c>
       <c r="B25" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="C25" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="D25" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="E25">
         <v>1</v>
@@ -5500,16 +5180,16 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920196</v>
+        <v>20330051920210</v>
       </c>
       <c r="B26" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="C26" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D26" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="E26">
         <v>1</v>
@@ -5517,16 +5197,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920197</v>
+        <v>20330051920212</v>
       </c>
       <c r="B27" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="C27" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="D27" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="E27">
         <v>1</v>
@@ -5534,16 +5214,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920198</v>
+        <v>20330051920215</v>
       </c>
       <c r="B28" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="C28" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="D28" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="E28">
         <v>1</v>
@@ -5551,19 +5231,19 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920215</v>
+        <v>20330051920192</v>
       </c>
       <c r="B29" t="s">
-        <v>84</v>
+        <v>131</v>
       </c>
       <c r="C29" t="s">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="D29" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -5571,16 +5251,16 @@
         <v>20330051920219</v>
       </c>
       <c r="B30" t="s">
-        <v>86</v>
+        <v>132</v>
       </c>
       <c r="C30" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="D30" t="s">
         <v>136</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5590,7 +5270,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5622,22 +5302,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920190</v>
+        <v>19330051920280</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G2">
         <v>-1</v>
@@ -5645,22 +5325,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920190</v>
+        <v>19330051920280</v>
       </c>
       <c r="B3" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G3">
         <v>-1</v>
@@ -5668,22 +5348,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920191</v>
+        <v>20330051920202</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -5691,19 +5371,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920191</v>
+        <v>20330051920202</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
         <v>51</v>
@@ -5714,22 +5394,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920193</v>
+        <v>20330051920206</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G6">
         <v>-1</v>
@@ -5737,22 +5417,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920193</v>
+        <v>20330051920206</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G7">
         <v>-1</v>
@@ -5760,22 +5440,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920199</v>
+        <v>20330051920209</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D8" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G8">
         <v>-1</v>
@@ -5783,22 +5463,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920199</v>
+        <v>20330051920209</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D9" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G9">
         <v>-1</v>
@@ -5806,22 +5486,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920200</v>
+        <v>20330051920213</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="D10" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G10">
         <v>-1</v>
@@ -5829,22 +5509,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920200</v>
+        <v>20330051920213</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="D11" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G11">
         <v>-1</v>
@@ -5852,22 +5532,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920201</v>
+        <v>19330051920177</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="D12" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G12">
         <v>-1</v>
@@ -5875,22 +5555,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920201</v>
+        <v>19330051920177</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="D13" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G13">
         <v>-1</v>
@@ -5898,22 +5578,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920280</v>
+        <v>20330051920217</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="C14" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="D14" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="E14" t="s">
         <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G14">
         <v>-1</v>
@@ -5921,22 +5601,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920280</v>
+        <v>20330051920217</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="C15" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="D15" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G15">
         <v>-1</v>
@@ -5944,22 +5624,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920206</v>
+        <v>20330051920190</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="C16" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D16" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="E16" t="s">
         <v>7</v>
       </c>
       <c r="F16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G16">
         <v>-1</v>
@@ -5967,19 +5647,19 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920206</v>
+        <v>20330051920191</v>
       </c>
       <c r="B17" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="C17" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D17" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F17" t="s">
         <v>51</v>
@@ -5990,22 +5670,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920208</v>
+        <v>20330051920193</v>
       </c>
       <c r="B18" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="C18" t="s">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="D18" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="E18" t="s">
         <v>7</v>
       </c>
       <c r="F18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G18">
         <v>-1</v>
@@ -6013,19 +5693,19 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920208</v>
+        <v>20330051920196</v>
       </c>
       <c r="B19" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C19" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="D19" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="E19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F19" t="s">
         <v>51</v>
@@ -6036,19 +5716,19 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>19330051920290</v>
+        <v>20330051920197</v>
       </c>
       <c r="B20" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="C20" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="D20" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="E20" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F20" t="s">
         <v>52</v>
@@ -6059,19 +5739,19 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>19330051920290</v>
+        <v>20330051920198</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C21" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="D21" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="E21" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F21" t="s">
         <v>51</v>
@@ -6082,22 +5762,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>20330051920209</v>
+        <v>20330051920199</v>
       </c>
       <c r="B22" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="C22" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="D22" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="E22" t="s">
         <v>7</v>
       </c>
       <c r="F22" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G22">
         <v>-1</v>
@@ -6105,19 +5785,19 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>20330051920209</v>
+        <v>20330051920200</v>
       </c>
       <c r="B23" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C23" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="D23" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="E23" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F23" t="s">
         <v>51</v>
@@ -6128,22 +5808,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>20330051920210</v>
+        <v>20330051920201</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="C24" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="D24" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="E24" t="s">
         <v>7</v>
       </c>
       <c r="F24" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G24">
         <v>-1</v>
@@ -6151,19 +5831,19 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>20330051920210</v>
+        <v>20330051920208</v>
       </c>
       <c r="B25" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C25" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="D25" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="E25" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F25" t="s">
         <v>51</v>
@@ -6174,22 +5854,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>20330051920212</v>
+        <v>19330051920290</v>
       </c>
       <c r="B26" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C26" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D26" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="E26" t="s">
         <v>7</v>
       </c>
       <c r="F26" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G26">
         <v>-1</v>
@@ -6197,19 +5877,19 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>20330051920212</v>
+        <v>20330051920210</v>
       </c>
       <c r="B27" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C27" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="D27" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="E27" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F27" t="s">
         <v>51</v>
@@ -6220,22 +5900,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>20330051920213</v>
+        <v>20330051920212</v>
       </c>
       <c r="B28" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C28" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D28" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E28" t="s">
         <v>7</v>
       </c>
       <c r="F28" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G28">
         <v>-1</v>
@@ -6243,254 +5923,24 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>20330051920213</v>
+        <v>20330051920215</v>
       </c>
       <c r="B29" t="s">
         <v>83</v>
       </c>
       <c r="C29" t="s">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="D29" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E29" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F29" t="s">
         <v>51</v>
       </c>
       <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>19330051920177</v>
-      </c>
-      <c r="B30" t="s">
-        <v>84</v>
-      </c>
-      <c r="C30" t="s">
-        <v>100</v>
-      </c>
-      <c r="D30" t="s">
-        <v>133</v>
-      </c>
-      <c r="E30" t="s">
-        <v>5</v>
-      </c>
-      <c r="F30" t="s">
-        <v>53</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>19330051920177</v>
-      </c>
-      <c r="B31" t="s">
-        <v>84</v>
-      </c>
-      <c r="C31" t="s">
-        <v>100</v>
-      </c>
-      <c r="D31" t="s">
-        <v>133</v>
-      </c>
-      <c r="E31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" t="s">
-        <v>51</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>20330051920217</v>
-      </c>
-      <c r="B32" t="s">
-        <v>84</v>
-      </c>
-      <c r="C32" t="s">
-        <v>106</v>
-      </c>
-      <c r="D32" t="s">
-        <v>134</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" t="s">
-        <v>52</v>
-      </c>
-      <c r="G32">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>20330051920217</v>
-      </c>
-      <c r="B33" t="s">
-        <v>84</v>
-      </c>
-      <c r="C33" t="s">
-        <v>106</v>
-      </c>
-      <c r="D33" t="s">
-        <v>134</v>
-      </c>
-      <c r="E33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" t="s">
-        <v>51</v>
-      </c>
-      <c r="G33">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>20330051920192</v>
-      </c>
-      <c r="B34" t="s">
-        <v>64</v>
-      </c>
-      <c r="C34" t="s">
-        <v>89</v>
-      </c>
-      <c r="D34" t="s">
-        <v>110</v>
-      </c>
-      <c r="E34" t="s">
-        <v>8</v>
-      </c>
-      <c r="F34" t="s">
-        <v>51</v>
-      </c>
-      <c r="G34">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>20330051920196</v>
-      </c>
-      <c r="B35" t="s">
-        <v>67</v>
-      </c>
-      <c r="C35" t="s">
-        <v>91</v>
-      </c>
-      <c r="D35" t="s">
-        <v>113</v>
-      </c>
-      <c r="E35" t="s">
-        <v>7</v>
-      </c>
-      <c r="F35" t="s">
-        <v>52</v>
-      </c>
-      <c r="G35">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>20330051920197</v>
-      </c>
-      <c r="B36" t="s">
-        <v>68</v>
-      </c>
-      <c r="C36" t="s">
-        <v>92</v>
-      </c>
-      <c r="D36" t="s">
-        <v>114</v>
-      </c>
-      <c r="E36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F36" t="s">
-        <v>51</v>
-      </c>
-      <c r="G36">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>20330051920198</v>
-      </c>
-      <c r="B37" t="s">
-        <v>69</v>
-      </c>
-      <c r="C37" t="s">
-        <v>93</v>
-      </c>
-      <c r="D37" t="s">
-        <v>115</v>
-      </c>
-      <c r="E37" t="s">
-        <v>7</v>
-      </c>
-      <c r="F37" t="s">
-        <v>52</v>
-      </c>
-      <c r="G37">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>20330051920215</v>
-      </c>
-      <c r="B38" t="s">
-        <v>84</v>
-      </c>
-      <c r="C38" t="s">
-        <v>73</v>
-      </c>
-      <c r="D38" t="s">
-        <v>132</v>
-      </c>
-      <c r="E38" t="s">
-        <v>7</v>
-      </c>
-      <c r="F38" t="s">
-        <v>52</v>
-      </c>
-      <c r="G38">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>20330051920219</v>
-      </c>
-      <c r="B39" t="s">
-        <v>86</v>
-      </c>
-      <c r="C39" t="s">
-        <v>107</v>
-      </c>
-      <c r="D39" t="s">
-        <v>136</v>
-      </c>
-      <c r="E39" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" t="s">
-        <v>51</v>
-      </c>
-      <c r="G39">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/4ALCV - Estadisticos 20212.xlsx
+++ b/grupos/4ALCV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="137">
   <si>
     <t>Materia</t>
   </si>
@@ -176,21 +176,21 @@
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
+    <t>Flores Ovalle Victor</t>
+  </si>
+  <si>
+    <t>Ángel Martínez Noe Cristobal</t>
+  </si>
+  <si>
+    <t>Martínez Castillo Columba</t>
+  </si>
+  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
-    <t>Flores Ovalle Victor</t>
-  </si>
-  <si>
-    <t>Ángel Martínez Noe Cristobal</t>
-  </si>
-  <si>
-    <t>Martínez Castillo Columba</t>
-  </si>
-  <si>
     <t>Rivera Serra Alma Lilian</t>
   </si>
   <si>
@@ -221,211 +221,211 @@
     <t>ESTEVEZ</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GALVEZ</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>MELENDEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>PEÑA</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>DE LA TEJA</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>ROQUE</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>SALGADO</t>
+  </si>
+  <si>
+    <t>OLIVERA</t>
+  </si>
+  <si>
+    <t>DAMIEN</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>MEJIA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>REYNA ARISBETH</t>
+  </si>
+  <si>
+    <t>ANALI</t>
+  </si>
+  <si>
+    <t>DULCE FERNANDA</t>
+  </si>
+  <si>
+    <t>KITZIA YAMILET</t>
+  </si>
+  <si>
+    <t>ERICK DE JESUS</t>
+  </si>
+  <si>
+    <t>AMARELY GUADALUPE</t>
+  </si>
+  <si>
+    <t>FRIDA SOFIA</t>
+  </si>
+  <si>
+    <t>ANTONIO ABIDAN</t>
+  </si>
+  <si>
+    <t>YAMILET</t>
+  </si>
+  <si>
+    <t>MILAGROS</t>
+  </si>
+  <si>
+    <t>ROBERTO JESUS</t>
+  </si>
+  <si>
+    <t>ITZEL</t>
+  </si>
+  <si>
+    <t>CRISTHIAN</t>
+  </si>
+  <si>
+    <t>MARITZA JULIANA</t>
+  </si>
+  <si>
+    <t>VICTOR MANUEL</t>
+  </si>
+  <si>
+    <t>LESLIE</t>
+  </si>
+  <si>
+    <t>HEIDY MARIAM</t>
+  </si>
+  <si>
+    <t>YEILI DAYNERIS</t>
+  </si>
+  <si>
+    <t>JULIO CESAR</t>
+  </si>
+  <si>
+    <t>INGRID SARAI</t>
+  </si>
+  <si>
+    <t>SUSANA</t>
+  </si>
+  <si>
+    <t>ALEJANDRA</t>
+  </si>
+  <si>
+    <t>AMADA ARELY</t>
+  </si>
+  <si>
+    <t>JOSSELIN ANDREA</t>
+  </si>
+  <si>
+    <t>LUIS DIEGO</t>
+  </si>
+  <si>
+    <t>ALISSON FERNANDA</t>
+  </si>
+  <si>
+    <t>BALTAZARES</t>
+  </si>
+  <si>
     <t>ESPERON</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GALVEZ</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>MELENDEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>PEÑA</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>DE LA TEJA</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>MORENO</t>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
   </si>
   <si>
     <t>MORA</t>
   </si>
   <si>
-    <t>ROQUE</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>SALGADO</t>
-  </si>
-  <si>
-    <t>OLIVERA</t>
-  </si>
-  <si>
-    <t>DAMIEN</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>MEJIA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>REYNA ARISBETH</t>
-  </si>
-  <si>
-    <t>ANALI</t>
-  </si>
-  <si>
-    <t>DULCE FERNANDA</t>
-  </si>
-  <si>
-    <t>KITZIA YAMILET</t>
-  </si>
-  <si>
-    <t>ERICK DE JESUS</t>
+    <t>GALEOTE</t>
+  </si>
+  <si>
+    <t>JOCELYN</t>
   </si>
   <si>
     <t>MIA VALENTINA</t>
-  </si>
-  <si>
-    <t>AMARELY GUADALUPE</t>
-  </si>
-  <si>
-    <t>FRIDA SOFIA</t>
-  </si>
-  <si>
-    <t>ANTONIO ABIDAN</t>
-  </si>
-  <si>
-    <t>YAMILET</t>
-  </si>
-  <si>
-    <t>MILAGROS</t>
-  </si>
-  <si>
-    <t>ROBERTO JESUS</t>
-  </si>
-  <si>
-    <t>ITZEL</t>
-  </si>
-  <si>
-    <t>CRISTHIAN</t>
-  </si>
-  <si>
-    <t>MARITZA JULIANA</t>
-  </si>
-  <si>
-    <t>VICTOR MANUEL</t>
-  </si>
-  <si>
-    <t>LESLIE</t>
-  </si>
-  <si>
-    <t>HEIDY MARIAM</t>
-  </si>
-  <si>
-    <t>YEILI DAYNERIS</t>
-  </si>
-  <si>
-    <t>JULIO CESAR</t>
-  </si>
-  <si>
-    <t>INGRID SARAI</t>
-  </si>
-  <si>
-    <t>SUSANA</t>
-  </si>
-  <si>
-    <t>ALEJANDRA</t>
-  </si>
-  <si>
-    <t>AMADA ARELY</t>
-  </si>
-  <si>
-    <t>JOSSELIN ANDREA</t>
-  </si>
-  <si>
-    <t>LUIS DIEGO</t>
-  </si>
-  <si>
-    <t>ALISSON FERNANDA</t>
-  </si>
-  <si>
-    <t>BALTAZARES</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>JOCELYN</t>
   </si>
   <si>
     <t>EMILY</t>
@@ -1651,7 +1651,7 @@
         <v>6</v>
       </c>
       <c r="E12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F12">
         <v>10</v>
@@ -1714,7 +1714,7 @@
         <v>6</v>
       </c>
       <c r="Z12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA12">
         <v>10</v>
@@ -2185,7 +2185,7 @@
         <v>-1</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F18">
         <v>10</v>
@@ -2248,7 +2248,7 @@
         <v>-1</v>
       </c>
       <c r="Z18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA18">
         <v>10</v>
@@ -2327,7 +2327,7 @@
         <v>-1</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F20">
         <v>9</v>
@@ -2390,7 +2390,7 @@
         <v>-1</v>
       </c>
       <c r="Z20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA20">
         <v>9</v>
@@ -2416,7 +2416,7 @@
         <v>-1</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F21">
         <v>5</v>
@@ -2479,7 +2479,7 @@
         <v>-1</v>
       </c>
       <c r="Z21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA21">
         <v>5</v>
@@ -2683,7 +2683,7 @@
         <v>-1</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F24">
         <v>9</v>
@@ -2746,7 +2746,7 @@
         <v>-1</v>
       </c>
       <c r="Z24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA24">
         <v>9</v>
@@ -2950,7 +2950,7 @@
         <v>-1</v>
       </c>
       <c r="E27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F27">
         <v>6</v>
@@ -3013,7 +3013,7 @@
         <v>-1</v>
       </c>
       <c r="Z27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA27">
         <v>6</v>
@@ -3128,7 +3128,7 @@
         <v>-1</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F29">
         <v>7</v>
@@ -3191,7 +3191,7 @@
         <v>-1</v>
       </c>
       <c r="Z29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA29">
         <v>7</v>
@@ -3217,7 +3217,7 @@
         <v>8</v>
       </c>
       <c r="E30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F30">
         <v>10</v>
@@ -3280,7 +3280,7 @@
         <v>8</v>
       </c>
       <c r="Z30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA30">
         <v>10</v>
@@ -3306,7 +3306,7 @@
         <v>-1</v>
       </c>
       <c r="E31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F31">
         <v>9</v>
@@ -3369,7 +3369,7 @@
         <v>-1</v>
       </c>
       <c r="Z31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA31">
         <v>9</v>
@@ -3555,7 +3555,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>52</v>
@@ -3564,62 +3564,62 @@
         <v>28</v>
       </c>
       <c r="D3">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>64.29000000000001</v>
+        <v>82.14</v>
       </c>
       <c r="G3">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J3">
-        <v>32.14</v>
+        <v>17.86</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>53</v>
       </c>
       <c r="C4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>82.14</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="I4">
         <v>5</v>
       </c>
       <c r="J4">
-        <v>17.86</v>
+        <v>17.24</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>54</v>
@@ -3631,27 +3631,27 @@
         <v>24</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F5">
         <v>82.76000000000001</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>13.79</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J5">
-        <v>17.24</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>55</v>
@@ -3660,57 +3660,57 @@
         <v>29</v>
       </c>
       <c r="D6">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>82.76000000000001</v>
+        <v>89.66</v>
       </c>
       <c r="G6">
-        <v>13.79</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J6">
-        <v>3.45</v>
+        <v>10.34</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>56</v>
       </c>
       <c r="C7">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D7">
         <v>26</v>
       </c>
       <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>92.86</v>
+      </c>
+      <c r="G7">
+        <v>7.14</v>
+      </c>
+      <c r="H7">
+        <v>8.1</v>
+      </c>
+      <c r="I7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>89.66</v>
-      </c>
-      <c r="G7">
+      <c r="J7">
         <v>0</v>
-      </c>
-      <c r="H7">
-        <v>8.4</v>
-      </c>
-      <c r="I7">
-        <v>3</v>
-      </c>
-      <c r="J7">
-        <v>10.34</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -3752,7 +3752,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3787,10 +3787,10 @@
         <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -3807,10 +3807,10 @@
         <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -3827,10 +3827,10 @@
         <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -3847,16 +3847,16 @@
         <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3867,10 +3867,10 @@
         <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -3887,16 +3887,16 @@
         <v>65</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E7" t="s">
         <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3907,16 +3907,16 @@
         <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3927,10 +3927,10 @@
         <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
@@ -3941,36 +3941,36 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920197</v>
+        <v>20330051920198</v>
       </c>
       <c r="B10" t="s">
         <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920198</v>
+        <v>20330051920199</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
@@ -3981,16 +3981,16 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920199</v>
+        <v>20330051920200</v>
       </c>
       <c r="B12" t="s">
         <v>68</v>
       </c>
       <c r="C12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D12" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
@@ -4001,16 +4001,16 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920200</v>
+        <v>20330051920201</v>
       </c>
       <c r="B13" t="s">
         <v>69</v>
       </c>
       <c r="C13" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="D13" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
@@ -4021,16 +4021,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>20330051920201</v>
+        <v>19330051920280</v>
       </c>
       <c r="B14" t="s">
         <v>70</v>
       </c>
       <c r="C14" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="D14" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E14" t="s">
         <v>7</v>
@@ -4041,42 +4041,42 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>19330051920280</v>
+        <v>19330051920420</v>
       </c>
       <c r="B15" t="s">
         <v>71</v>
       </c>
       <c r="C15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D15" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>19330051920280</v>
+        <v>19330051920420</v>
       </c>
       <c r="B16" t="s">
         <v>71</v>
       </c>
       <c r="C16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D16" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -4084,19 +4084,19 @@
         <v>19330051920420</v>
       </c>
       <c r="B17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C17" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D17" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E17" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -4104,99 +4104,99 @@
         <v>19330051920420</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C18" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D18" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E18" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F18" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>19330051920420</v>
+        <v>20330051920202</v>
       </c>
       <c r="B19" t="s">
         <v>72</v>
       </c>
       <c r="C19" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D19" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F19" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>19330051920420</v>
+        <v>20330051920202</v>
       </c>
       <c r="B20" t="s">
         <v>72</v>
       </c>
       <c r="C20" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D20" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E20" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F20" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>20330051920202</v>
+        <v>20330051920204</v>
       </c>
       <c r="B21" t="s">
         <v>73</v>
       </c>
       <c r="C21" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="D21" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E21" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F21" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>20330051920202</v>
+        <v>20330051920204</v>
       </c>
       <c r="B22" t="s">
         <v>73</v>
       </c>
       <c r="C22" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="D22" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E22" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F22" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -4204,33 +4204,33 @@
         <v>20330051920204</v>
       </c>
       <c r="B23" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C23" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D23" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E23" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F23" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>20330051920204</v>
+        <v>20330051920206</v>
       </c>
       <c r="B24" t="s">
         <v>74</v>
       </c>
       <c r="C24" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="D24" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E24" t="s">
         <v>7</v>
@@ -4241,76 +4241,76 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>20330051920204</v>
+        <v>20330051920207</v>
       </c>
       <c r="B25" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C25" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D25" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E25" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F25" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>20330051920206</v>
+        <v>20330051920207</v>
       </c>
       <c r="B26" t="s">
         <v>75</v>
       </c>
       <c r="C26" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="D26" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E26" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F26" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>20330051920206</v>
+        <v>20330051920207</v>
       </c>
       <c r="B27" t="s">
         <v>75</v>
       </c>
       <c r="C27" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="D27" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E27" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>20330051920207</v>
+        <v>20330051920208</v>
       </c>
       <c r="B28" t="s">
         <v>76</v>
       </c>
       <c r="C28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D28" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E28" t="s">
         <v>7</v>
@@ -4321,76 +4321,76 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>20330051920207</v>
+        <v>19330051920290</v>
       </c>
       <c r="B29" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C29" t="s">
         <v>96</v>
       </c>
       <c r="D29" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E29" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F29" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>20330051920207</v>
+        <v>20330051920209</v>
       </c>
       <c r="B30" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C30" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D30" t="s">
         <v>119</v>
       </c>
       <c r="E30" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F30" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>20330051920207</v>
+        <v>20330051920210</v>
       </c>
       <c r="B31" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C31" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="D31" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E31" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F31" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>20330051920208</v>
+        <v>20330051920212</v>
       </c>
       <c r="B32" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C32" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D32" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E32" t="s">
         <v>7</v>
@@ -4401,16 +4401,16 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>19330051920290</v>
+        <v>20330051920213</v>
       </c>
       <c r="B33" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C33" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D33" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E33" t="s">
         <v>7</v>
@@ -4421,16 +4421,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>20330051920209</v>
+        <v>20330051920214</v>
       </c>
       <c r="B34" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C34" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D34" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E34" t="s">
         <v>7</v>
@@ -4441,36 +4441,36 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>20330051920209</v>
+        <v>20330051920214</v>
       </c>
       <c r="B35" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C35" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D35" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E35" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F35" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>20330051920210</v>
+        <v>20330051920215</v>
       </c>
       <c r="B36" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C36" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="D36" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E36" t="s">
         <v>7</v>
@@ -4481,27 +4481,27 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>20330051920212</v>
+        <v>19330051920177</v>
       </c>
       <c r="B37" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C37" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D37" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E37" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F37" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>20330051920213</v>
+        <v>20330051920217</v>
       </c>
       <c r="B38" t="s">
         <v>82</v>
@@ -4510,7 +4510,7 @@
         <v>101</v>
       </c>
       <c r="D38" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E38" t="s">
         <v>7</v>
@@ -4521,222 +4521,42 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>20330051920213</v>
+        <v>20330051920218</v>
       </c>
       <c r="B39" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C39" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D39" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E39" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F39" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <v>20330051920214</v>
+        <v>20330051920218</v>
       </c>
       <c r="B40" t="s">
         <v>83</v>
       </c>
       <c r="C40" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D40" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E40" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F40" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>20330051920214</v>
-      </c>
-      <c r="B41" t="s">
-        <v>83</v>
-      </c>
-      <c r="C41" t="s">
-        <v>102</v>
-      </c>
-      <c r="D41" t="s">
-        <v>126</v>
-      </c>
-      <c r="E41" t="s">
-        <v>8</v>
-      </c>
-      <c r="F41" t="s">
         <v>52</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>20330051920214</v>
-      </c>
-      <c r="B42" t="s">
-        <v>83</v>
-      </c>
-      <c r="C42" t="s">
-        <v>102</v>
-      </c>
-      <c r="D42" t="s">
-        <v>126</v>
-      </c>
-      <c r="E42" t="s">
-        <v>10</v>
-      </c>
-      <c r="F42" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>20330051920215</v>
-      </c>
-      <c r="B43" t="s">
-        <v>83</v>
-      </c>
-      <c r="C43" t="s">
-        <v>72</v>
-      </c>
-      <c r="D43" t="s">
-        <v>127</v>
-      </c>
-      <c r="E43" t="s">
-        <v>7</v>
-      </c>
-      <c r="F43" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>19330051920177</v>
-      </c>
-      <c r="B44" t="s">
-        <v>83</v>
-      </c>
-      <c r="C44" t="s">
-        <v>97</v>
-      </c>
-      <c r="D44" t="s">
-        <v>128</v>
-      </c>
-      <c r="E44" t="s">
-        <v>5</v>
-      </c>
-      <c r="F44" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>19330051920177</v>
-      </c>
-      <c r="B45" t="s">
-        <v>83</v>
-      </c>
-      <c r="C45" t="s">
-        <v>97</v>
-      </c>
-      <c r="D45" t="s">
-        <v>128</v>
-      </c>
-      <c r="E45" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>20330051920217</v>
-      </c>
-      <c r="B46" t="s">
-        <v>83</v>
-      </c>
-      <c r="C46" t="s">
-        <v>103</v>
-      </c>
-      <c r="D46" t="s">
-        <v>129</v>
-      </c>
-      <c r="E46" t="s">
-        <v>7</v>
-      </c>
-      <c r="F46" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>20330051920217</v>
-      </c>
-      <c r="B47" t="s">
-        <v>83</v>
-      </c>
-      <c r="C47" t="s">
-        <v>103</v>
-      </c>
-      <c r="D47" t="s">
-        <v>129</v>
-      </c>
-      <c r="E47" t="s">
-        <v>8</v>
-      </c>
-      <c r="F47" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>20330051920218</v>
-      </c>
-      <c r="B48" t="s">
-        <v>84</v>
-      </c>
-      <c r="C48" t="s">
-        <v>100</v>
-      </c>
-      <c r="D48" t="s">
-        <v>130</v>
-      </c>
-      <c r="E48" t="s">
-        <v>7</v>
-      </c>
-      <c r="F48" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>20330051920218</v>
-      </c>
-      <c r="B49" t="s">
-        <v>84</v>
-      </c>
-      <c r="C49" t="s">
-        <v>100</v>
-      </c>
-      <c r="D49" t="s">
-        <v>130</v>
-      </c>
-      <c r="E49" t="s">
-        <v>5</v>
-      </c>
-      <c r="F49" t="s">
-        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -4778,10 +4598,10 @@
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E2">
         <v>4</v>
@@ -4792,13 +4612,13 @@
         <v>19330051920420</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E3">
         <v>4</v>
@@ -4806,33 +4626,33 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920207</v>
+        <v>20330051920204</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920204</v>
+        <v>20330051920207</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E5">
         <v>3</v>
@@ -4840,33 +4660,33 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920214</v>
+        <v>20330051920202</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="C6" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920280</v>
+        <v>20330051920214</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D7" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="E7">
         <v>2</v>
@@ -4874,16 +4694,16 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920202</v>
+        <v>20330051920218</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="D8" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="E8">
         <v>2</v>
@@ -4891,118 +4711,118 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920206</v>
+        <v>20330051920190</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D9" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920209</v>
+        <v>20330051920191</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920213</v>
+        <v>20330051920193</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>69</v>
       </c>
       <c r="D11" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920177</v>
+        <v>20330051920196</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="D12" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920217</v>
+        <v>20330051920198</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920218</v>
+        <v>20330051920199</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="D14" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920190</v>
+        <v>20330051920200</v>
       </c>
       <c r="B15" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D15" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -5010,16 +4830,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920191</v>
+        <v>20330051920201</v>
       </c>
       <c r="B16" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C16" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="D16" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -5027,16 +4847,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920193</v>
+        <v>19330051920280</v>
       </c>
       <c r="B17" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="C17" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="D17" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -5044,16 +4864,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920196</v>
+        <v>20330051920206</v>
       </c>
       <c r="B18" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C18" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D18" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -5061,16 +4881,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920197</v>
+        <v>20330051920208</v>
       </c>
       <c r="B19" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="C19" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D19" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="E19">
         <v>1</v>
@@ -5078,16 +4898,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920198</v>
+        <v>19330051920290</v>
       </c>
       <c r="B20" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="C20" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D20" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -5095,16 +4915,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920199</v>
+        <v>20330051920209</v>
       </c>
       <c r="B21" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C21" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D21" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -5112,16 +4932,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920200</v>
+        <v>20330051920210</v>
       </c>
       <c r="B22" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="C22" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="D22" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="E22">
         <v>1</v>
@@ -5129,16 +4949,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920201</v>
+        <v>20330051920212</v>
       </c>
       <c r="B23" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="C23" t="s">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="D23" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -5146,16 +4966,16 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920208</v>
+        <v>20330051920213</v>
       </c>
       <c r="B24" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C24" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D24" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -5163,16 +4983,16 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920290</v>
+        <v>20330051920215</v>
       </c>
       <c r="B25" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C25" t="s">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="D25" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E25">
         <v>1</v>
@@ -5180,16 +5000,16 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920210</v>
+        <v>19330051920177</v>
       </c>
       <c r="B26" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C26" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="D26" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E26">
         <v>1</v>
@@ -5197,16 +5017,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920212</v>
+        <v>20330051920217</v>
       </c>
       <c r="B27" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C27" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D27" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E27">
         <v>1</v>
@@ -5214,30 +5034,30 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920215</v>
+        <v>20330051920192</v>
       </c>
       <c r="B28" t="s">
-        <v>83</v>
+        <v>128</v>
       </c>
       <c r="C28" t="s">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D28" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920192</v>
+        <v>20330051920197</v>
       </c>
       <c r="B29" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C29" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D29" t="s">
         <v>135</v>
@@ -5251,10 +5071,10 @@
         <v>20330051920219</v>
       </c>
       <c r="B30" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C30" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D30" t="s">
         <v>136</v>
@@ -5270,7 +5090,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5302,22 +5122,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920280</v>
+        <v>20330051920202</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G2">
         <v>-1</v>
@@ -5325,22 +5145,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920280</v>
+        <v>20330051920202</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G3">
         <v>-1</v>
@@ -5348,22 +5168,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920202</v>
+        <v>20330051920214</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G4">
         <v>-1</v>
@@ -5371,22 +5191,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920202</v>
+        <v>20330051920214</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D5" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G5">
         <v>-1</v>
@@ -5394,16 +5214,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920206</v>
+        <v>20330051920190</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -5417,22 +5237,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920206</v>
+        <v>20330051920191</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D7" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G7">
         <v>-1</v>
@@ -5440,16 +5260,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920209</v>
+        <v>20330051920193</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="D8" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -5463,22 +5283,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920209</v>
+        <v>20330051920196</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G9">
         <v>-1</v>
@@ -5486,16 +5306,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920213</v>
+        <v>20330051920198</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
@@ -5509,22 +5329,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920213</v>
+        <v>20330051920199</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="D11" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G11">
         <v>-1</v>
@@ -5532,22 +5352,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920177</v>
+        <v>20330051920200</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="D12" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G12">
         <v>-1</v>
@@ -5555,22 +5375,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920177</v>
+        <v>20330051920201</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="C13" t="s">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="D13" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G13">
         <v>-1</v>
@@ -5578,16 +5398,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920217</v>
+        <v>19330051920280</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="D14" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="E14" t="s">
         <v>7</v>
@@ -5601,22 +5421,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920217</v>
+        <v>20330051920206</v>
       </c>
       <c r="B15" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="D15" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G15">
         <v>-1</v>
@@ -5624,16 +5444,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920190</v>
+        <v>20330051920208</v>
       </c>
       <c r="B16" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="D16" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="E16" t="s">
         <v>7</v>
@@ -5647,16 +5467,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920191</v>
+        <v>19330051920290</v>
       </c>
       <c r="B17" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="C17" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D17" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="E17" t="s">
         <v>7</v>
@@ -5670,16 +5490,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920193</v>
+        <v>20330051920209</v>
       </c>
       <c r="B18" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="C18" t="s">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="D18" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="E18" t="s">
         <v>7</v>
@@ -5693,16 +5513,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920196</v>
+        <v>20330051920210</v>
       </c>
       <c r="B19" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C19" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D19" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="E19" t="s">
         <v>7</v>
@@ -5716,22 +5536,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920197</v>
+        <v>20330051920212</v>
       </c>
       <c r="B20" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="C20" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="D20" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="E20" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G20">
         <v>-1</v>
@@ -5739,16 +5559,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20330051920198</v>
+        <v>20330051920213</v>
       </c>
       <c r="B21" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="C21" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="D21" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="E21" t="s">
         <v>7</v>
@@ -5762,16 +5582,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>20330051920199</v>
+        <v>20330051920215</v>
       </c>
       <c r="B22" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="C22" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="D22" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="E22" t="s">
         <v>7</v>
@@ -5785,22 +5605,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>20330051920200</v>
+        <v>19330051920177</v>
       </c>
       <c r="B23" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="C23" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D23" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="E23" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F23" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G23">
         <v>-1</v>
@@ -5808,16 +5628,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>20330051920201</v>
+        <v>20330051920217</v>
       </c>
       <c r="B24" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="C24" t="s">
-        <v>71</v>
+        <v>101</v>
       </c>
       <c r="D24" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="E24" t="s">
         <v>7</v>
@@ -5826,121 +5646,6 @@
         <v>51</v>
       </c>
       <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>20330051920208</v>
-      </c>
-      <c r="B25" t="s">
-        <v>77</v>
-      </c>
-      <c r="C25" t="s">
-        <v>97</v>
-      </c>
-      <c r="D25" t="s">
-        <v>120</v>
-      </c>
-      <c r="E25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" t="s">
-        <v>51</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>19330051920290</v>
-      </c>
-      <c r="B26" t="s">
-        <v>78</v>
-      </c>
-      <c r="C26" t="s">
-        <v>98</v>
-      </c>
-      <c r="D26" t="s">
-        <v>121</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
-        <v>51</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>20330051920210</v>
-      </c>
-      <c r="B27" t="s">
-        <v>80</v>
-      </c>
-      <c r="C27" t="s">
-        <v>85</v>
-      </c>
-      <c r="D27" t="s">
-        <v>123</v>
-      </c>
-      <c r="E27" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" t="s">
-        <v>51</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>20330051920212</v>
-      </c>
-      <c r="B28" t="s">
-        <v>81</v>
-      </c>
-      <c r="C28" t="s">
-        <v>100</v>
-      </c>
-      <c r="D28" t="s">
-        <v>124</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" t="s">
-        <v>51</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>20330051920215</v>
-      </c>
-      <c r="B29" t="s">
-        <v>83</v>
-      </c>
-      <c r="C29" t="s">
-        <v>72</v>
-      </c>
-      <c r="D29" t="s">
-        <v>127</v>
-      </c>
-      <c r="E29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" t="s">
-        <v>51</v>
-      </c>
-      <c r="G29">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/4ALCV - Estadisticos 20212.xlsx
+++ b/grupos/4ALCV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="140">
   <si>
     <t>Materia</t>
   </si>
@@ -146,6 +146,9 @@
     <t>VELAZQUEZ GALEOTE EMILY</t>
   </si>
   <si>
+    <t>XOTLANIHUA XOTLANIHUA JESUS URIEL</t>
+  </si>
+  <si>
     <t>Docente</t>
   </si>
   <si>
@@ -173,18 +176,18 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Ángel Martínez Noe Cristobal</t>
+  </si>
+  <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
+    <t>Flores Ovalle Victor</t>
+  </si>
+  <si>
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
-    <t>Flores Ovalle Victor</t>
-  </si>
-  <si>
-    <t>Ángel Martínez Noe Cristobal</t>
-  </si>
-  <si>
     <t>Martínez Castillo Columba</t>
   </si>
   <si>
@@ -206,21 +209,87 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CHICO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>DE LA TEJA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>SALGADO</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>OLIVERA</t>
+  </si>
+  <si>
+    <t>DAMIEN</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>KITZIA YAMILET</t>
+  </si>
+  <si>
+    <t>ROBERTO JESUS</t>
+  </si>
+  <si>
+    <t>ITZEL</t>
+  </si>
+  <si>
+    <t>CRISTHIAN</t>
+  </si>
+  <si>
+    <t>VICTOR MANUEL</t>
+  </si>
+  <si>
+    <t>ALEJANDRA</t>
+  </si>
+  <si>
+    <t>ALISSON FERNANDA</t>
+  </si>
+  <si>
     <t>ASCENCION</t>
   </si>
   <si>
     <t>ARIAS</t>
   </si>
   <si>
+    <t>BALTAZARES</t>
+  </si>
+  <si>
     <t>CARRERA</t>
   </si>
   <si>
-    <t>CHICO</t>
-  </si>
-  <si>
     <t>ESTEVEZ</t>
   </si>
   <si>
+    <t>ESPERON</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
@@ -233,21 +302,9 @@
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
     <t>MELENDEZ</t>
   </si>
   <si>
-    <t>MORALES</t>
-  </si>
-  <si>
     <t>MUÑOZ</t>
   </si>
   <si>
@@ -266,24 +323,24 @@
     <t>ROMERO</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>DE LA TEJA</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
   </si>
   <si>
     <t>BARRAGAN</t>
   </si>
   <si>
-    <t>CRUZ</t>
+    <t>CONTRERAS</t>
   </si>
   <si>
     <t>MORENO</t>
   </si>
   <si>
+    <t>MORA</t>
+  </si>
+  <si>
     <t>ROQUE</t>
   </si>
   <si>
@@ -296,15 +353,6 @@
     <t>TREJO</t>
   </si>
   <si>
-    <t>SALGADO</t>
-  </si>
-  <si>
-    <t>OLIVERA</t>
-  </si>
-  <si>
-    <t>DAMIEN</t>
-  </si>
-  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
@@ -314,33 +362,33 @@
     <t>MEJIA</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
     <t>ZACARIAS</t>
   </si>
   <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
     <t>SOLIS</t>
   </si>
   <si>
+    <t>GALEOTE</t>
+  </si>
+  <si>
     <t>REYNA ARISBETH</t>
   </si>
   <si>
     <t>ANALI</t>
   </si>
   <si>
+    <t>JOCELYN</t>
+  </si>
+  <si>
     <t>DULCE FERNANDA</t>
   </si>
   <si>
-    <t>KITZIA YAMILET</t>
-  </si>
-  <si>
     <t>ERICK DE JESUS</t>
   </si>
   <si>
+    <t>MIA VALENTINA</t>
+  </si>
+  <si>
     <t>AMARELY GUADALUPE</t>
   </si>
   <si>
@@ -356,21 +404,9 @@
     <t>MILAGROS</t>
   </si>
   <si>
-    <t>ROBERTO JESUS</t>
-  </si>
-  <si>
-    <t>ITZEL</t>
-  </si>
-  <si>
-    <t>CRISTHIAN</t>
-  </si>
-  <si>
     <t>MARITZA JULIANA</t>
   </si>
   <si>
-    <t>VICTOR MANUEL</t>
-  </si>
-  <si>
     <t>LESLIE</t>
   </si>
   <si>
@@ -389,9 +425,6 @@
     <t>SUSANA</t>
   </si>
   <si>
-    <t>ALEJANDRA</t>
-  </si>
-  <si>
     <t>AMADA ARELY</t>
   </si>
   <si>
@@ -401,34 +434,10 @@
     <t>LUIS DIEGO</t>
   </si>
   <si>
-    <t>ALISSON FERNANDA</t>
-  </si>
-  <si>
-    <t>BALTAZARES</t>
-  </si>
-  <si>
-    <t>ESPERON</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>JOCELYN</t>
-  </si>
-  <si>
-    <t>MIA VALENTINA</t>
-  </si>
-  <si>
     <t>EMILY</t>
+  </si>
+  <si>
+    <t>JESUS URIEL</t>
   </si>
 </sst>
 </file>
@@ -786,7 +795,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC32"/>
+  <dimension ref="A1:AC33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -936,7 +945,7 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E4">
         <v>8</v>
@@ -954,16 +963,16 @@
         <v>-1</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L4">
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -999,13 +1008,13 @@
         <v>6</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z4">
         <v>8</v>
       </c>
       <c r="AA4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB4">
         <v>7</v>
@@ -1025,7 +1034,7 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E5">
         <v>7</v>
@@ -1043,16 +1052,16 @@
         <v>-1</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L5">
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1088,13 +1097,13 @@
         <v>7</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z5">
         <v>7</v>
       </c>
       <c r="AA5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB5">
         <v>7</v>
@@ -1132,16 +1141,16 @@
         <v>-1</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L6">
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1177,7 +1186,7 @@
         <v>9</v>
       </c>
       <c r="Y6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z6">
         <v>9</v>
@@ -1203,7 +1212,7 @@
         <v>6</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E7">
         <v>8</v>
@@ -1221,16 +1230,16 @@
         <v>-1</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L7">
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1266,13 +1275,13 @@
         <v>6</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z7">
         <v>8</v>
       </c>
       <c r="AA7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB7">
         <v>7</v>
@@ -1292,7 +1301,7 @@
         <v>-1</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E8">
         <v>5</v>
@@ -1313,13 +1322,13 @@
         <v>-1</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L8">
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1355,7 +1364,7 @@
         <v>-1</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z8">
         <v>5</v>
@@ -1381,7 +1390,7 @@
         <v>9</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -1399,7 +1408,7 @@
         <v>-1</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K9">
         <v>-1</v>
@@ -1408,7 +1417,7 @@
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1444,7 +1453,7 @@
         <v>9</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z9">
         <v>8</v>
@@ -1470,7 +1479,7 @@
         <v>-1</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E10">
         <v>6</v>
@@ -1491,13 +1500,13 @@
         <v>-1</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1533,7 +1542,7 @@
         <v>-1</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z10">
         <v>6</v>
@@ -1559,7 +1568,7 @@
         <v>7</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E11">
         <v>7</v>
@@ -1577,7 +1586,7 @@
         <v>-1</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K11">
         <v>-1</v>
@@ -1586,7 +1595,7 @@
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1622,7 +1631,7 @@
         <v>7</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z11">
         <v>7</v>
@@ -1666,16 +1675,16 @@
         <v>-1</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L12">
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1708,10 +1717,10 @@
         <v>9</v>
       </c>
       <c r="X12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z12">
         <v>9</v>
@@ -1737,7 +1746,7 @@
         <v>9</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E13">
         <v>6</v>
@@ -1755,16 +1764,16 @@
         <v>-1</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L13">
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1800,7 +1809,7 @@
         <v>9</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z13">
         <v>6</v>
@@ -1826,7 +1835,7 @@
         <v>10</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E14">
         <v>9</v>
@@ -1847,13 +1856,13 @@
         <v>-1</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L14">
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1889,13 +1898,13 @@
         <v>10</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z14">
         <v>9</v>
       </c>
       <c r="AA14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB14">
         <v>10</v>
@@ -1915,7 +1924,7 @@
         <v>10</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E15">
         <v>10</v>
@@ -1933,16 +1942,16 @@
         <v>-1</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L15">
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1975,10 +1984,10 @@
         <v>10</v>
       </c>
       <c r="X15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z15">
         <v>10</v>
@@ -2004,7 +2013,7 @@
         <v>9</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E16">
         <v>8</v>
@@ -2025,13 +2034,13 @@
         <v>-1</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L16">
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -2067,13 +2076,13 @@
         <v>9</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z16">
         <v>8</v>
       </c>
       <c r="AA16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB16">
         <v>7</v>
@@ -2093,7 +2102,7 @@
         <v>10</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E17">
         <v>8</v>
@@ -2111,7 +2120,7 @@
         <v>-1</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K17">
         <v>-1</v>
@@ -2120,7 +2129,7 @@
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2156,7 +2165,7 @@
         <v>10</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z17">
         <v>8</v>
@@ -2182,7 +2191,7 @@
         <v>9</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E18">
         <v>10</v>
@@ -2200,16 +2209,16 @@
         <v>-1</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L18">
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2242,10 +2251,10 @@
         <v>10</v>
       </c>
       <c r="X18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z18">
         <v>10</v>
@@ -2268,7 +2277,7 @@
         <v>-1</v>
       </c>
       <c r="F19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G19">
         <v>-1</v>
@@ -2280,7 +2289,7 @@
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2304,7 +2313,7 @@
         <v>-1</v>
       </c>
       <c r="AA19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB19">
         <v>-1</v>
@@ -2324,7 +2333,7 @@
         <v>10</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E20">
         <v>10</v>
@@ -2342,16 +2351,16 @@
         <v>-1</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L20">
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2387,13 +2396,13 @@
         <v>10</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z20">
         <v>10</v>
       </c>
       <c r="AA20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB20">
         <v>8</v>
@@ -2413,7 +2422,7 @@
         <v>6</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E21">
         <v>5</v>
@@ -2434,13 +2443,13 @@
         <v>-1</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L21">
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2476,7 +2485,7 @@
         <v>6</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Z21">
         <v>5</v>
@@ -2502,7 +2511,7 @@
         <v>8</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E22">
         <v>9</v>
@@ -2520,16 +2529,16 @@
         <v>-1</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2565,7 +2574,7 @@
         <v>8</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z22">
         <v>9</v>
@@ -2591,7 +2600,7 @@
         <v>10</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E23">
         <v>9</v>
@@ -2609,16 +2618,16 @@
         <v>-1</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L23">
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2654,13 +2663,13 @@
         <v>10</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z23">
         <v>9</v>
       </c>
       <c r="AA23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB23">
         <v>8</v>
@@ -2680,7 +2689,7 @@
         <v>10</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E24">
         <v>10</v>
@@ -2698,16 +2707,16 @@
         <v>-1</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2743,7 +2752,7 @@
         <v>10</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z24">
         <v>10</v>
@@ -2769,7 +2778,7 @@
         <v>6</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E25">
         <v>8</v>
@@ -2787,16 +2796,16 @@
         <v>-1</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L25">
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2829,10 +2838,10 @@
         <v>8</v>
       </c>
       <c r="X25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z25">
         <v>8</v>
@@ -2858,7 +2867,7 @@
         <v>10</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E26">
         <v>9</v>
@@ -2876,16 +2885,16 @@
         <v>-1</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L26">
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2921,13 +2930,13 @@
         <v>10</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z26">
         <v>9</v>
       </c>
       <c r="AA26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB26">
         <v>7</v>
@@ -2947,7 +2956,7 @@
         <v>8</v>
       </c>
       <c r="D27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E27">
         <v>9</v>
@@ -2965,16 +2974,16 @@
         <v>-1</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L27">
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -3007,16 +3016,16 @@
         <v>7</v>
       </c>
       <c r="X27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z27">
         <v>9</v>
       </c>
       <c r="AA27">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB27">
         <v>7</v>
@@ -3036,7 +3045,7 @@
         <v>9</v>
       </c>
       <c r="D28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E28">
         <v>9</v>
@@ -3054,16 +3063,16 @@
         <v>-1</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L28">
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -3099,13 +3108,13 @@
         <v>9</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z28">
         <v>9</v>
       </c>
       <c r="AA28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB28">
         <v>8</v>
@@ -3125,7 +3134,7 @@
         <v>7</v>
       </c>
       <c r="D29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E29">
         <v>6</v>
@@ -3143,16 +3152,16 @@
         <v>-1</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L29">
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -3188,13 +3197,13 @@
         <v>7</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z29">
         <v>6</v>
       </c>
       <c r="AA29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB29">
         <v>-1</v>
@@ -3208,7 +3217,7 @@
         <v>39</v>
       </c>
       <c r="B30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C30">
         <v>6</v>
@@ -3232,16 +3241,16 @@
         <v>-1</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L30">
         <v>-1</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3271,7 +3280,7 @@
         <v>-1</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X30">
         <v>6</v>
@@ -3283,7 +3292,7 @@
         <v>8</v>
       </c>
       <c r="AA30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AB30">
         <v>7</v>
@@ -3303,7 +3312,7 @@
         <v>8</v>
       </c>
       <c r="D31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E31">
         <v>8</v>
@@ -3321,16 +3330,16 @@
         <v>-1</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L31">
         <v>-1</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3363,10 +3372,10 @@
         <v>7</v>
       </c>
       <c r="X31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z31">
         <v>8</v>
@@ -3410,16 +3419,16 @@
         <v>-1</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L32">
         <v>-1</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3455,7 +3464,7 @@
         <v>10</v>
       </c>
       <c r="Y32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z32">
         <v>9</v>
@@ -3468,6 +3477,95 @@
       </c>
       <c r="AC32">
         <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:29">
+      <c r="A33" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33">
+        <v>5</v>
+      </c>
+      <c r="C33">
+        <v>5</v>
+      </c>
+      <c r="D33">
+        <v>6</v>
+      </c>
+      <c r="E33">
+        <v>6</v>
+      </c>
+      <c r="F33">
+        <v>5</v>
+      </c>
+      <c r="G33">
+        <v>6</v>
+      </c>
+      <c r="H33">
+        <v>5</v>
+      </c>
+      <c r="I33">
+        <v>-1</v>
+      </c>
+      <c r="J33">
+        <v>9</v>
+      </c>
+      <c r="K33">
+        <v>7</v>
+      </c>
+      <c r="L33">
+        <v>-1</v>
+      </c>
+      <c r="M33">
+        <v>7</v>
+      </c>
+      <c r="N33">
+        <v>-1</v>
+      </c>
+      <c r="O33">
+        <v>-1</v>
+      </c>
+      <c r="P33">
+        <v>-1</v>
+      </c>
+      <c r="Q33">
+        <v>-1</v>
+      </c>
+      <c r="R33">
+        <v>-1</v>
+      </c>
+      <c r="S33">
+        <v>-1</v>
+      </c>
+      <c r="T33">
+        <v>-1</v>
+      </c>
+      <c r="U33">
+        <v>-1</v>
+      </c>
+      <c r="V33">
+        <v>-1</v>
+      </c>
+      <c r="W33">
+        <v>5</v>
+      </c>
+      <c r="X33">
+        <v>7</v>
+      </c>
+      <c r="Y33">
+        <v>7</v>
+      </c>
+      <c r="Z33">
+        <v>6</v>
+      </c>
+      <c r="AA33">
+        <v>6</v>
+      </c>
+      <c r="AB33">
+        <v>6</v>
+      </c>
+      <c r="AC33">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3494,63 +3592,63 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="E2">
+        <v>6</v>
+      </c>
+      <c r="F2">
+        <v>80</v>
+      </c>
+      <c r="G2">
+        <v>20</v>
+      </c>
+      <c r="H2">
+        <v>7.9</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="F2">
-        <v>14.29</v>
-      </c>
-      <c r="G2">
+      <c r="J2">
         <v>0</v>
-      </c>
-      <c r="H2">
-        <v>6.8</v>
-      </c>
-      <c r="I2">
-        <v>24</v>
-      </c>
-      <c r="J2">
-        <v>85.70999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3558,31 +3656,31 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>82.14</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="H3">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="I3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J3">
-        <v>17.86</v>
+        <v>13.79</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3590,63 +3688,63 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C4">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>82.76000000000001</v>
+        <v>83.33</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="I4">
         <v>5</v>
       </c>
       <c r="J4">
-        <v>17.24</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C5">
         <v>29</v>
       </c>
       <c r="D5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
       <c r="F5">
-        <v>82.76000000000001</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="G5">
         <v>13.79</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>3.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3654,19 +3752,19 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>89.66</v>
+        <v>90</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -3678,7 +3776,7 @@
         <v>3</v>
       </c>
       <c r="J6">
-        <v>10.34</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3686,25 +3784,25 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E7">
         <v>2</v>
       </c>
       <c r="F7">
-        <v>92.86</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="G7">
-        <v>7.14</v>
+        <v>6.9</v>
       </c>
       <c r="H7">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3718,31 +3816,31 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D8">
         <v>28</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8">
-        <v>96.55</v>
+        <v>93.33</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="H8">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I8">
         <v>1</v>
       </c>
       <c r="J8">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
     </row>
   </sheetData>
@@ -3752,7 +3850,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3761,16 +3859,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -3781,139 +3879,139 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>20330051920190</v>
+        <v>20330051920194</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920191</v>
+        <v>20330051920194</v>
       </c>
       <c r="B3" t="s">
         <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920193</v>
+        <v>20330051920194</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>104</v>
+        <v>77</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920194</v>
+        <v>19330051920420</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920194</v>
+        <v>19330051920420</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920194</v>
+        <v>19330051920420</v>
       </c>
       <c r="B7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920194</v>
+        <v>20330051920202</v>
       </c>
       <c r="B8" t="s">
         <v>65</v>
       </c>
       <c r="C8" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
         <v>53</v>
@@ -3921,642 +4019,122 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920196</v>
+        <v>20330051920204</v>
       </c>
       <c r="B9" t="s">
         <v>66</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="D9" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920198</v>
+        <v>20330051920204</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="D10" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920199</v>
+        <v>20330051920207</v>
       </c>
       <c r="B11" t="s">
         <v>67</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="D11" t="s">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920200</v>
+        <v>20330051920207</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="D12" t="s">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920201</v>
+        <v>20330051920214</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C13" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D13" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>19330051920280</v>
+        <v>20330051920218</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C14" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="D14" t="s">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>19330051920420</v>
-      </c>
-      <c r="B15" t="s">
-        <v>71</v>
-      </c>
-      <c r="C15" t="s">
-        <v>92</v>
-      </c>
-      <c r="D15" t="s">
-        <v>112</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>19330051920420</v>
-      </c>
-      <c r="B16" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" t="s">
-        <v>92</v>
-      </c>
-      <c r="D16" t="s">
-        <v>112</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
         <v>53</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>19330051920420</v>
-      </c>
-      <c r="B17" t="s">
-        <v>71</v>
-      </c>
-      <c r="C17" t="s">
-        <v>92</v>
-      </c>
-      <c r="D17" t="s">
-        <v>112</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>19330051920420</v>
-      </c>
-      <c r="B18" t="s">
-        <v>71</v>
-      </c>
-      <c r="C18" t="s">
-        <v>92</v>
-      </c>
-      <c r="D18" t="s">
-        <v>112</v>
-      </c>
-      <c r="E18" t="s">
-        <v>11</v>
-      </c>
-      <c r="F18" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>20330051920202</v>
-      </c>
-      <c r="B19" t="s">
-        <v>72</v>
-      </c>
-      <c r="C19" t="s">
-        <v>84</v>
-      </c>
-      <c r="D19" t="s">
-        <v>113</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>20330051920202</v>
-      </c>
-      <c r="B20" t="s">
-        <v>72</v>
-      </c>
-      <c r="C20" t="s">
-        <v>84</v>
-      </c>
-      <c r="D20" t="s">
-        <v>113</v>
-      </c>
-      <c r="E20" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>20330051920204</v>
-      </c>
-      <c r="B21" t="s">
-        <v>73</v>
-      </c>
-      <c r="C21" t="s">
-        <v>93</v>
-      </c>
-      <c r="D21" t="s">
-        <v>114</v>
-      </c>
-      <c r="E21" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>20330051920204</v>
-      </c>
-      <c r="B22" t="s">
-        <v>73</v>
-      </c>
-      <c r="C22" t="s">
-        <v>93</v>
-      </c>
-      <c r="D22" t="s">
-        <v>114</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>20330051920204</v>
-      </c>
-      <c r="B23" t="s">
-        <v>73</v>
-      </c>
-      <c r="C23" t="s">
-        <v>93</v>
-      </c>
-      <c r="D23" t="s">
-        <v>114</v>
-      </c>
-      <c r="E23" t="s">
-        <v>10</v>
-      </c>
-      <c r="F23" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>20330051920206</v>
-      </c>
-      <c r="B24" t="s">
-        <v>74</v>
-      </c>
-      <c r="C24" t="s">
-        <v>81</v>
-      </c>
-      <c r="D24" t="s">
-        <v>115</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>20330051920207</v>
-      </c>
-      <c r="B25" t="s">
-        <v>75</v>
-      </c>
-      <c r="C25" t="s">
-        <v>94</v>
-      </c>
-      <c r="D25" t="s">
-        <v>116</v>
-      </c>
-      <c r="E25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>20330051920207</v>
-      </c>
-      <c r="B26" t="s">
-        <v>75</v>
-      </c>
-      <c r="C26" t="s">
-        <v>94</v>
-      </c>
-      <c r="D26" t="s">
-        <v>116</v>
-      </c>
-      <c r="E26" t="s">
-        <v>5</v>
-      </c>
-      <c r="F26" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>20330051920207</v>
-      </c>
-      <c r="B27" t="s">
-        <v>75</v>
-      </c>
-      <c r="C27" t="s">
-        <v>94</v>
-      </c>
-      <c r="D27" t="s">
-        <v>116</v>
-      </c>
-      <c r="E27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>20330051920208</v>
-      </c>
-      <c r="B28" t="s">
-        <v>76</v>
-      </c>
-      <c r="C28" t="s">
-        <v>95</v>
-      </c>
-      <c r="D28" t="s">
-        <v>117</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>19330051920290</v>
-      </c>
-      <c r="B29" t="s">
-        <v>77</v>
-      </c>
-      <c r="C29" t="s">
-        <v>96</v>
-      </c>
-      <c r="D29" t="s">
-        <v>118</v>
-      </c>
-      <c r="E29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>20330051920209</v>
-      </c>
-      <c r="B30" t="s">
-        <v>78</v>
-      </c>
-      <c r="C30" t="s">
-        <v>97</v>
-      </c>
-      <c r="D30" t="s">
-        <v>119</v>
-      </c>
-      <c r="E30" t="s">
-        <v>7</v>
-      </c>
-      <c r="F30" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>20330051920210</v>
-      </c>
-      <c r="B31" t="s">
-        <v>79</v>
-      </c>
-      <c r="C31" t="s">
-        <v>84</v>
-      </c>
-      <c r="D31" t="s">
-        <v>120</v>
-      </c>
-      <c r="E31" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>20330051920212</v>
-      </c>
-      <c r="B32" t="s">
-        <v>80</v>
-      </c>
-      <c r="C32" t="s">
-        <v>98</v>
-      </c>
-      <c r="D32" t="s">
-        <v>121</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>20330051920213</v>
-      </c>
-      <c r="B33" t="s">
-        <v>81</v>
-      </c>
-      <c r="C33" t="s">
-        <v>99</v>
-      </c>
-      <c r="D33" t="s">
-        <v>122</v>
-      </c>
-      <c r="E33" t="s">
-        <v>7</v>
-      </c>
-      <c r="F33" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>20330051920214</v>
-      </c>
-      <c r="B34" t="s">
-        <v>82</v>
-      </c>
-      <c r="C34" t="s">
-        <v>100</v>
-      </c>
-      <c r="D34" t="s">
-        <v>123</v>
-      </c>
-      <c r="E34" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>20330051920214</v>
-      </c>
-      <c r="B35" t="s">
-        <v>82</v>
-      </c>
-      <c r="C35" t="s">
-        <v>100</v>
-      </c>
-      <c r="D35" t="s">
-        <v>123</v>
-      </c>
-      <c r="E35" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>20330051920215</v>
-      </c>
-      <c r="B36" t="s">
-        <v>82</v>
-      </c>
-      <c r="C36" t="s">
-        <v>71</v>
-      </c>
-      <c r="D36" t="s">
-        <v>124</v>
-      </c>
-      <c r="E36" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>19330051920177</v>
-      </c>
-      <c r="B37" t="s">
-        <v>82</v>
-      </c>
-      <c r="C37" t="s">
-        <v>95</v>
-      </c>
-      <c r="D37" t="s">
-        <v>125</v>
-      </c>
-      <c r="E37" t="s">
-        <v>5</v>
-      </c>
-      <c r="F37" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>20330051920217</v>
-      </c>
-      <c r="B38" t="s">
-        <v>82</v>
-      </c>
-      <c r="C38" t="s">
-        <v>101</v>
-      </c>
-      <c r="D38" t="s">
-        <v>126</v>
-      </c>
-      <c r="E38" t="s">
-        <v>7</v>
-      </c>
-      <c r="F38" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>20330051920218</v>
-      </c>
-      <c r="B39" t="s">
-        <v>83</v>
-      </c>
-      <c r="C39" t="s">
-        <v>98</v>
-      </c>
-      <c r="D39" t="s">
-        <v>127</v>
-      </c>
-      <c r="E39" t="s">
-        <v>7</v>
-      </c>
-      <c r="F39" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>20330051920218</v>
-      </c>
-      <c r="B40" t="s">
-        <v>83</v>
-      </c>
-      <c r="C40" t="s">
-        <v>98</v>
-      </c>
-      <c r="D40" t="s">
-        <v>127</v>
-      </c>
-      <c r="E40" t="s">
-        <v>5</v>
-      </c>
-      <c r="F40" t="s">
-        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -4566,7 +4144,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4575,19 +4153,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -4595,16 +4173,16 @@
         <v>20330051920194</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4612,16 +4190,16 @@
         <v>19330051920420</v>
       </c>
       <c r="B3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" t="s">
         <v>71</v>
       </c>
-      <c r="C3" t="s">
-        <v>92</v>
-      </c>
       <c r="D3" t="s">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -4629,16 +4207,16 @@
         <v>20330051920204</v>
       </c>
       <c r="B4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" t="s">
         <v>73</v>
       </c>
-      <c r="C4" t="s">
-        <v>93</v>
-      </c>
       <c r="D4" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -4646,16 +4224,16 @@
         <v>20330051920207</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>116</v>
+        <v>81</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -4663,16 +4241,16 @@
         <v>20330051920202</v>
       </c>
       <c r="B6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" t="s">
         <v>72</v>
       </c>
-      <c r="C6" t="s">
-        <v>84</v>
-      </c>
       <c r="D6" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -4680,16 +4258,16 @@
         <v>20330051920214</v>
       </c>
       <c r="B7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D7" t="s">
         <v>82</v>
       </c>
-      <c r="C7" t="s">
-        <v>100</v>
-      </c>
-      <c r="D7" t="s">
-        <v>123</v>
-      </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -4697,16 +4275,16 @@
         <v>20330051920218</v>
       </c>
       <c r="B8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" t="s">
         <v>83</v>
       </c>
-      <c r="C8" t="s">
-        <v>98</v>
-      </c>
-      <c r="D8" t="s">
-        <v>127</v>
-      </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -4714,16 +4292,16 @@
         <v>20330051920190</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -4731,319 +4309,319 @@
         <v>20330051920191</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="D10" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920193</v>
+        <v>20330051920192</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>104</v>
       </c>
       <c r="D11" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920196</v>
+        <v>20330051920193</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D12" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920198</v>
+        <v>20330051920196</v>
       </c>
       <c r="B13" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="D13" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920199</v>
+        <v>20330051920197</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="C14" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="D14" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920200</v>
+        <v>20330051920198</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="C15" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="D15" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920201</v>
+        <v>20330051920199</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="C16" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
       <c r="D16" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920280</v>
+        <v>20330051920200</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="C17" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="D17" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920206</v>
+        <v>20330051920201</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C18" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="D18" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920208</v>
+        <v>19330051920280</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="C19" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="D19" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920290</v>
+        <v>20330051920206</v>
       </c>
       <c r="B20" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="C20" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D20" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920209</v>
+        <v>20330051920208</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="C21" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="D21" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920210</v>
+        <v>19330051920290</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="C22" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="D22" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="E22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920212</v>
+        <v>20330051920209</v>
       </c>
       <c r="B23" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="C23" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="D23" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920213</v>
+        <v>20330051920210</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="C24" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="D24" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920215</v>
+        <v>20330051920212</v>
       </c>
       <c r="B25" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="C25" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D25" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920177</v>
+        <v>20330051920213</v>
       </c>
       <c r="B26" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="C26" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="D26" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920217</v>
+        <v>20330051920215</v>
       </c>
       <c r="B27" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="C27" t="s">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="D27" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="E27">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920192</v>
+        <v>19330051920177</v>
       </c>
       <c r="B28" t="s">
-        <v>128</v>
+        <v>68</v>
       </c>
       <c r="C28" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="D28" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -5051,16 +4629,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920197</v>
+        <v>20330051920217</v>
       </c>
       <c r="B29" t="s">
-        <v>129</v>
+        <v>68</v>
       </c>
       <c r="C29" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="D29" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -5071,15 +4649,32 @@
         <v>20330051920219</v>
       </c>
       <c r="B30" t="s">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="C30" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="D30" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31">
+        <v>20330051920259</v>
+      </c>
+      <c r="B31" t="s">
+        <v>102</v>
+      </c>
+      <c r="C31" t="s">
+        <v>102</v>
+      </c>
+      <c r="D31" t="s">
+        <v>139</v>
+      </c>
+      <c r="E31">
         <v>0</v>
       </c>
     </row>
@@ -5090,7 +4685,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5099,22 +4694,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -5122,114 +4717,114 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920202</v>
+        <v>20330051920259</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="D2" t="s">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920202</v>
+        <v>20330051920259</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="D3" t="s">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920214</v>
+        <v>20330051920191</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D4" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920214</v>
+        <v>20330051920196</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920190</v>
+        <v>20330051920202</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G6">
         <v>-1</v>
@@ -5237,415 +4832,24 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920191</v>
+        <v>20330051920214</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="D7" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G7">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920193</v>
-      </c>
-      <c r="B8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C8" t="s">
-        <v>69</v>
-      </c>
-      <c r="D8" t="s">
-        <v>104</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>51</v>
-      </c>
-      <c r="G8">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920196</v>
-      </c>
-      <c r="B9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C9" t="s">
-        <v>87</v>
-      </c>
-      <c r="D9" t="s">
-        <v>106</v>
-      </c>
-      <c r="E9" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" t="s">
-        <v>51</v>
-      </c>
-      <c r="G9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920198</v>
-      </c>
-      <c r="B10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" t="s">
-        <v>88</v>
-      </c>
-      <c r="D10" t="s">
-        <v>107</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>51</v>
-      </c>
-      <c r="G10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920199</v>
-      </c>
-      <c r="B11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C11" t="s">
-        <v>89</v>
-      </c>
-      <c r="D11" t="s">
-        <v>108</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>51</v>
-      </c>
-      <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920200</v>
-      </c>
-      <c r="B12" t="s">
-        <v>68</v>
-      </c>
-      <c r="C12" t="s">
-        <v>90</v>
-      </c>
-      <c r="D12" t="s">
-        <v>109</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>51</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920201</v>
-      </c>
-      <c r="B13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" t="s">
-        <v>70</v>
-      </c>
-      <c r="D13" t="s">
-        <v>110</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>51</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>19330051920280</v>
-      </c>
-      <c r="B14" t="s">
-        <v>70</v>
-      </c>
-      <c r="C14" t="s">
-        <v>91</v>
-      </c>
-      <c r="D14" t="s">
-        <v>111</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>51</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920206</v>
-      </c>
-      <c r="B15" t="s">
-        <v>74</v>
-      </c>
-      <c r="C15" t="s">
-        <v>81</v>
-      </c>
-      <c r="D15" t="s">
-        <v>115</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>51</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>20330051920208</v>
-      </c>
-      <c r="B16" t="s">
-        <v>76</v>
-      </c>
-      <c r="C16" t="s">
-        <v>95</v>
-      </c>
-      <c r="D16" t="s">
-        <v>117</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>51</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>19330051920290</v>
-      </c>
-      <c r="B17" t="s">
-        <v>77</v>
-      </c>
-      <c r="C17" t="s">
-        <v>96</v>
-      </c>
-      <c r="D17" t="s">
-        <v>118</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>51</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>20330051920209</v>
-      </c>
-      <c r="B18" t="s">
-        <v>78</v>
-      </c>
-      <c r="C18" t="s">
-        <v>97</v>
-      </c>
-      <c r="D18" t="s">
-        <v>119</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>51</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>20330051920210</v>
-      </c>
-      <c r="B19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C19" t="s">
-        <v>84</v>
-      </c>
-      <c r="D19" t="s">
-        <v>120</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>51</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>20330051920212</v>
-      </c>
-      <c r="B20" t="s">
-        <v>80</v>
-      </c>
-      <c r="C20" t="s">
-        <v>98</v>
-      </c>
-      <c r="D20" t="s">
-        <v>121</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>51</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>20330051920213</v>
-      </c>
-      <c r="B21" t="s">
-        <v>81</v>
-      </c>
-      <c r="C21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D21" t="s">
-        <v>122</v>
-      </c>
-      <c r="E21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" t="s">
-        <v>51</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>20330051920215</v>
-      </c>
-      <c r="B22" t="s">
-        <v>82</v>
-      </c>
-      <c r="C22" t="s">
-        <v>71</v>
-      </c>
-      <c r="D22" t="s">
-        <v>124</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>51</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>19330051920177</v>
-      </c>
-      <c r="B23" t="s">
-        <v>82</v>
-      </c>
-      <c r="C23" t="s">
-        <v>95</v>
-      </c>
-      <c r="D23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E23" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" t="s">
-        <v>52</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>20330051920217</v>
-      </c>
-      <c r="B24" t="s">
-        <v>82</v>
-      </c>
-      <c r="C24" t="s">
-        <v>101</v>
-      </c>
-      <c r="D24" t="s">
-        <v>126</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" t="s">
-        <v>51</v>
-      </c>
-      <c r="G24">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/4ALCV - Estadisticos 20212.xlsx
+++ b/grupos/4ALCV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="140">
   <si>
     <t>Materia</t>
   </si>
@@ -179,18 +179,18 @@
     <t>Ángel Martínez Noe Cristobal</t>
   </si>
   <si>
+    <t>Polanco Domínguez Rosa María</t>
+  </si>
+  <si>
+    <t>Flores Ovalle Victor</t>
+  </si>
+  <si>
+    <t>Martínez Castillo Columba</t>
+  </si>
+  <si>
     <t>Muñoz Rivadeneyra Salvador</t>
   </si>
   <si>
-    <t>Flores Ovalle Victor</t>
-  </si>
-  <si>
-    <t>Polanco Domínguez Rosa María</t>
-  </si>
-  <si>
-    <t>Martínez Castillo Columba</t>
-  </si>
-  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
@@ -215,223 +215,223 @@
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>SALGADO</t>
+  </si>
+  <si>
+    <t>OLIVERA</t>
+  </si>
+  <si>
+    <t>KITZIA YAMILET</t>
+  </si>
+  <si>
+    <t>ROBERTO JESUS</t>
+  </si>
+  <si>
+    <t>CRISTHIAN</t>
+  </si>
+  <si>
+    <t>ASCENCION</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>BALTAZARES</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>ESPERON</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GALVEZ</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>DE LA LUZ</t>
+    <t>MELENDEZ</t>
   </si>
   <si>
     <t>MORALES</t>
   </si>
   <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>PEÑA</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
     <t>DE LA TEJA</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>SALGADO</t>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
   </si>
   <si>
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>OLIVERA</t>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>ROQUE</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>TREJO</t>
   </si>
   <si>
     <t>DAMIEN</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>MEJIA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
     <t>HUERTA</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>KITZIA YAMILET</t>
-  </si>
-  <si>
-    <t>ROBERTO JESUS</t>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>GALEOTE</t>
+  </si>
+  <si>
+    <t>REYNA ARISBETH</t>
+  </si>
+  <si>
+    <t>ANALI</t>
+  </si>
+  <si>
+    <t>JOCELYN</t>
+  </si>
+  <si>
+    <t>DULCE FERNANDA</t>
+  </si>
+  <si>
+    <t>ERICK DE JESUS</t>
+  </si>
+  <si>
+    <t>MIA VALENTINA</t>
+  </si>
+  <si>
+    <t>AMARELY GUADALUPE</t>
+  </si>
+  <si>
+    <t>FRIDA SOFIA</t>
+  </si>
+  <si>
+    <t>ANTONIO ABIDAN</t>
+  </si>
+  <si>
+    <t>YAMILET</t>
+  </si>
+  <si>
+    <t>MILAGROS</t>
   </si>
   <si>
     <t>ITZEL</t>
   </si>
   <si>
-    <t>CRISTHIAN</t>
+    <t>MARITZA JULIANA</t>
   </si>
   <si>
     <t>VICTOR MANUEL</t>
   </si>
   <si>
+    <t>LESLIE</t>
+  </si>
+  <si>
+    <t>HEIDY MARIAM</t>
+  </si>
+  <si>
+    <t>YEILI DAYNERIS</t>
+  </si>
+  <si>
+    <t>JULIO CESAR</t>
+  </si>
+  <si>
+    <t>INGRID SARAI</t>
+  </si>
+  <si>
+    <t>SUSANA</t>
+  </si>
+  <si>
     <t>ALEJANDRA</t>
   </si>
   <si>
+    <t>AMADA ARELY</t>
+  </si>
+  <si>
+    <t>JOSSELIN ANDREA</t>
+  </si>
+  <si>
+    <t>LUIS DIEGO</t>
+  </si>
+  <si>
     <t>ALISSON FERNANDA</t>
-  </si>
-  <si>
-    <t>ASCENCION</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>BALTAZARES</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>ESPERON</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GALVEZ</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MELENDEZ</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>PEÑA</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>ROQUE</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>MEJIA</t>
-  </si>
-  <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>REYNA ARISBETH</t>
-  </si>
-  <si>
-    <t>ANALI</t>
-  </si>
-  <si>
-    <t>JOCELYN</t>
-  </si>
-  <si>
-    <t>DULCE FERNANDA</t>
-  </si>
-  <si>
-    <t>ERICK DE JESUS</t>
-  </si>
-  <si>
-    <t>MIA VALENTINA</t>
-  </si>
-  <si>
-    <t>AMARELY GUADALUPE</t>
-  </si>
-  <si>
-    <t>FRIDA SOFIA</t>
-  </si>
-  <si>
-    <t>ANTONIO ABIDAN</t>
-  </si>
-  <si>
-    <t>YAMILET</t>
-  </si>
-  <si>
-    <t>MILAGROS</t>
-  </si>
-  <si>
-    <t>MARITZA JULIANA</t>
-  </si>
-  <si>
-    <t>LESLIE</t>
-  </si>
-  <si>
-    <t>HEIDY MARIAM</t>
-  </si>
-  <si>
-    <t>YEILI DAYNERIS</t>
-  </si>
-  <si>
-    <t>JULIO CESAR</t>
-  </si>
-  <si>
-    <t>INGRID SARAI</t>
-  </si>
-  <si>
-    <t>SUSANA</t>
-  </si>
-  <si>
-    <t>AMADA ARELY</t>
-  </si>
-  <si>
-    <t>JOSSELIN ANDREA</t>
-  </si>
-  <si>
-    <t>LUIS DIEGO</t>
   </si>
   <si>
     <t>EMILY</t>
@@ -960,7 +960,7 @@
         <v>8</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -978,7 +978,7 @@
         <v>-1</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -1002,7 +1002,7 @@
         <v>-1</v>
       </c>
       <c r="W4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X4">
         <v>6</v>
@@ -1020,7 +1020,7 @@
         <v>7</v>
       </c>
       <c r="AC4">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -1049,7 +1049,7 @@
         <v>9</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -1064,10 +1064,10 @@
         <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P5">
         <v>-1</v>
@@ -1091,7 +1091,7 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X5">
         <v>7</v>
@@ -1138,7 +1138,7 @@
         <v>9</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
         <v>9</v>
@@ -1153,10 +1153,10 @@
         <v>8</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -1198,7 +1198,7 @@
         <v>10</v>
       </c>
       <c r="AC6">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1227,7 +1227,7 @@
         <v>9</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J7">
         <v>6</v>
@@ -1242,10 +1242,10 @@
         <v>6</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1295,7 +1295,7 @@
         <v>17</v>
       </c>
       <c r="B8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C8">
         <v>-1</v>
@@ -1310,13 +1310,13 @@
         <v>5</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H8">
         <v>7</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J8">
         <v>-1</v>
@@ -1358,7 +1358,7 @@
         <v>-1</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X8">
         <v>-1</v>
@@ -1373,7 +1373,7 @@
         <v>5</v>
       </c>
       <c r="AB8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC8">
         <v>7</v>
@@ -1384,7 +1384,7 @@
         <v>18</v>
       </c>
       <c r="B9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="C9">
         <v>9</v>
@@ -1405,7 +1405,7 @@
         <v>7</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J9">
         <v>9</v>
@@ -1420,10 +1420,10 @@
         <v>10</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1447,7 +1447,7 @@
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X9">
         <v>9</v>
@@ -1488,13 +1488,13 @@
         <v>5</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H10">
         <v>6</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J10">
         <v>-1</v>
@@ -1512,7 +1512,7 @@
         <v>-1</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1536,7 +1536,7 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X10">
         <v>-1</v>
@@ -1551,7 +1551,7 @@
         <v>5</v>
       </c>
       <c r="AB10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AC10">
         <v>6</v>
@@ -1562,7 +1562,7 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="C11">
         <v>7</v>
@@ -1583,7 +1583,7 @@
         <v>6</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J11">
         <v>7</v>
@@ -1598,10 +1598,10 @@
         <v>5</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1625,7 +1625,7 @@
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X11">
         <v>7</v>
@@ -1643,7 +1643,7 @@
         <v>7</v>
       </c>
       <c r="AC11">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1672,7 +1672,7 @@
         <v>9</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J12">
         <v>10</v>
@@ -1687,10 +1687,10 @@
         <v>10</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1714,7 +1714,7 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X12">
         <v>10</v>
@@ -1732,7 +1732,7 @@
         <v>9</v>
       </c>
       <c r="AC12">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1761,7 +1761,7 @@
         <v>7</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J13">
         <v>8</v>
@@ -1776,10 +1776,10 @@
         <v>6</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1803,7 +1803,7 @@
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X13">
         <v>9</v>
@@ -1818,10 +1818,10 @@
         <v>6</v>
       </c>
       <c r="AB13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC13">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1850,7 +1850,7 @@
         <v>9</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J14">
         <v>-1</v>
@@ -1865,10 +1865,10 @@
         <v>6</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1892,7 +1892,7 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X14">
         <v>10</v>
@@ -1910,7 +1910,7 @@
         <v>10</v>
       </c>
       <c r="AC14">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1939,7 +1939,7 @@
         <v>9</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J15">
         <v>8</v>
@@ -1954,10 +1954,10 @@
         <v>9</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1981,7 +1981,7 @@
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X15">
         <v>9</v>
@@ -1996,10 +1996,10 @@
         <v>9</v>
       </c>
       <c r="AB15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC15">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -2028,7 +2028,7 @@
         <v>7</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J16">
         <v>-1</v>
@@ -2043,10 +2043,10 @@
         <v>5</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -2117,7 +2117,7 @@
         <v>7</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J17">
         <v>10</v>
@@ -2132,10 +2132,10 @@
         <v>8</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -2159,7 +2159,7 @@
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X17">
         <v>10</v>
@@ -2174,10 +2174,10 @@
         <v>8</v>
       </c>
       <c r="AB17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC17">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2206,7 +2206,7 @@
         <v>10</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J18">
         <v>10</v>
@@ -2221,10 +2221,10 @@
         <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2280,10 +2280,10 @@
         <v>5</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
         <v>-1</v>
@@ -2316,10 +2316,10 @@
         <v>5</v>
       </c>
       <c r="AB19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC19">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2348,7 +2348,7 @@
         <v>9</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J20">
         <v>10</v>
@@ -2363,10 +2363,10 @@
         <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2390,7 +2390,7 @@
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X20">
         <v>10</v>
@@ -2405,10 +2405,10 @@
         <v>10</v>
       </c>
       <c r="AB20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC20">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2416,7 +2416,7 @@
         <v>30</v>
       </c>
       <c r="B21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="C21">
         <v>6</v>
@@ -2431,13 +2431,13 @@
         <v>5</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H21">
         <v>7</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J21">
         <v>-1</v>
@@ -2455,7 +2455,7 @@
         <v>-1</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2479,7 +2479,7 @@
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X21">
         <v>6</v>
@@ -2494,7 +2494,7 @@
         <v>5</v>
       </c>
       <c r="AB21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC21">
         <v>7</v>
@@ -2526,7 +2526,7 @@
         <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J22">
         <v>7</v>
@@ -2541,10 +2541,10 @@
         <v>9</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2568,7 +2568,7 @@
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X22">
         <v>8</v>
@@ -2615,7 +2615,7 @@
         <v>8</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J23">
         <v>10</v>
@@ -2630,10 +2630,10 @@
         <v>9</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2657,7 +2657,7 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X23">
         <v>10</v>
@@ -2675,7 +2675,7 @@
         <v>8</v>
       </c>
       <c r="AC23">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2704,7 +2704,7 @@
         <v>10</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J24">
         <v>10</v>
@@ -2719,10 +2719,10 @@
         <v>9</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2746,7 +2746,7 @@
         <v>-1</v>
       </c>
       <c r="W24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X24">
         <v>10</v>
@@ -2761,7 +2761,7 @@
         <v>9</v>
       </c>
       <c r="AB24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC24">
         <v>10</v>
@@ -2793,7 +2793,7 @@
         <v>9</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J25">
         <v>10</v>
@@ -2808,10 +2808,10 @@
         <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P25">
         <v>-1</v>
@@ -2835,7 +2835,7 @@
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X25">
         <v>8</v>
@@ -2882,7 +2882,7 @@
         <v>8</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J26">
         <v>9</v>
@@ -2897,10 +2897,10 @@
         <v>9</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
         <v>-1</v>
@@ -2924,7 +2924,7 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X26">
         <v>10</v>
@@ -2939,10 +2939,10 @@
         <v>9</v>
       </c>
       <c r="AB26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC26">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:29">
@@ -2971,7 +2971,7 @@
         <v>9</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J27">
         <v>9</v>
@@ -2986,10 +2986,10 @@
         <v>9</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -3013,7 +3013,7 @@
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X27">
         <v>9</v>
@@ -3028,7 +3028,7 @@
         <v>8</v>
       </c>
       <c r="AB27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC27">
         <v>9</v>
@@ -3060,7 +3060,7 @@
         <v>10</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J28">
         <v>9</v>
@@ -3075,10 +3075,10 @@
         <v>8</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
         <v>-1</v>
@@ -3102,7 +3102,7 @@
         <v>-1</v>
       </c>
       <c r="W28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X28">
         <v>9</v>
@@ -3117,7 +3117,7 @@
         <v>9</v>
       </c>
       <c r="AB28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC28">
         <v>10</v>
@@ -3143,13 +3143,13 @@
         <v>7</v>
       </c>
       <c r="G29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H29">
         <v>9</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J29">
         <v>6</v>
@@ -3167,7 +3167,7 @@
         <v>-1</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P29">
         <v>-1</v>
@@ -3191,7 +3191,7 @@
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X29">
         <v>7</v>
@@ -3206,7 +3206,7 @@
         <v>6</v>
       </c>
       <c r="AB29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AC29">
         <v>9</v>
@@ -3238,7 +3238,7 @@
         <v>8</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J30">
         <v>6</v>
@@ -3253,7 +3253,7 @@
         <v>5</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O30">
         <v>-1</v>
@@ -3280,7 +3280,7 @@
         <v>-1</v>
       </c>
       <c r="W30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X30">
         <v>6</v>
@@ -3295,7 +3295,7 @@
         <v>8</v>
       </c>
       <c r="AB30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC30">
         <v>8</v>
@@ -3327,7 +3327,7 @@
         <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J31">
         <v>6</v>
@@ -3342,10 +3342,10 @@
         <v>8</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P31">
         <v>-1</v>
@@ -3387,7 +3387,7 @@
         <v>7</v>
       </c>
       <c r="AC31">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -3416,7 +3416,7 @@
         <v>10</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J32">
         <v>10</v>
@@ -3431,10 +3431,10 @@
         <v>10</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P32">
         <v>-1</v>
@@ -3505,7 +3505,7 @@
         <v>5</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J33">
         <v>9</v>
@@ -3523,7 +3523,7 @@
         <v>-1</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P33">
         <v>-1</v>
@@ -3565,7 +3565,7 @@
         <v>6</v>
       </c>
       <c r="AC33">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3653,7 +3653,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>53</v>
@@ -3662,25 +3662,25 @@
         <v>29</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>82.76000000000001</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="G3">
-        <v>3.45</v>
+        <v>13.79</v>
       </c>
       <c r="H3">
-        <v>8.6</v>
+        <v>6.8</v>
       </c>
       <c r="I3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>13.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3694,89 +3694,89 @@
         <v>30</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <v>86.67</v>
+      </c>
+      <c r="G4">
+        <v>13.33</v>
+      </c>
+      <c r="H4">
+        <v>7.6</v>
+      </c>
+      <c r="I4">
         <v>0</v>
       </c>
-      <c r="F4">
-        <v>83.33</v>
-      </c>
-      <c r="G4">
+      <c r="J4">
         <v>0</v>
-      </c>
-      <c r="H4">
-        <v>7.7</v>
-      </c>
-      <c r="I4">
-        <v>5</v>
-      </c>
-      <c r="J4">
-        <v>16.67</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>55</v>
       </c>
       <c r="C5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>86.20999999999999</v>
+        <v>90</v>
       </c>
       <c r="G5">
-        <v>13.79</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>56</v>
       </c>
       <c r="C6">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6">
         <v>27</v>
       </c>
       <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>93.09999999999999</v>
+      </c>
+      <c r="G6">
+        <v>6.9</v>
+      </c>
+      <c r="H6">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>90</v>
-      </c>
-      <c r="G6">
+      <c r="J6">
         <v>0</v>
-      </c>
-      <c r="H6">
-        <v>8.4</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
-      </c>
-      <c r="J6">
-        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3822,25 +3822,25 @@
         <v>30</v>
       </c>
       <c r="D8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E8">
         <v>1</v>
       </c>
       <c r="F8">
-        <v>93.33</v>
+        <v>96.67</v>
       </c>
       <c r="G8">
         <v>3.33</v>
       </c>
       <c r="H8">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>3.33</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3850,7 +3850,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3885,256 +3885,56 @@
         <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920194</v>
+        <v>19330051920420</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" t="s">
         <v>70</v>
       </c>
-      <c r="D3" t="s">
-        <v>77</v>
-      </c>
       <c r="E3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920194</v>
+        <v>20330051920204</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>19330051920420</v>
-      </c>
-      <c r="B5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>19330051920420</v>
-      </c>
-      <c r="B6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D6" t="s">
-        <v>78</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>19330051920420</v>
-      </c>
-      <c r="B7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D7" t="s">
-        <v>78</v>
-      </c>
-      <c r="E7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>20330051920202</v>
-      </c>
-      <c r="B8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" t="s">
-        <v>72</v>
-      </c>
-      <c r="D8" t="s">
-        <v>79</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920204</v>
-      </c>
-      <c r="B9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C9" t="s">
-        <v>73</v>
-      </c>
-      <c r="D9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920204</v>
-      </c>
-      <c r="B10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" t="s">
-        <v>73</v>
-      </c>
-      <c r="D10" t="s">
-        <v>80</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>20330051920207</v>
-      </c>
-      <c r="B11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C11" t="s">
-        <v>74</v>
-      </c>
-      <c r="D11" t="s">
-        <v>81</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920207</v>
-      </c>
-      <c r="B12" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" t="s">
-        <v>74</v>
-      </c>
-      <c r="D12" t="s">
-        <v>81</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>20330051920214</v>
-      </c>
-      <c r="B13" t="s">
-        <v>68</v>
-      </c>
-      <c r="C13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D13" t="s">
-        <v>82</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>20330051920218</v>
-      </c>
-      <c r="B14" t="s">
-        <v>69</v>
-      </c>
-      <c r="C14" t="s">
-        <v>76</v>
-      </c>
-      <c r="D14" t="s">
-        <v>83</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -4176,13 +3976,13 @@
         <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4193,13 +3993,13 @@
         <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -4207,95 +4007,95 @@
         <v>20330051920204</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920207</v>
+        <v>20330051920190</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920202</v>
+        <v>20330051920191</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920214</v>
+        <v>20330051920192</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920218</v>
+        <v>20330051920193</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920190</v>
+        <v>20330051920196</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
       <c r="D9" t="s">
         <v>117</v>
@@ -4306,13 +4106,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920191</v>
+        <v>20330051920197</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D10" t="s">
         <v>118</v>
@@ -4323,13 +4123,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920192</v>
+        <v>20330051920198</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D11" t="s">
         <v>119</v>
@@ -4340,13 +4140,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920193</v>
+        <v>20330051920199</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="D12" t="s">
         <v>120</v>
@@ -4357,13 +4157,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920196</v>
+        <v>20330051920200</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="C13" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D13" t="s">
         <v>121</v>
@@ -4374,13 +4174,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920197</v>
+        <v>20330051920201</v>
       </c>
       <c r="B14" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s">
         <v>122</v>
@@ -4391,13 +4191,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920198</v>
+        <v>19330051920280</v>
       </c>
       <c r="B15" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="C15" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D15" t="s">
         <v>123</v>
@@ -4408,13 +4208,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920199</v>
+        <v>20330051920202</v>
       </c>
       <c r="B16" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C16" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="D16" t="s">
         <v>124</v>
@@ -4425,13 +4225,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920200</v>
+        <v>20330051920206</v>
       </c>
       <c r="B17" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C17" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="D17" t="s">
         <v>125</v>
@@ -4442,13 +4242,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920201</v>
+        <v>20330051920207</v>
       </c>
       <c r="B18" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C18" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="D18" t="s">
         <v>126</v>
@@ -4459,13 +4259,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920280</v>
+        <v>20330051920208</v>
       </c>
       <c r="B19" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C19" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D19" t="s">
         <v>127</v>
@@ -4476,13 +4276,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920206</v>
+        <v>19330051920290</v>
       </c>
       <c r="B20" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C20" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="D20" t="s">
         <v>128</v>
@@ -4493,13 +4293,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920208</v>
+        <v>20330051920209</v>
       </c>
       <c r="B21" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C21" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D21" t="s">
         <v>129</v>
@@ -4510,13 +4310,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920290</v>
+        <v>20330051920210</v>
       </c>
       <c r="B22" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="D22" t="s">
         <v>130</v>
@@ -4527,13 +4327,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920209</v>
+        <v>20330051920212</v>
       </c>
       <c r="B23" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="C23" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D23" t="s">
         <v>131</v>
@@ -4544,13 +4344,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920210</v>
+        <v>20330051920213</v>
       </c>
       <c r="B24" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C24" t="s">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="D24" t="s">
         <v>132</v>
@@ -4561,13 +4361,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920212</v>
+        <v>20330051920214</v>
       </c>
       <c r="B25" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C25" t="s">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="D25" t="s">
         <v>133</v>
@@ -4578,13 +4378,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920213</v>
+        <v>20330051920215</v>
       </c>
       <c r="B26" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="C26" t="s">
-        <v>114</v>
+        <v>64</v>
       </c>
       <c r="D26" t="s">
         <v>134</v>
@@ -4595,13 +4395,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920215</v>
+        <v>19330051920177</v>
       </c>
       <c r="B27" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="C27" t="s">
-        <v>64</v>
+        <v>105</v>
       </c>
       <c r="D27" t="s">
         <v>135</v>
@@ -4612,10 +4412,10 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920177</v>
+        <v>20330051920217</v>
       </c>
       <c r="B28" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="C28" t="s">
         <v>111</v>
@@ -4629,13 +4429,13 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920217</v>
+        <v>20330051920218</v>
       </c>
       <c r="B29" t="s">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="C29" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D29" t="s">
         <v>137</v>
@@ -4649,10 +4449,10 @@
         <v>20330051920219</v>
       </c>
       <c r="B30" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C30" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D30" t="s">
         <v>138</v>
@@ -4666,10 +4466,10 @@
         <v>20330051920259</v>
       </c>
       <c r="B31" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C31" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="D31" t="s">
         <v>139</v>
@@ -4685,7 +4485,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4717,45 +4517,45 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920259</v>
+        <v>20330051920204</v>
       </c>
       <c r="B2" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>139</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920259</v>
+        <v>20330051920204</v>
       </c>
       <c r="B3" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>139</v>
+        <v>71</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4763,22 +4563,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920191</v>
+        <v>20330051920218</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="C4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D4" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4786,22 +4586,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920196</v>
+        <v>20330051920218</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C5" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D5" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4809,48 +4609,94 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920202</v>
+        <v>20330051920191</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>114</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
+        <v>20330051920196</v>
+      </c>
+      <c r="B7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D7" t="s">
+        <v>117</v>
+      </c>
+      <c r="E7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
         <v>20330051920214</v>
       </c>
-      <c r="B7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D7" t="s">
-        <v>82</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="B8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8" t="s">
+        <v>110</v>
+      </c>
+      <c r="D8" t="s">
+        <v>133</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
         <v>54</v>
       </c>
-      <c r="G7">
-        <v>-1</v>
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>20330051920259</v>
+      </c>
+      <c r="B9" t="s">
+        <v>94</v>
+      </c>
+      <c r="C9" t="s">
+        <v>94</v>
+      </c>
+      <c r="D9" t="s">
+        <v>139</v>
+      </c>
+      <c r="E9" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/4ALCV - Estadisticos 20212.xlsx
+++ b/grupos/4ALCV - Estadisticos 20212.xlsx
@@ -969,7 +969,7 @@
         <v>6</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M4">
         <v>5</v>
@@ -1011,7 +1011,7 @@
         <v>6</v>
       </c>
       <c r="Z4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA4">
         <v>5</v>
@@ -1058,7 +1058,7 @@
         <v>6</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
         <v>6</v>
@@ -1100,7 +1100,7 @@
         <v>6</v>
       </c>
       <c r="Z5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA5">
         <v>8</v>
@@ -1147,7 +1147,7 @@
         <v>8</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M6">
         <v>8</v>
@@ -1236,7 +1236,7 @@
         <v>8</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M7">
         <v>6</v>
@@ -1278,7 +1278,7 @@
         <v>7</v>
       </c>
       <c r="Z7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA7">
         <v>8</v>
@@ -1414,7 +1414,7 @@
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M9">
         <v>10</v>
@@ -1592,7 +1592,7 @@
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M11">
         <v>5</v>
@@ -1634,7 +1634,7 @@
         <v>5</v>
       </c>
       <c r="Z11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA11">
         <v>5</v>
@@ -1681,7 +1681,7 @@
         <v>8</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
         <v>10</v>
@@ -1723,7 +1723,7 @@
         <v>7</v>
       </c>
       <c r="Z12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA12">
         <v>10</v>
@@ -1770,7 +1770,7 @@
         <v>5</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M13">
         <v>6</v>
@@ -1812,7 +1812,7 @@
         <v>5</v>
       </c>
       <c r="Z13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA13">
         <v>6</v>
@@ -1859,7 +1859,7 @@
         <v>7</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
         <v>6</v>
@@ -1901,7 +1901,7 @@
         <v>7</v>
       </c>
       <c r="Z14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA14">
         <v>8</v>
@@ -1948,7 +1948,7 @@
         <v>8</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M15">
         <v>9</v>
@@ -1990,7 +1990,7 @@
         <v>7</v>
       </c>
       <c r="Z15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA15">
         <v>9</v>
@@ -2037,7 +2037,7 @@
         <v>7</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M16">
         <v>5</v>
@@ -2079,7 +2079,7 @@
         <v>7</v>
       </c>
       <c r="Z16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA16">
         <v>7</v>
@@ -2126,7 +2126,7 @@
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>10</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
         <v>10</v>
@@ -2357,7 +2357,7 @@
         <v>8</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
         <v>10</v>
@@ -2624,7 +2624,7 @@
         <v>8</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M23">
         <v>9</v>
@@ -2713,7 +2713,7 @@
         <v>10</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
         <v>9</v>
@@ -2802,7 +2802,7 @@
         <v>7</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
         <v>10</v>
@@ -2844,7 +2844,7 @@
         <v>7</v>
       </c>
       <c r="Z25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA25">
         <v>10</v>
@@ -2891,7 +2891,7 @@
         <v>8</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M26">
         <v>9</v>
@@ -2980,7 +2980,7 @@
         <v>8</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M27">
         <v>9</v>
@@ -3069,7 +3069,7 @@
         <v>8</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M28">
         <v>8</v>
@@ -3158,7 +3158,7 @@
         <v>6</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M29">
         <v>5</v>
@@ -3200,7 +3200,7 @@
         <v>6</v>
       </c>
       <c r="Z29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA29">
         <v>6</v>
@@ -3336,7 +3336,7 @@
         <v>7</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M31">
         <v>8</v>
@@ -3425,7 +3425,7 @@
         <v>9</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M32">
         <v>10</v>
@@ -3467,7 +3467,7 @@
         <v>8</v>
       </c>
       <c r="Z32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA32">
         <v>10</v>
@@ -3802,7 +3802,7 @@
         <v>6.9</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/4ALCV - Estadisticos 20212.xlsx
+++ b/grupos/4ALCV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="140">
   <si>
     <t>Materia</t>
   </si>
@@ -185,13 +185,13 @@
     <t>Flores Ovalle Victor</t>
   </si>
   <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
     <t>Martínez Castillo Columba</t>
-  </si>
-  <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
-    <t>González Nuñez Veronica</t>
   </si>
   <si>
     <t>Rivera Serra Alma Lilian</t>
@@ -981,7 +981,7 @@
         <v>6</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q4">
         <v>-1</v>
@@ -990,10 +990,10 @@
         <v>-1</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U4">
         <v>-1</v>
@@ -1002,7 +1002,7 @@
         <v>-1</v>
       </c>
       <c r="W4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X4">
         <v>6</v>
@@ -1070,7 +1070,7 @@
         <v>9</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q5">
         <v>-1</v>
@@ -1079,10 +1079,10 @@
         <v>-1</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U5">
         <v>-1</v>
@@ -1091,7 +1091,7 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X5">
         <v>7</v>
@@ -1100,10 +1100,10 @@
         <v>6</v>
       </c>
       <c r="Z5">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB5">
         <v>7</v>
@@ -1159,7 +1159,7 @@
         <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
         <v>-1</v>
@@ -1168,10 +1168,10 @@
         <v>-1</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U6">
         <v>-1</v>
@@ -1192,7 +1192,7 @@
         <v>9</v>
       </c>
       <c r="AA6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB6">
         <v>10</v>
@@ -1248,7 +1248,7 @@
         <v>9</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
         <v>-1</v>
@@ -1257,10 +1257,10 @@
         <v>-1</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U7">
         <v>-1</v>
@@ -1269,7 +1269,7 @@
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X7">
         <v>6</v>
@@ -1278,10 +1278,10 @@
         <v>7</v>
       </c>
       <c r="Z7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB7">
         <v>7</v>
@@ -1325,7 +1325,7 @@
         <v>5</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M8">
         <v>5</v>
@@ -1337,7 +1337,7 @@
         <v>-1</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q8">
         <v>-1</v>
@@ -1346,10 +1346,10 @@
         <v>-1</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U8">
         <v>-1</v>
@@ -1426,7 +1426,7 @@
         <v>7</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
         <v>-1</v>
@@ -1435,10 +1435,10 @@
         <v>-1</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U9">
         <v>-1</v>
@@ -1447,7 +1447,7 @@
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X9">
         <v>9</v>
@@ -1459,7 +1459,7 @@
         <v>8</v>
       </c>
       <c r="AA9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB9">
         <v>7</v>
@@ -1503,7 +1503,7 @@
         <v>8</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
         <v>5</v>
@@ -1515,7 +1515,7 @@
         <v>6</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q10">
         <v>-1</v>
@@ -1524,10 +1524,10 @@
         <v>-1</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U10">
         <v>-1</v>
@@ -1536,7 +1536,7 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X10">
         <v>-1</v>
@@ -1545,7 +1545,7 @@
         <v>7</v>
       </c>
       <c r="Z10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA10">
         <v>5</v>
@@ -1604,7 +1604,7 @@
         <v>7</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q11">
         <v>-1</v>
@@ -1613,10 +1613,10 @@
         <v>-1</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U11">
         <v>-1</v>
@@ -1625,7 +1625,7 @@
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X11">
         <v>7</v>
@@ -1693,7 +1693,7 @@
         <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
         <v>-1</v>
@@ -1702,10 +1702,10 @@
         <v>-1</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U12">
         <v>-1</v>
@@ -1723,10 +1723,10 @@
         <v>7</v>
       </c>
       <c r="Z12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB12">
         <v>9</v>
@@ -1782,7 +1782,7 @@
         <v>8</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q13">
         <v>-1</v>
@@ -1791,10 +1791,10 @@
         <v>-1</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U13">
         <v>-1</v>
@@ -1803,7 +1803,7 @@
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>9</v>
@@ -1812,7 +1812,7 @@
         <v>5</v>
       </c>
       <c r="Z13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA13">
         <v>6</v>
@@ -1871,7 +1871,7 @@
         <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q14">
         <v>-1</v>
@@ -1880,10 +1880,10 @@
         <v>-1</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U14">
         <v>-1</v>
@@ -1892,7 +1892,7 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X14">
         <v>10</v>
@@ -1901,10 +1901,10 @@
         <v>7</v>
       </c>
       <c r="Z14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AA14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB14">
         <v>10</v>
@@ -1960,7 +1960,7 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
         <v>-1</v>
@@ -1969,10 +1969,10 @@
         <v>-1</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U15">
         <v>-1</v>
@@ -1990,7 +1990,7 @@
         <v>7</v>
       </c>
       <c r="Z15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA15">
         <v>9</v>
@@ -2049,7 +2049,7 @@
         <v>7</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q16">
         <v>-1</v>
@@ -2058,10 +2058,10 @@
         <v>-1</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U16">
         <v>-1</v>
@@ -2070,7 +2070,7 @@
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X16">
         <v>9</v>
@@ -2138,7 +2138,7 @@
         <v>9</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q17">
         <v>-1</v>
@@ -2147,10 +2147,10 @@
         <v>-1</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U17">
         <v>-1</v>
@@ -2227,7 +2227,7 @@
         <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q18">
         <v>-1</v>
@@ -2236,10 +2236,10 @@
         <v>-1</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U18">
         <v>-1</v>
@@ -2248,7 +2248,7 @@
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X18">
         <v>10</v>
@@ -2257,7 +2257,7 @@
         <v>10</v>
       </c>
       <c r="Z18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA18">
         <v>10</v>
@@ -2301,7 +2301,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="U19">
         <v>-1</v>
@@ -2348,7 +2348,7 @@
         <v>9</v>
       </c>
       <c r="I20">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J20">
         <v>10</v>
@@ -2369,7 +2369,7 @@
         <v>10</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q20">
         <v>-1</v>
@@ -2378,10 +2378,10 @@
         <v>-1</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U20">
         <v>-1</v>
@@ -2390,7 +2390,7 @@
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X20">
         <v>10</v>
@@ -2402,7 +2402,7 @@
         <v>10</v>
       </c>
       <c r="AA20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB20">
         <v>9</v>
@@ -2446,7 +2446,7 @@
         <v>5</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M21">
         <v>5</v>
@@ -2458,7 +2458,7 @@
         <v>6</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q21">
         <v>-1</v>
@@ -2467,10 +2467,10 @@
         <v>-1</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U21">
         <v>-1</v>
@@ -2479,7 +2479,7 @@
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X21">
         <v>6</v>
@@ -2535,7 +2535,7 @@
         <v>8</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M22">
         <v>9</v>
@@ -2547,7 +2547,7 @@
         <v>10</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q22">
         <v>-1</v>
@@ -2556,10 +2556,10 @@
         <v>-1</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U22">
         <v>-1</v>
@@ -2568,7 +2568,7 @@
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>8</v>
@@ -2580,7 +2580,7 @@
         <v>9</v>
       </c>
       <c r="AA22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB22">
         <v>7</v>
@@ -2636,7 +2636,7 @@
         <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q23">
         <v>-1</v>
@@ -2645,10 +2645,10 @@
         <v>-1</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U23">
         <v>-1</v>
@@ -2657,7 +2657,7 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X23">
         <v>10</v>
@@ -2666,10 +2666,10 @@
         <v>7</v>
       </c>
       <c r="Z23">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB23">
         <v>8</v>
@@ -2725,7 +2725,7 @@
         <v>10</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
         <v>-1</v>
@@ -2734,10 +2734,10 @@
         <v>-1</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U24">
         <v>-1</v>
@@ -2814,7 +2814,7 @@
         <v>8</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q25">
         <v>-1</v>
@@ -2823,10 +2823,10 @@
         <v>-1</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U25">
         <v>-1</v>
@@ -2844,10 +2844,10 @@
         <v>7</v>
       </c>
       <c r="Z25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB25">
         <v>8</v>
@@ -2903,7 +2903,7 @@
         <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q26">
         <v>-1</v>
@@ -2912,10 +2912,10 @@
         <v>-1</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U26">
         <v>-1</v>
@@ -2924,7 +2924,7 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X26">
         <v>10</v>
@@ -2992,7 +2992,7 @@
         <v>9</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q27">
         <v>-1</v>
@@ -3001,10 +3001,10 @@
         <v>-1</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U27">
         <v>-1</v>
@@ -3013,7 +3013,7 @@
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X27">
         <v>9</v>
@@ -3022,10 +3022,10 @@
         <v>7</v>
       </c>
       <c r="Z27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB27">
         <v>8</v>
@@ -3081,7 +3081,7 @@
         <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
         <v>-1</v>
@@ -3090,10 +3090,10 @@
         <v>-1</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U28">
         <v>-1</v>
@@ -3111,7 +3111,7 @@
         <v>7</v>
       </c>
       <c r="Z28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA28">
         <v>9</v>
@@ -3170,7 +3170,7 @@
         <v>9</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q29">
         <v>-1</v>
@@ -3179,10 +3179,10 @@
         <v>-1</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U29">
         <v>-1</v>
@@ -3191,7 +3191,7 @@
         <v>-1</v>
       </c>
       <c r="W29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X29">
         <v>7</v>
@@ -3247,7 +3247,7 @@
         <v>7</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M30">
         <v>5</v>
@@ -3259,7 +3259,7 @@
         <v>-1</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q30">
         <v>-1</v>
@@ -3268,10 +3268,10 @@
         <v>-1</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U30">
         <v>-1</v>
@@ -3280,7 +3280,7 @@
         <v>-1</v>
       </c>
       <c r="W30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X30">
         <v>6</v>
@@ -3289,10 +3289,10 @@
         <v>8</v>
       </c>
       <c r="Z30">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB30">
         <v>8</v>
@@ -3348,7 +3348,7 @@
         <v>8</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q31">
         <v>-1</v>
@@ -3357,10 +3357,10 @@
         <v>-1</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U31">
         <v>-1</v>
@@ -3369,7 +3369,7 @@
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X31">
         <v>7</v>
@@ -3381,7 +3381,7 @@
         <v>8</v>
       </c>
       <c r="AA31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AB31">
         <v>7</v>
@@ -3437,7 +3437,7 @@
         <v>10</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q32">
         <v>-1</v>
@@ -3446,10 +3446,10 @@
         <v>-1</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U32">
         <v>-1</v>
@@ -3467,10 +3467,10 @@
         <v>8</v>
       </c>
       <c r="Z32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AB32">
         <v>10</v>
@@ -3514,7 +3514,7 @@
         <v>7</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M33">
         <v>7</v>
@@ -3526,7 +3526,7 @@
         <v>8</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q33">
         <v>-1</v>
@@ -3535,10 +3535,10 @@
         <v>-1</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U33">
         <v>-1</v>
@@ -3556,7 +3556,7 @@
         <v>7</v>
       </c>
       <c r="Z33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA33">
         <v>6</v>
@@ -3642,7 +3642,7 @@
         <v>20</v>
       </c>
       <c r="H2">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3717,39 +3717,39 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>55</v>
       </c>
       <c r="C5">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>89.66</v>
+      </c>
+      <c r="G5">
+        <v>10.34</v>
+      </c>
+      <c r="H5">
+        <v>7.7</v>
+      </c>
+      <c r="I5">
         <v>0</v>
       </c>
-      <c r="F5">
-        <v>90</v>
-      </c>
-      <c r="G5">
+      <c r="J5">
         <v>0</v>
-      </c>
-      <c r="H5">
-        <v>8.4</v>
-      </c>
-      <c r="I5">
-        <v>3</v>
-      </c>
-      <c r="J5">
-        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>56</v>
@@ -3758,19 +3758,19 @@
         <v>29</v>
       </c>
       <c r="D6">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>93.09999999999999</v>
+        <v>89.66</v>
       </c>
       <c r="G6">
-        <v>6.9</v>
+        <v>10.34</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3781,34 +3781,34 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>57</v>
       </c>
       <c r="C7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D7">
         <v>27</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>93.09999999999999</v>
+        <v>90</v>
       </c>
       <c r="G7">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -3894,7 +3894,7 @@
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3914,7 +3914,7 @@
         <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3934,7 +3934,7 @@
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -4485,7 +4485,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4532,7 +4532,7 @@
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G2">
         <v>-1</v>
@@ -4609,22 +4609,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920191</v>
+        <v>20330051920259</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4632,22 +4632,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920196</v>
+        <v>20330051920259</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C7" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920214</v>
+        <v>20330051920191</v>
       </c>
       <c r="B8" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -4678,24 +4678,47 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920259</v>
+        <v>20330051920196</v>
       </c>
       <c r="B9" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D9" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>20330051920214</v>
+      </c>
+      <c r="B10" t="s">
+        <v>91</v>
+      </c>
+      <c r="C10" t="s">
+        <v>110</v>
+      </c>
+      <c r="D10" t="s">
+        <v>133</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10">
         <v>5</v>
       </c>
     </row>

--- a/grupos/4ALCV - Estadisticos 20212.xlsx
+++ b/grupos/4ALCV - Estadisticos 20212.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="140">
   <si>
     <t>Materia</t>
   </si>
@@ -182,18 +182,18 @@
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
+    <t>Martínez Castillo Columba</t>
+  </si>
+  <si>
     <t>Flores Ovalle Victor</t>
   </si>
   <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
-    <t>Martínez Castillo Columba</t>
-  </si>
-  <si>
     <t>Rivera Serra Alma Lilian</t>
   </si>
   <si>
@@ -209,190 +209,190 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ASCENCION</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>BALTAZARES</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
     <t>CHICO</t>
   </si>
   <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>ESPERON</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GALVEZ</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
     <t>DE LA LUZ</t>
   </si>
   <si>
+    <t>MELENDEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>PEÑA</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>DE LA TEJA</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>ROQUE</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
     <t>SALGADO</t>
   </si>
   <si>
     <t>OLIVERA</t>
   </si>
   <si>
+    <t>DAMIEN</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>MEJIA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>GALEOTE</t>
+  </si>
+  <si>
+    <t>REYNA ARISBETH</t>
+  </si>
+  <si>
+    <t>ANALI</t>
+  </si>
+  <si>
+    <t>JOCELYN</t>
+  </si>
+  <si>
+    <t>DULCE FERNANDA</t>
+  </si>
+  <si>
     <t>KITZIA YAMILET</t>
   </si>
   <si>
+    <t>ERICK DE JESUS</t>
+  </si>
+  <si>
+    <t>MIA VALENTINA</t>
+  </si>
+  <si>
+    <t>AMARELY GUADALUPE</t>
+  </si>
+  <si>
+    <t>FRIDA SOFIA</t>
+  </si>
+  <si>
+    <t>ANTONIO ABIDAN</t>
+  </si>
+  <si>
+    <t>YAMILET</t>
+  </si>
+  <si>
+    <t>MILAGROS</t>
+  </si>
+  <si>
     <t>ROBERTO JESUS</t>
   </si>
   <si>
+    <t>ITZEL</t>
+  </si>
+  <si>
     <t>CRISTHIAN</t>
-  </si>
-  <si>
-    <t>ASCENCION</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>BALTAZARES</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>ESPERON</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GALVEZ</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MELENDEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>PEÑA</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>DE LA TEJA</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>ROQUE</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>DAMIEN</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>MEJIA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>REYNA ARISBETH</t>
-  </si>
-  <si>
-    <t>ANALI</t>
-  </si>
-  <si>
-    <t>JOCELYN</t>
-  </si>
-  <si>
-    <t>DULCE FERNANDA</t>
-  </si>
-  <si>
-    <t>ERICK DE JESUS</t>
-  </si>
-  <si>
-    <t>MIA VALENTINA</t>
-  </si>
-  <si>
-    <t>AMARELY GUADALUPE</t>
-  </si>
-  <si>
-    <t>FRIDA SOFIA</t>
-  </si>
-  <si>
-    <t>ANTONIO ABIDAN</t>
-  </si>
-  <si>
-    <t>YAMILET</t>
-  </si>
-  <si>
-    <t>MILAGROS</t>
-  </si>
-  <si>
-    <t>ITZEL</t>
   </si>
   <si>
     <t>MARITZA JULIANA</t>
@@ -975,7 +975,7 @@
         <v>5</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O4">
         <v>6</v>
@@ -984,10 +984,10 @@
         <v>5</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S4">
         <v>7</v>
@@ -996,16 +996,16 @@
         <v>4</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>7</v>
       </c>
       <c r="X4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y4">
         <v>6</v>
@@ -1073,10 +1073,10 @@
         <v>6</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S5">
         <v>5</v>
@@ -1085,16 +1085,16 @@
         <v>5</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W5">
         <v>7</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y5">
         <v>6</v>
@@ -1106,10 +1106,10 @@
         <v>7</v>
       </c>
       <c r="AB5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC5">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1162,10 +1162,10 @@
         <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
         <v>9</v>
@@ -1174,10 +1174,10 @@
         <v>8</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W6">
         <v>10</v>
@@ -1186,7 +1186,7 @@
         <v>9</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z6">
         <v>9</v>
@@ -1251,10 +1251,10 @@
         <v>8</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
         <v>5</v>
@@ -1263,16 +1263,16 @@
         <v>6</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>8</v>
       </c>
       <c r="X7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y7">
         <v>7</v>
@@ -1298,7 +1298,7 @@
         <v>5</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D8">
         <v>5</v>
@@ -1319,7 +1319,7 @@
         <v>5</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K8">
         <v>5</v>
@@ -1331,19 +1331,19 @@
         <v>5</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P8">
         <v>5</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S8">
         <v>5</v>
@@ -1352,16 +1352,16 @@
         <v>5</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W8">
         <v>5</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y8">
         <v>5</v>
@@ -1376,7 +1376,7 @@
         <v>5</v>
       </c>
       <c r="AC8">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1411,7 +1411,7 @@
         <v>9</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L9">
         <v>8</v>
@@ -1429,10 +1429,10 @@
         <v>10</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S9">
         <v>8</v>
@@ -1441,10 +1441,10 @@
         <v>7</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W9">
         <v>7</v>
@@ -1465,7 +1465,7 @@
         <v>7</v>
       </c>
       <c r="AC9">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:29">
@@ -1476,7 +1476,7 @@
         <v>10</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D10">
         <v>6</v>
@@ -1497,7 +1497,7 @@
         <v>8</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K10">
         <v>8</v>
@@ -1509,7 +1509,7 @@
         <v>5</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O10">
         <v>6</v>
@@ -1518,10 +1518,10 @@
         <v>7</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S10">
         <v>10</v>
@@ -1530,19 +1530,19 @@
         <v>5</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W10">
         <v>8</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y10">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z10">
         <v>7</v>
@@ -1554,7 +1554,7 @@
         <v>7</v>
       </c>
       <c r="AC10">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:29">
@@ -1589,7 +1589,7 @@
         <v>7</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L11">
         <v>9</v>
@@ -1607,10 +1607,10 @@
         <v>5</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S11">
         <v>7</v>
@@ -1619,10 +1619,10 @@
         <v>5</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>7</v>
@@ -1696,10 +1696,10 @@
         <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S12">
         <v>9</v>
@@ -1708,10 +1708,10 @@
         <v>8</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W12">
         <v>10</v>
@@ -1785,10 +1785,10 @@
         <v>5</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S13">
         <v>6</v>
@@ -1797,16 +1797,16 @@
         <v>6</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W13">
         <v>8</v>
       </c>
       <c r="X13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y13">
         <v>5</v>
@@ -1853,7 +1853,7 @@
         <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K14">
         <v>7</v>
@@ -1874,10 +1874,10 @@
         <v>8</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
         <v>6</v>
@@ -1886,16 +1886,16 @@
         <v>6</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W14">
         <v>9</v>
       </c>
       <c r="X14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y14">
         <v>7</v>
@@ -1963,10 +1963,10 @@
         <v>8</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
         <v>7</v>
@@ -1975,10 +1975,10 @@
         <v>8</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W15">
         <v>9</v>
@@ -2031,7 +2031,7 @@
         <v>7</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K16">
         <v>7</v>
@@ -2052,10 +2052,10 @@
         <v>5</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S16">
         <v>6</v>
@@ -2064,19 +2064,19 @@
         <v>7</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W16">
         <v>7</v>
       </c>
       <c r="X16">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z16">
         <v>7</v>
@@ -2123,7 +2123,7 @@
         <v>10</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L17">
         <v>8</v>
@@ -2141,10 +2141,10 @@
         <v>8</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S17">
         <v>7</v>
@@ -2153,10 +2153,10 @@
         <v>8</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W17">
         <v>8</v>
@@ -2177,7 +2177,7 @@
         <v>8</v>
       </c>
       <c r="AC17">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2230,10 +2230,10 @@
         <v>7</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
         <v>8</v>
@@ -2242,10 +2242,10 @@
         <v>9</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W18">
         <v>9</v>
@@ -2274,7 +2274,7 @@
         <v>28</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F19">
         <v>5</v>
@@ -2286,31 +2286,31 @@
         <v>5</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M19">
         <v>5</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T19">
         <v>4</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA19">
         <v>5</v>
@@ -2372,10 +2372,10 @@
         <v>9</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S20">
         <v>9</v>
@@ -2384,10 +2384,10 @@
         <v>8</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W20">
         <v>9</v>
@@ -2440,7 +2440,7 @@
         <v>5</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K21">
         <v>5</v>
@@ -2452,7 +2452,7 @@
         <v>5</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O21">
         <v>6</v>
@@ -2461,10 +2461,10 @@
         <v>5</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S21">
         <v>5</v>
@@ -2473,16 +2473,16 @@
         <v>5</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W21">
         <v>5</v>
       </c>
       <c r="X21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y21">
         <v>5</v>
@@ -2497,7 +2497,7 @@
         <v>5</v>
       </c>
       <c r="AC21">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2550,10 +2550,10 @@
         <v>7</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S22">
         <v>9</v>
@@ -2562,10 +2562,10 @@
         <v>7</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W22">
         <v>8</v>
@@ -2583,7 +2583,7 @@
         <v>9</v>
       </c>
       <c r="AB22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC22">
         <v>10</v>
@@ -2639,10 +2639,10 @@
         <v>7</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S23">
         <v>5</v>
@@ -2651,16 +2651,16 @@
         <v>6</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W23">
         <v>8</v>
       </c>
       <c r="X23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y23">
         <v>7</v>
@@ -2728,10 +2728,10 @@
         <v>10</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
         <v>9</v>
@@ -2740,10 +2740,10 @@
         <v>8</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W24">
         <v>10</v>
@@ -2817,10 +2817,10 @@
         <v>6</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S25">
         <v>7</v>
@@ -2829,16 +2829,16 @@
         <v>6</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W25">
         <v>7</v>
       </c>
       <c r="X25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y25">
         <v>7</v>
@@ -2906,10 +2906,10 @@
         <v>6</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S26">
         <v>8</v>
@@ -2918,10 +2918,10 @@
         <v>9</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W26">
         <v>7</v>
@@ -2995,10 +2995,10 @@
         <v>7</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S27">
         <v>7</v>
@@ -3007,10 +3007,10 @@
         <v>6</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W27">
         <v>7</v>
@@ -3084,10 +3084,10 @@
         <v>10</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
         <v>7</v>
@@ -3096,10 +3096,10 @@
         <v>8</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W28">
         <v>10</v>
@@ -3108,7 +3108,7 @@
         <v>9</v>
       </c>
       <c r="Y28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z28">
         <v>8</v>
@@ -3164,7 +3164,7 @@
         <v>5</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O29">
         <v>9</v>
@@ -3173,10 +3173,10 @@
         <v>6</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S29">
         <v>8</v>
@@ -3185,16 +3185,16 @@
         <v>6</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W29">
         <v>7</v>
       </c>
       <c r="X29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y29">
         <v>6</v>
@@ -3206,7 +3206,7 @@
         <v>6</v>
       </c>
       <c r="AB29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC29">
         <v>9</v>
@@ -3256,16 +3256,16 @@
         <v>8</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P30">
         <v>5</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S30">
         <v>5</v>
@@ -3274,19 +3274,19 @@
         <v>5</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W30">
         <v>6</v>
       </c>
       <c r="X30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z30">
         <v>6</v>
@@ -3298,7 +3298,7 @@
         <v>8</v>
       </c>
       <c r="AC30">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3351,10 +3351,10 @@
         <v>5</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S31">
         <v>7</v>
@@ -3363,16 +3363,16 @@
         <v>6</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W31">
         <v>6</v>
       </c>
       <c r="X31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y31">
         <v>7</v>
@@ -3384,10 +3384,10 @@
         <v>8</v>
       </c>
       <c r="AB31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC31">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -3440,10 +3440,10 @@
         <v>10</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
         <v>8</v>
@@ -3452,10 +3452,10 @@
         <v>8</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W32">
         <v>10</v>
@@ -3464,7 +3464,7 @@
         <v>10</v>
       </c>
       <c r="Y32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z32">
         <v>9</v>
@@ -3520,7 +3520,7 @@
         <v>7</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O33">
         <v>8</v>
@@ -3529,10 +3529,10 @@
         <v>5</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S33">
         <v>5</v>
@@ -3541,19 +3541,19 @@
         <v>7</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W33">
         <v>5</v>
       </c>
       <c r="X33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z33">
         <v>5</v>
@@ -3562,7 +3562,7 @@
         <v>6</v>
       </c>
       <c r="AB33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC33">
         <v>7</v>
@@ -3662,16 +3662,16 @@
         <v>29</v>
       </c>
       <c r="D3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>86.20999999999999</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="G3">
-        <v>13.79</v>
+        <v>17.24</v>
       </c>
       <c r="H3">
         <v>6.8</v>
@@ -3685,28 +3685,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>54</v>
       </c>
       <c r="C4">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4">
         <v>26</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>86.67</v>
+        <v>89.66</v>
       </c>
       <c r="G4">
-        <v>13.33</v>
+        <v>10.34</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3717,7 +3717,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>55</v>
@@ -3749,28 +3749,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>56</v>
       </c>
       <c r="C6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E6">
         <v>3</v>
       </c>
       <c r="F6">
-        <v>89.66</v>
+        <v>90</v>
       </c>
       <c r="G6">
-        <v>10.34</v>
+        <v>10</v>
       </c>
       <c r="H6">
-        <v>7.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3781,7 +3781,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>57</v>
@@ -3793,22 +3793,22 @@
         <v>27</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F7">
         <v>90</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H7">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="I7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -3834,7 +3834,7 @@
         <v>3.33</v>
       </c>
       <c r="H8">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -3850,7 +3850,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3875,66 +3875,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>20330051920194</v>
-      </c>
-      <c r="B2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>19330051920420</v>
-      </c>
-      <c r="B3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>20330051920204</v>
-      </c>
-      <c r="B4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" t="s">
-        <v>68</v>
-      </c>
-      <c r="D4" t="s">
-        <v>71</v>
-      </c>
-      <c r="E4" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -3970,64 +3910,64 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920194</v>
+        <v>20330051920190</v>
       </c>
       <c r="B2" t="s">
         <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>110</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920420</v>
+        <v>20330051920191</v>
       </c>
       <c r="B3" t="s">
         <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>111</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920204</v>
+        <v>20330051920192</v>
       </c>
       <c r="B4" t="s">
         <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>71</v>
+        <v>112</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920190</v>
+        <v>20330051920193</v>
       </c>
       <c r="B5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" t="s">
         <v>72</v>
-      </c>
-      <c r="C5" t="s">
-        <v>95</v>
       </c>
       <c r="D5" t="s">
         <v>113</v>
@@ -4038,13 +3978,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920191</v>
+        <v>20330051920194</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D6" t="s">
         <v>114</v>
@@ -4055,13 +3995,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920192</v>
+        <v>20330051920196</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
         <v>115</v>
@@ -4072,13 +4012,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920193</v>
+        <v>20330051920197</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
         <v>116</v>
@@ -4089,13 +4029,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920196</v>
+        <v>20330051920198</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D9" t="s">
         <v>117</v>
@@ -4106,13 +4046,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920197</v>
+        <v>20330051920199</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D10" t="s">
         <v>118</v>
@@ -4123,13 +4063,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920198</v>
+        <v>20330051920200</v>
       </c>
       <c r="B11" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D11" t="s">
         <v>119</v>
@@ -4140,13 +4080,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920199</v>
+        <v>20330051920201</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="D12" t="s">
         <v>120</v>
@@ -4157,13 +4097,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920200</v>
+        <v>19330051920280</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="D13" t="s">
         <v>121</v>
@@ -4174,13 +4114,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920201</v>
+        <v>19330051920420</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="D14" t="s">
         <v>122</v>
@@ -4191,13 +4131,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920280</v>
+        <v>20330051920202</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="D15" t="s">
         <v>123</v>
@@ -4208,13 +4148,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920202</v>
+        <v>20330051920204</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D16" t="s">
         <v>124</v>
@@ -4228,10 +4168,10 @@
         <v>20330051920206</v>
       </c>
       <c r="B17" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C17" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="D17" t="s">
         <v>125</v>
@@ -4245,10 +4185,10 @@
         <v>20330051920207</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D18" t="s">
         <v>126</v>
@@ -4262,10 +4202,10 @@
         <v>20330051920208</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C19" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D19" t="s">
         <v>127</v>
@@ -4279,10 +4219,10 @@
         <v>19330051920290</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C20" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D20" t="s">
         <v>128</v>
@@ -4296,10 +4236,10 @@
         <v>20330051920209</v>
       </c>
       <c r="B21" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C21" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D21" t="s">
         <v>129</v>
@@ -4313,10 +4253,10 @@
         <v>20330051920210</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C22" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="D22" t="s">
         <v>130</v>
@@ -4330,10 +4270,10 @@
         <v>20330051920212</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C23" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D23" t="s">
         <v>131</v>
@@ -4347,10 +4287,10 @@
         <v>20330051920213</v>
       </c>
       <c r="B24" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="C24" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D24" t="s">
         <v>132</v>
@@ -4364,10 +4304,10 @@
         <v>20330051920214</v>
       </c>
       <c r="B25" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C25" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D25" t="s">
         <v>133</v>
@@ -4381,10 +4321,10 @@
         <v>20330051920215</v>
       </c>
       <c r="B26" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C26" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="D26" t="s">
         <v>134</v>
@@ -4398,10 +4338,10 @@
         <v>19330051920177</v>
       </c>
       <c r="B27" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C27" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D27" t="s">
         <v>135</v>
@@ -4415,10 +4355,10 @@
         <v>20330051920217</v>
       </c>
       <c r="B28" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C28" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D28" t="s">
         <v>136</v>
@@ -4432,10 +4372,10 @@
         <v>20330051920218</v>
       </c>
       <c r="B29" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C29" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D29" t="s">
         <v>137</v>
@@ -4449,10 +4389,10 @@
         <v>20330051920219</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C30" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D30" t="s">
         <v>138</v>
@@ -4466,10 +4406,10 @@
         <v>20330051920259</v>
       </c>
       <c r="B31" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C31" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D31" t="s">
         <v>139</v>
@@ -4485,7 +4425,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4520,22 +4460,22 @@
         <v>20330051920204</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>124</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -4543,13 +4483,13 @@
         <v>20330051920204</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>124</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -4566,10 +4506,10 @@
         <v>20330051920218</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D4" t="s">
         <v>137</v>
@@ -4589,10 +4529,10 @@
         <v>20330051920218</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D5" t="s">
         <v>137</v>
@@ -4612,10 +4552,10 @@
         <v>20330051920259</v>
       </c>
       <c r="B6" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D6" t="s">
         <v>139</v>
@@ -4624,7 +4564,7 @@
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4635,10 +4575,10 @@
         <v>20330051920259</v>
       </c>
       <c r="B7" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D7" t="s">
         <v>139</v>
@@ -4647,7 +4587,7 @@
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4658,13 +4598,13 @@
         <v>20330051920191</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -4681,13 +4621,13 @@
         <v>20330051920196</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
@@ -4696,29 +4636,6 @@
         <v>53</v>
       </c>
       <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920214</v>
-      </c>
-      <c r="B10" t="s">
-        <v>91</v>
-      </c>
-      <c r="C10" t="s">
-        <v>110</v>
-      </c>
-      <c r="D10" t="s">
-        <v>133</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>54</v>
-      </c>
-      <c r="G10">
         <v>5</v>
       </c>
     </row>
